--- a/Outputs/Recycling_Plot_Data/ACCII/08_Recycled_Content_Ratio_data_ACCII.xlsx
+++ b/Outputs/Recycling_Plot_Data/ACCII/08_Recycled_Content_Ratio_data_ACCII.xlsx
@@ -421,7 +421,7 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.4523874089146827</v>
+        <v>0.4521593870929269</v>
       </c>
     </row>
     <row r="3">
@@ -454,7 +454,7 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.4523874089146827</v>
+        <v>0.4521593870929269</v>
       </c>
     </row>
     <row r="4">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.55871107397645</v>
+        <v>0.5527615716926496</v>
       </c>
     </row>
     <row r="5">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="G5">
-        <v>0.55871107397645</v>
+        <v>0.5527615716926496</v>
       </c>
     </row>
     <row r="6">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="G6">
-        <v>0.7678281512174451</v>
+        <v>0.7607658784707583</v>
       </c>
     </row>
     <row r="7">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="G7">
-        <v>0.7678281512174451</v>
+        <v>0.7607658784707583</v>
       </c>
     </row>
     <row r="8">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="G8">
-        <v>1.027394323478352</v>
+        <v>1.018071986847554</v>
       </c>
     </row>
     <row r="9">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="G9">
-        <v>1.027394323478352</v>
+        <v>1.018071986847554</v>
       </c>
     </row>
     <row r="10">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="G10">
-        <v>1.315909715527853</v>
+        <v>1.30377805114819</v>
       </c>
     </row>
     <row r="11">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="G11">
-        <v>1.315909715527853</v>
+        <v>1.30377805114819</v>
       </c>
     </row>
     <row r="12">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="G12">
-        <v>1.706489010837948</v>
+        <v>1.689854044089737</v>
       </c>
     </row>
     <row r="13">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="G13">
-        <v>1.706489010837948</v>
+        <v>1.689854044089737</v>
       </c>
     </row>
     <row r="14">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="G14">
-        <v>2.218361321166414</v>
+        <v>2.195903154727183</v>
       </c>
     </row>
     <row r="15">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="G15">
-        <v>2.218361321166414</v>
+        <v>2.195903154727183</v>
       </c>
     </row>
     <row r="16">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="G16">
-        <v>2.693464065038904</v>
+        <v>2.663770166401768</v>
       </c>
     </row>
     <row r="17">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="G17">
-        <v>2.693464065038904</v>
+        <v>2.663770166401768</v>
       </c>
     </row>
     <row r="18">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="G18">
-        <v>3.287562633754831</v>
+        <v>3.248366975203735</v>
       </c>
     </row>
     <row r="19">
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="G19">
-        <v>3.287562633754831</v>
+        <v>3.248366975203735</v>
       </c>
     </row>
     <row r="20">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="G20">
-        <v>4.079076900334417</v>
+        <v>4.025519094929882</v>
       </c>
     </row>
     <row r="21">
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="G21">
-        <v>4.079076900334417</v>
+        <v>4.025519094929882</v>
       </c>
     </row>
     <row r="22">
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="G22">
-        <v>4.694949381209558</v>
+        <v>4.684537857923211</v>
       </c>
     </row>
     <row r="23">
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="G23">
-        <v>5.436082542549824</v>
+        <v>5.358599850220956</v>
       </c>
     </row>
     <row r="24">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="G24">
-        <v>4.558997381028177</v>
+        <v>4.551064103813219</v>
       </c>
     </row>
     <row r="25">
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="G25">
-        <v>7.240586914157496</v>
+        <v>7.133135988846494</v>
       </c>
     </row>
     <row r="26">
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="G26">
-        <v>4.448664848049931</v>
+        <v>4.445246483813185</v>
       </c>
     </row>
     <row r="27">
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="G27">
-        <v>9.43723256199657</v>
+        <v>9.296456154158108</v>
       </c>
     </row>
     <row r="28">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="G28">
-        <v>4.448108257249241</v>
+        <v>4.424880945252663</v>
       </c>
     </row>
     <row r="29">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="G29">
-        <v>13.08618924387706</v>
+        <v>12.63600910159174</v>
       </c>
     </row>
     <row r="30">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="G30">
-        <v>4.196707794089923</v>
+        <v>4.177671167438994</v>
       </c>
     </row>
     <row r="31">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="G31">
-        <v>15.86511288611039</v>
+        <v>15.36515009241974</v>
       </c>
     </row>
     <row r="32">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="G32">
-        <v>4.030164521897012</v>
+        <v>4.015766972590634</v>
       </c>
     </row>
     <row r="33">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G33">
-        <v>19.13541095219628</v>
+        <v>18.62817180329625</v>
       </c>
     </row>
     <row r="34">
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="G34">
-        <v>3.859613141217878</v>
+        <v>3.849847877797227</v>
       </c>
     </row>
     <row r="35">
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="G35">
-        <v>22.43431692147873</v>
+        <v>21.98111436141375</v>
       </c>
     </row>
     <row r="36">
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="G36">
-        <v>3.691400421882858</v>
+        <v>3.68543010279599</v>
       </c>
     </row>
     <row r="37">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="G37">
-        <v>25.90994121273183</v>
+        <v>25.55001134785422</v>
       </c>
     </row>
     <row r="38">
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="G38">
-        <v>3.54306629923019</v>
+        <v>3.539900400321864</v>
       </c>
     </row>
     <row r="39">
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="G39">
-        <v>29.66497847204212</v>
+        <v>29.40640524213769</v>
       </c>
     </row>
     <row r="40">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="G40">
-        <v>3.415396602736775</v>
+        <v>3.414025844774673</v>
       </c>
     </row>
     <row r="41">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="G41">
-        <v>33.70358787712656</v>
+        <v>33.52853106643267</v>
       </c>
     </row>
     <row r="42">
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="G42">
-        <v>3.306865725568428</v>
+        <v>3.306640284973502</v>
       </c>
     </row>
     <row r="43">
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="G43">
-        <v>38.00810970537656</v>
+        <v>37.89077543548215</v>
       </c>
     </row>
     <row r="44">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="G44">
-        <v>3.216960866952519</v>
+        <v>3.217605832572886</v>
       </c>
     </row>
     <row r="45">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="G45">
-        <v>42.61455251599821</v>
+        <v>42.53450974228556</v>
       </c>
     </row>
     <row r="46">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="G46">
-        <v>3.139884167891305</v>
+        <v>3.141343510353849</v>
       </c>
     </row>
     <row r="47">
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="G47">
-        <v>47.34305997329596</v>
+        <v>47.28814538114669</v>
       </c>
     </row>
     <row r="48">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="G48">
-        <v>3.074375546949011</v>
+        <v>3.076727187526864</v>
       </c>
     </row>
     <row r="49">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="G49">
-        <v>52.14206790480269</v>
+        <v>52.10670597421346</v>
       </c>
     </row>
     <row r="50">
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="G50">
-        <v>3.015756821385363</v>
+        <v>3.019046172435904</v>
       </c>
     </row>
     <row r="51">
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="G51">
-        <v>56.67165282802686</v>
+        <v>56.65194039013981</v>
       </c>
     </row>
     <row r="52">
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="G52">
-        <v>0.4698271325462957</v>
+        <v>0.4695902867118504</v>
       </c>
     </row>
     <row r="53">
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="G53">
-        <v>0.4698271325462957</v>
+        <v>0.4695902867118504</v>
       </c>
     </row>
     <row r="54">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="G54">
-        <v>0.608425671508091</v>
+        <v>0.6019422634526058</v>
       </c>
     </row>
     <row r="55">
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="G55">
-        <v>0.608425671508091</v>
+        <v>0.6019422634526058</v>
       </c>
     </row>
     <row r="56">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="G56">
-        <v>0.8652374468812704</v>
+        <v>0.8572597972662875</v>
       </c>
     </row>
     <row r="57">
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="G57">
-        <v>0.8652374468812704</v>
+        <v>0.8572597972662875</v>
       </c>
     </row>
     <row r="58">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="G58">
-        <v>1.192702048248255</v>
+        <v>1.181831385976293</v>
       </c>
     </row>
     <row r="59">
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="G59">
-        <v>1.192702048248255</v>
+        <v>1.181831385976293</v>
       </c>
     </row>
     <row r="60">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="G60">
-        <v>1.566331970021094</v>
+        <v>1.551789059870823</v>
       </c>
     </row>
     <row r="61">
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="G61">
-        <v>1.566331970021094</v>
+        <v>1.551789059870823</v>
       </c>
     </row>
     <row r="62">
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="G62">
-        <v>2.070954206790327</v>
+        <v>2.050555138313961</v>
       </c>
     </row>
     <row r="63">
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="G63">
-        <v>2.070954206790327</v>
+        <v>2.050555138313961</v>
       </c>
     </row>
     <row r="64">
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="G64">
-        <v>2.751140779135163</v>
+        <v>2.722905360977651</v>
       </c>
     </row>
     <row r="65">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="G65">
-        <v>2.751140779135163</v>
+        <v>2.722905360977651</v>
       </c>
     </row>
     <row r="66">
@@ -2533,7 +2533,7 @@
         </is>
       </c>
       <c r="G66">
-        <v>3.422197978934957</v>
+        <v>3.383802117550839</v>
       </c>
     </row>
     <row r="67">
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="G67">
-        <v>3.422197978934957</v>
+        <v>3.383802117550839</v>
       </c>
     </row>
     <row r="68">
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="G68">
-        <v>4.272213909453322</v>
+        <v>4.220118532851214</v>
       </c>
     </row>
     <row r="69">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="G69">
-        <v>4.272213909453322</v>
+        <v>4.220118532851214</v>
       </c>
     </row>
     <row r="70">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="G70">
-        <v>5.413070642458695</v>
+        <v>5.339981829698603</v>
       </c>
     </row>
     <row r="71">
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="G71">
-        <v>5.413070642458695</v>
+        <v>5.339981829698603</v>
       </c>
     </row>
     <row r="72">
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="G72">
-        <v>6.301222903221233</v>
+        <v>6.283791654995656</v>
       </c>
     </row>
     <row r="73">
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="G73">
-        <v>7.328222741483296</v>
+        <v>7.220163649372795</v>
       </c>
     </row>
     <row r="74">
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="G74">
-        <v>6.186620040536204</v>
+        <v>6.171535707509848</v>
       </c>
     </row>
     <row r="75">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="G75">
-        <v>9.877908657835398</v>
+        <v>9.725132948289849</v>
       </c>
     </row>
     <row r="76">
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="G76">
-        <v>6.092594511325744</v>
+        <v>6.082519290165072</v>
       </c>
     </row>
     <row r="77">
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="G77">
-        <v>13.00753568546812</v>
+        <v>12.80314930225438</v>
       </c>
     </row>
     <row r="78">
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="G78">
-        <v>6.1460552848654</v>
+        <v>6.100974694866637</v>
       </c>
     </row>
     <row r="79">
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="G79">
-        <v>18.21272284148079</v>
+        <v>17.55239034623512</v>
       </c>
     </row>
     <row r="80">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="G80">
-        <v>5.868637534135924</v>
+        <v>5.827530256914849</v>
       </c>
     </row>
     <row r="81">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="G81">
-        <v>22.38650877259519</v>
+        <v>21.63225130762005</v>
       </c>
     </row>
     <row r="82">
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="G82">
-        <v>5.524241405751948</v>
+        <v>5.489598373664651</v>
       </c>
     </row>
     <row r="83">
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="G83">
-        <v>26.53342803848622</v>
+        <v>25.76643877355414</v>
       </c>
     </row>
     <row r="84">
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="G84">
-        <v>5.162002706327304</v>
+        <v>5.135382548099668</v>
       </c>
     </row>
     <row r="85">
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="G85">
-        <v>30.44651507924533</v>
+        <v>29.75980770251139</v>
       </c>
     </row>
     <row r="86">
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="G86">
-        <v>4.802253046980214</v>
+        <v>4.783759353382617</v>
       </c>
     </row>
     <row r="87">
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="G87">
-        <v>34.32276517422599</v>
+        <v>33.77674088066723</v>
       </c>
     </row>
     <row r="88">
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="G88">
-        <v>4.478701975152728</v>
+        <v>4.467241206143811</v>
       </c>
     </row>
     <row r="89">
@@ -3292,7 +3292,7 @@
         </is>
       </c>
       <c r="G89">
-        <v>38.32294873551984</v>
+        <v>37.93087981937205</v>
       </c>
     </row>
     <row r="90">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="G90">
-        <v>4.198998880737379</v>
+        <v>4.192575383066272</v>
       </c>
     </row>
     <row r="91">
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="G91">
-        <v>42.49705414350711</v>
+        <v>42.2324599944119</v>
       </c>
     </row>
     <row r="92">
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="G92">
-        <v>3.959128476878877</v>
+        <v>3.955949273488093</v>
       </c>
     </row>
     <row r="93">
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="G93">
-        <v>46.82829812081607</v>
+        <v>46.65206933314471</v>
       </c>
     </row>
     <row r="94">
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="G94">
-        <v>3.753314504989873</v>
+        <v>3.752262915368203</v>
       </c>
     </row>
     <row r="95">
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="G95">
-        <v>51.33444919693832</v>
+        <v>51.2151470610106</v>
       </c>
     </row>
     <row r="96">
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="G96">
-        <v>3.571966528880704</v>
+        <v>3.572491801105376</v>
       </c>
     </row>
     <row r="97">
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="G97">
-        <v>55.78520183231029</v>
+        <v>55.70385910277938</v>
       </c>
     </row>
     <row r="98">
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="G98">
-        <v>3.412150359654145</v>
+        <v>3.414057382857135</v>
       </c>
     </row>
     <row r="99">
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="G99">
-        <v>60.12659906278108</v>
+        <v>60.07393771716898</v>
       </c>
     </row>
     <row r="100">
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="G100">
-        <v>3.269418949563661</v>
+        <v>3.272573994609719</v>
       </c>
     </row>
     <row r="101">
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="G101">
-        <v>64.01432888296603</v>
+        <v>63.98399204958378</v>
       </c>
     </row>
     <row r="102">
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="G102">
-        <v>0.5071291604531932</v>
+        <v>0.5068564951210688</v>
       </c>
     </row>
     <row r="103">
@@ -3754,7 +3754,7 @@
         </is>
       </c>
       <c r="G103">
-        <v>0.5071291604531932</v>
+        <v>0.5068564951210688</v>
       </c>
     </row>
     <row r="104">
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="G104">
-        <v>0.6593717673402946</v>
+        <v>0.6525254686105553</v>
       </c>
     </row>
     <row r="105">
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="G105">
-        <v>0.6593717673402946</v>
+        <v>0.6525254686105553</v>
       </c>
     </row>
     <row r="106">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="G106">
-        <v>0.9500257664268189</v>
+        <v>0.9414581687305625</v>
       </c>
     </row>
     <row r="107">
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="G107">
-        <v>0.9500257664268189</v>
+        <v>0.9414581687305625</v>
       </c>
     </row>
     <row r="108">
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="G108">
-        <v>1.330477703211771</v>
+        <v>1.318576481597203</v>
       </c>
     </row>
     <row r="109">
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="G109">
-        <v>1.330477703211771</v>
+        <v>1.318576481597203</v>
       </c>
     </row>
     <row r="110">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="G110">
-        <v>1.781530518427571</v>
+        <v>1.765248828027296</v>
       </c>
     </row>
     <row r="111">
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="G111">
-        <v>1.781530518427571</v>
+        <v>1.765248828027296</v>
       </c>
     </row>
     <row r="112">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="G112">
-        <v>2.408742674182713</v>
+        <v>2.385297726569596</v>
       </c>
     </row>
     <row r="113">
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="G113">
-        <v>2.408742674182713</v>
+        <v>2.385297726569596</v>
       </c>
     </row>
     <row r="114">
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="G114">
-        <v>3.262915642875637</v>
+        <v>3.229701985227562</v>
       </c>
     </row>
     <row r="115">
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="G115">
-        <v>3.262915642875637</v>
+        <v>3.229701985227562</v>
       </c>
     </row>
     <row r="116">
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="G116">
-        <v>4.118303292541357</v>
+        <v>4.072273732591635</v>
       </c>
     </row>
     <row r="117">
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="G117">
-        <v>4.118303292541357</v>
+        <v>4.072273732591635</v>
       </c>
     </row>
     <row r="118">
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="G118">
-        <v>5.210730783000335</v>
+        <v>5.147147789002354</v>
       </c>
     </row>
     <row r="119">
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="G119">
-        <v>5.210730783000335</v>
+        <v>5.147147789002354</v>
       </c>
     </row>
     <row r="120">
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="G120">
-        <v>6.694595074656889</v>
+        <v>6.603705850511648</v>
       </c>
     </row>
     <row r="121">
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="G121">
-        <v>6.694595074656889</v>
+        <v>6.603705850511648</v>
       </c>
     </row>
     <row r="122">
@@ -4381,7 +4381,7 @@
         </is>
       </c>
       <c r="G122">
-        <v>8.934136865063886</v>
+        <v>8.800997880999287</v>
       </c>
     </row>
     <row r="123">
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="G123">
-        <v>8.934136865063886</v>
+        <v>8.800997880999287</v>
       </c>
     </row>
     <row r="124">
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="G124">
-        <v>10.88281317013462</v>
+        <v>10.87486449268053</v>
       </c>
     </row>
     <row r="125">
@@ -4480,7 +4480,7 @@
         </is>
       </c>
       <c r="G125">
-        <v>11.90593056926635</v>
+        <v>11.7189357400846</v>
       </c>
     </row>
     <row r="126">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="G126">
-        <v>10.73774159134397</v>
+        <v>10.74146332412868</v>
       </c>
     </row>
     <row r="127">
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="G127">
-        <v>15.4888844216235</v>
+        <v>15.240366156418</v>
       </c>
     </row>
     <row r="128">
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="G128">
-        <v>10.79300653410851</v>
+        <v>10.75739080243197</v>
       </c>
     </row>
     <row r="129">
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="G129">
-        <v>21.47332029050401</v>
+        <v>20.67168169796034</v>
       </c>
     </row>
     <row r="130">
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="G130">
-        <v>10.23890603916978</v>
+        <v>10.20766354173831</v>
       </c>
     </row>
     <row r="131">
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="G131">
-        <v>25.67470907716181</v>
+        <v>24.77220091717705</v>
       </c>
     </row>
     <row r="132">
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="G132">
-        <v>9.760637143411838</v>
+        <v>9.734737738558874</v>
       </c>
     </row>
     <row r="133">
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="G133">
-        <v>30.01930978592475</v>
+        <v>29.10076976998466</v>
       </c>
     </row>
     <row r="134">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="G134">
-        <v>9.253337238591081</v>
+        <v>9.233464858197131</v>
       </c>
     </row>
     <row r="135">
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="G135">
-        <v>33.9251647364685</v>
+        <v>33.10243922173436</v>
       </c>
     </row>
     <row r="136">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="G136">
-        <v>8.743576589486457</v>
+        <v>8.7294864684446</v>
       </c>
     </row>
     <row r="137">
@@ -4876,7 +4876,7 @@
         </is>
       </c>
       <c r="G137">
-        <v>37.6348998918608</v>
+        <v>36.98070960296525</v>
       </c>
     </row>
     <row r="138">
@@ -4909,7 +4909,7 @@
         </is>
       </c>
       <c r="G138">
-        <v>8.289122319145616</v>
+        <v>8.280353245369071</v>
       </c>
     </row>
     <row r="139">
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c r="G139">
-        <v>41.33971556475576</v>
+        <v>40.87029772742359</v>
       </c>
     </row>
     <row r="140">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="G140">
-        <v>7.896205046899631</v>
+        <v>7.891507132427892</v>
       </c>
     </row>
     <row r="141">
@@ -5008,7 +5008,7 @@
         </is>
       </c>
       <c r="G141">
-        <v>45.10078279792687</v>
+        <v>44.78452349425995</v>
       </c>
     </row>
     <row r="142">
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="G142">
-        <v>7.562231579111119</v>
+        <v>7.560489145124611</v>
       </c>
     </row>
     <row r="143">
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="G143">
-        <v>48.9206319938151</v>
+        <v>48.71061898028662</v>
       </c>
     </row>
     <row r="144">
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="G144">
-        <v>7.283187024813979</v>
+        <v>7.283799877847221</v>
       </c>
     </row>
     <row r="145">
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="G145">
-        <v>52.84241714396693</v>
+        <v>52.70067602439544</v>
       </c>
     </row>
     <row r="146">
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="G146">
-        <v>7.044928894812269</v>
+        <v>7.047721431387929</v>
       </c>
     </row>
     <row r="147">
@@ -5206,7 +5206,7 @@
         </is>
       </c>
       <c r="G147">
-        <v>56.65743228906601</v>
+        <v>56.56095302961638</v>
       </c>
     </row>
     <row r="148">
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="G148">
-        <v>6.84214210574866</v>
+        <v>6.847239040624155</v>
       </c>
     </row>
     <row r="149">
@@ -5272,7 +5272,7 @@
         </is>
       </c>
       <c r="G149">
-        <v>60.3357902486316</v>
+        <v>60.27300574091815</v>
       </c>
     </row>
     <row r="150">
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="G150">
-        <v>6.667800959234503</v>
+        <v>6.675270221378926</v>
       </c>
     </row>
     <row r="151">
@@ -5338,7 +5338,7 @@
         </is>
       </c>
       <c r="G151">
-        <v>63.70108281883291</v>
+        <v>63.66413943368816</v>
       </c>
     </row>
     <row r="152">
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="G152">
-        <v>0.5266673412724786</v>
+        <v>0.5263841323177446</v>
       </c>
     </row>
     <row r="153">
@@ -5404,7 +5404,7 @@
         </is>
       </c>
       <c r="G153">
-        <v>0.5266673412724786</v>
+        <v>0.5263841323177446</v>
       </c>
     </row>
     <row r="154">
@@ -5437,7 +5437,7 @@
         </is>
       </c>
       <c r="G154">
-        <v>0.7179892944859966</v>
+        <v>0.710529302440013</v>
       </c>
     </row>
     <row r="155">
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="G155">
-        <v>0.7179892944859966</v>
+        <v>0.710529302440013</v>
       </c>
     </row>
     <row r="156">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="G156">
-        <v>1.070583547586565</v>
+        <v>1.060906976180135</v>
       </c>
     </row>
     <row r="157">
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="G157">
-        <v>1.070583547586565</v>
+        <v>1.060906976180135</v>
       </c>
     </row>
     <row r="158">
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="G158">
-        <v>1.544912063107286</v>
+        <v>1.531037315233602</v>
       </c>
     </row>
     <row r="159">
@@ -5602,7 +5602,7 @@
         </is>
       </c>
       <c r="G159">
-        <v>1.544912063107286</v>
+        <v>1.531037315233602</v>
       </c>
     </row>
     <row r="160">
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="G160">
-        <v>2.1217767377025</v>
+        <v>2.102265444681175</v>
       </c>
     </row>
     <row r="161">
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="G161">
-        <v>2.1217767377025</v>
+        <v>2.102265444681175</v>
       </c>
     </row>
     <row r="162">
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="G162">
-        <v>2.926084750400996</v>
+        <v>2.897349806547505</v>
       </c>
     </row>
     <row r="163">
@@ -5734,7 +5734,7 @@
         </is>
       </c>
       <c r="G163">
-        <v>2.926084750400996</v>
+        <v>2.897349806547505</v>
       </c>
     </row>
     <row r="164">
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="G164">
-        <v>4.052469795725062</v>
+        <v>4.010742788668072</v>
       </c>
     </row>
     <row r="165">
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="G165">
-        <v>4.052469795725062</v>
+        <v>4.010742788668072</v>
       </c>
     </row>
     <row r="166">
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="G166">
-        <v>5.243212677320455</v>
+        <v>5.183751644959629</v>
       </c>
     </row>
     <row r="167">
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="G167">
-        <v>5.243212677320455</v>
+        <v>5.183751644959629</v>
       </c>
     </row>
     <row r="168">
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="G168">
-        <v>6.790064045755943</v>
+        <v>6.705656200359806</v>
       </c>
     </row>
     <row r="169">
@@ -5932,7 +5932,7 @@
         </is>
       </c>
       <c r="G169">
-        <v>6.790064045755943</v>
+        <v>6.705656200359806</v>
       </c>
     </row>
     <row r="170">
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="G170">
-        <v>8.915524972373284</v>
+        <v>8.79167683472002</v>
       </c>
     </row>
     <row r="171">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="G171">
-        <v>8.915524972373284</v>
+        <v>8.79167683472002</v>
       </c>
     </row>
     <row r="172">
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="G172">
-        <v>12.09799504384724</v>
+        <v>11.91262870449939</v>
       </c>
     </row>
     <row r="173">
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="G173">
-        <v>12.09799504384724</v>
+        <v>11.91262870449939</v>
       </c>
     </row>
     <row r="174">
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="G174">
-        <v>14.86127465003937</v>
+        <v>14.84131208631903</v>
       </c>
     </row>
     <row r="175">
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="G175">
-        <v>16.33270180355976</v>
+        <v>16.06734336165262</v>
       </c>
     </row>
     <row r="176">
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="G176">
-        <v>14.81805816484183</v>
+        <v>14.81142420576036</v>
       </c>
     </row>
     <row r="177">
@@ -6196,7 +6196,7 @@
         </is>
       </c>
       <c r="G177">
-        <v>21.49261092212679</v>
+        <v>21.13267361015706</v>
       </c>
     </row>
     <row r="178">
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="G178">
-        <v>15.04010966467871</v>
+        <v>14.96212881161092</v>
       </c>
     </row>
     <row r="179">
@@ -6262,7 +6262,7 @@
         </is>
       </c>
       <c r="G179">
-        <v>30.10919615101997</v>
+        <v>28.93630936852399</v>
       </c>
     </row>
     <row r="180">
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="G180">
-        <v>14.45701923922346</v>
+        <v>14.37961576515364</v>
       </c>
     </row>
     <row r="181">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="G181">
-        <v>36.53894061613276</v>
+        <v>35.18167827728028</v>
       </c>
     </row>
     <row r="182">
@@ -6361,7 +6361,7 @@
         </is>
       </c>
       <c r="G182">
-        <v>13.52599068811123</v>
+        <v>13.45405207911199</v>
       </c>
     </row>
     <row r="183">
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="G183">
-        <v>42.03292200073518</v>
+        <v>40.64900586955351</v>
       </c>
     </row>
     <row r="184">
@@ -6427,7 +6427,7 @@
         </is>
       </c>
       <c r="G184">
-        <v>12.52269105031288</v>
+        <v>12.46122316337318</v>
       </c>
     </row>
     <row r="185">
@@ -6460,7 +6460,7 @@
         </is>
       </c>
       <c r="G185">
-        <v>46.53361121450136</v>
+        <v>45.29187724956291</v>
       </c>
     </row>
     <row r="186">
@@ -6493,7 +6493,7 @@
         </is>
       </c>
       <c r="G186">
-        <v>11.51307174949039</v>
+        <v>11.46571670227281</v>
       </c>
     </row>
     <row r="187">
@@ -6526,7 +6526,7 @@
         </is>
       </c>
       <c r="G187">
-        <v>50.4049344863589</v>
+        <v>49.41648172904172</v>
       </c>
     </row>
     <row r="188">
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="G188">
-        <v>10.6020280753843</v>
+        <v>10.56976481824871</v>
       </c>
     </row>
     <row r="189">
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="G189">
-        <v>53.98089991705444</v>
+        <v>53.27162419754141</v>
       </c>
     </row>
     <row r="190">
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="G190">
-        <v>9.816172975628165</v>
+        <v>9.796323963600237</v>
       </c>
     </row>
     <row r="191">
@@ -6658,7 +6658,7 @@
         </is>
       </c>
       <c r="G191">
-        <v>57.44612663042156</v>
+        <v>56.96903335777173</v>
       </c>
     </row>
     <row r="192">
@@ -6691,7 +6691,7 @@
         </is>
       </c>
       <c r="G192">
-        <v>9.148377006581407</v>
+        <v>9.137270498518559</v>
       </c>
     </row>
     <row r="193">
@@ -6724,7 +6724,7 @@
         </is>
       </c>
       <c r="G193">
-        <v>60.84372461925111</v>
+        <v>60.52793412739433</v>
       </c>
     </row>
     <row r="194">
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="G194">
-        <v>8.580817292793522</v>
+        <v>8.575695105622572</v>
       </c>
     </row>
     <row r="195">
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="G195">
-        <v>64.21512331531113</v>
+        <v>64.00269170244015</v>
       </c>
     </row>
     <row r="196">
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="G196">
-        <v>8.088348228519742</v>
+        <v>8.087684525626504</v>
       </c>
     </row>
     <row r="197">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="G197">
-        <v>67.30461102572663</v>
+        <v>67.16013515418608</v>
       </c>
     </row>
     <row r="198">
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="G198">
-        <v>7.659594510592595</v>
+        <v>7.662749366284307</v>
       </c>
     </row>
     <row r="199">
@@ -6922,7 +6922,7 @@
         </is>
       </c>
       <c r="G199">
-        <v>70.09607065226214</v>
+        <v>70.00116177838987</v>
       </c>
     </row>
     <row r="200">
@@ -6955,7 +6955,7 @@
         </is>
       </c>
       <c r="G200">
-        <v>7.285505364680342</v>
+        <v>7.292043425935693</v>
       </c>
     </row>
     <row r="201">
@@ -6988,7 +6988,7 @@
         </is>
       </c>
       <c r="G201">
-        <v>72.43251487102447</v>
+        <v>72.37492943285615</v>
       </c>
     </row>
     <row r="202">
@@ -7021,7 +7021,7 @@
         </is>
       </c>
       <c r="G202">
-        <v>0.2070329006644703</v>
+        <v>0.2069286813205199</v>
       </c>
     </row>
     <row r="203">
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="G203">
-        <v>0.218534728479163</v>
+        <v>0.21842471917166</v>
       </c>
     </row>
     <row r="204">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="G204">
-        <v>0.347102597187797</v>
+        <v>0.3425790821579021</v>
       </c>
     </row>
     <row r="205">
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="G205">
-        <v>0.3663860748093413</v>
+        <v>0.3616112533888968</v>
       </c>
     </row>
     <row r="206">
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="G206">
-        <v>0.5588073157156281</v>
+        <v>0.5534089660500932</v>
       </c>
     </row>
     <row r="207">
@@ -7186,7 +7186,7 @@
         </is>
       </c>
       <c r="G207">
-        <v>0.5898521665887182</v>
+        <v>0.5841539086084315</v>
       </c>
     </row>
     <row r="208">
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="G208">
-        <v>0.8160170555946918</v>
+        <v>0.809057802819419</v>
       </c>
     </row>
     <row r="209">
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="G209">
-        <v>0.8613513364610634</v>
+        <v>0.8540054585316093</v>
       </c>
     </row>
     <row r="210">
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="G210">
-        <v>1.116530986910155</v>
+        <v>1.107675612745854</v>
       </c>
     </row>
     <row r="211">
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="G211">
-        <v>1.178560486182942</v>
+        <v>1.169213146787291</v>
       </c>
     </row>
     <row r="212">
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="G212">
-        <v>1.50699479117342</v>
+        <v>1.495251243966478</v>
       </c>
     </row>
     <row r="213">
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="G213">
-        <v>1.590716724016388</v>
+        <v>1.57832075752017</v>
       </c>
     </row>
     <row r="214">
@@ -7417,7 +7417,7 @@
         </is>
       </c>
       <c r="G214">
-        <v>2.017113213166181</v>
+        <v>2.001466262044216</v>
       </c>
     </row>
     <row r="215">
@@ -7450,7 +7450,7 @@
         </is>
       </c>
       <c r="G215">
-        <v>2.129175058342079</v>
+        <v>2.112658832157783</v>
       </c>
     </row>
     <row r="216">
@@ -7483,7 +7483,7 @@
         </is>
       </c>
       <c r="G216">
-        <v>2.524911379215054</v>
+        <v>2.504407119938433</v>
       </c>
     </row>
     <row r="217">
@@ -7516,7 +7516,7 @@
         </is>
       </c>
       <c r="G217">
-        <v>2.665184233615889</v>
+        <v>2.643540848823903</v>
       </c>
     </row>
     <row r="218">
@@ -7549,7 +7549,7 @@
         </is>
       </c>
       <c r="G218">
-        <v>3.149970411249293</v>
+        <v>3.122898021500133</v>
       </c>
     </row>
     <row r="219">
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="G219">
-        <v>3.324968767429809</v>
+        <v>3.296392356027918</v>
       </c>
     </row>
     <row r="220">
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="G220">
-        <v>3.896989879125533</v>
+        <v>3.860673644026095</v>
       </c>
     </row>
     <row r="221">
@@ -7648,7 +7648,7 @@
         </is>
       </c>
       <c r="G221">
-        <v>4.11348931685473</v>
+        <v>4.075155513138654</v>
       </c>
     </row>
     <row r="222">
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="G222">
-        <v>4.631257200482799</v>
+        <v>4.641162690378395</v>
       </c>
     </row>
     <row r="223">
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="G223">
-        <v>5.362609988555356</v>
+        <v>5.309235442864145</v>
       </c>
     </row>
     <row r="224">
@@ -7747,7 +7747,7 @@
         </is>
       </c>
       <c r="G224">
-        <v>4.344798657721261</v>
+        <v>4.356863217973013</v>
       </c>
     </row>
     <row r="225">
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="G225">
-        <v>6.901376867105117</v>
+        <v>6.829709028757219</v>
       </c>
     </row>
     <row r="226">
@@ -7813,7 +7813,7 @@
         </is>
       </c>
       <c r="G226">
-        <v>4.084858167942436</v>
+        <v>4.10041973562388</v>
       </c>
     </row>
     <row r="227">
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="G227">
-        <v>8.667263420101094</v>
+        <v>8.577080525123861</v>
       </c>
     </row>
     <row r="228">
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="G228">
-        <v>3.843451029716648</v>
+        <v>3.861371023658795</v>
       </c>
     </row>
     <row r="229">
@@ -7912,7 +7912,7 @@
         </is>
       </c>
       <c r="G229">
-        <v>11.31022067780761</v>
+        <v>11.02965399432633</v>
       </c>
     </row>
     <row r="230">
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="G230">
-        <v>3.626033717959928</v>
+        <v>3.643043580525339</v>
       </c>
     </row>
     <row r="231">
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="G231">
-        <v>13.71184277023911</v>
+        <v>13.40285115983329</v>
       </c>
     </row>
     <row r="232">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="G232">
-        <v>3.507291345033729</v>
+        <v>3.522296565424395</v>
       </c>
     </row>
     <row r="233">
@@ -8044,7 +8044,7 @@
         </is>
       </c>
       <c r="G233">
-        <v>16.6582969269057</v>
+        <v>16.34452763806197</v>
       </c>
     </row>
     <row r="234">
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="G234">
-        <v>3.38507964662715</v>
+        <v>3.396814575526379</v>
       </c>
     </row>
     <row r="235">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="G235">
-        <v>19.68299532833085</v>
+        <v>19.40135823382166</v>
       </c>
     </row>
     <row r="236">
@@ -8143,7 +8143,7 @@
         </is>
       </c>
       <c r="G236">
-        <v>3.260458038066845</v>
+        <v>3.268627613977901</v>
       </c>
     </row>
     <row r="237">
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="G237">
-        <v>22.89369323223406</v>
+        <v>22.66893305561638</v>
       </c>
     </row>
     <row r="238">
@@ -8209,7 +8209,7 @@
         </is>
       </c>
       <c r="G238">
-        <v>3.144862116330589</v>
+        <v>3.150133274317452</v>
       </c>
     </row>
     <row r="239">
@@ -8242,7 +8242,7 @@
         </is>
       </c>
       <c r="G239">
-        <v>26.34119232284792</v>
+        <v>26.17877951831674</v>
       </c>
     </row>
     <row r="240">
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="G240">
-        <v>3.043489806316682</v>
+        <v>3.046883262006407</v>
       </c>
     </row>
     <row r="241">
@@ -8308,7 +8308,7 @@
         </is>
       </c>
       <c r="G241">
-        <v>30.04566630221163</v>
+        <v>29.93497207886193</v>
       </c>
     </row>
     <row r="242">
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="G242">
-        <v>2.954677378107507</v>
+        <v>2.95710049660644</v>
       </c>
     </row>
     <row r="243">
@@ -8374,7 +8374,7 @@
         </is>
       </c>
       <c r="G243">
-        <v>33.97422259690812</v>
+        <v>33.89944435737463</v>
       </c>
     </row>
     <row r="244">
@@ -8407,7 +8407,7 @@
         </is>
       </c>
       <c r="G244">
-        <v>2.877935672598963</v>
+        <v>2.88003948764238</v>
       </c>
     </row>
     <row r="245">
@@ -8440,7 +8440,7 @@
         </is>
       </c>
       <c r="G245">
-        <v>38.13973548349984</v>
+        <v>38.0883011545889</v>
       </c>
     </row>
     <row r="246">
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="G246">
-        <v>2.809535827410676</v>
+        <v>2.811739764218966</v>
       </c>
     </row>
     <row r="247">
@@ -8506,7 +8506,7 @@
         </is>
       </c>
       <c r="G247">
-        <v>42.38040365038757</v>
+        <v>42.34477921469922</v>
       </c>
     </row>
     <row r="248">
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="G248">
-        <v>2.753702435910117</v>
+        <v>2.756305203751898</v>
       </c>
     </row>
     <row r="249">
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="G249">
-        <v>46.72393557728947</v>
+        <v>46.70066412444835</v>
       </c>
     </row>
     <row r="250">
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="G250">
-        <v>2.707144909131856</v>
+        <v>2.710322128325315</v>
       </c>
     </row>
     <row r="251">
@@ -8638,7 +8638,7 @@
         </is>
       </c>
       <c r="G251">
-        <v>50.89507215113728</v>
+        <v>50.88158559501923</v>
       </c>
     </row>
     <row r="252">
@@ -8671,7 +8671,7 @@
         </is>
       </c>
       <c r="G252">
-        <v>0.2051766104382828</v>
+        <v>0.2050733531452029</v>
       </c>
     </row>
     <row r="253">
@@ -8704,7 +8704,7 @@
         </is>
       </c>
       <c r="G253">
-        <v>0.2165753110181873</v>
+        <v>0.2164663172088253</v>
       </c>
     </row>
     <row r="254">
@@ -8737,7 +8737,7 @@
         </is>
       </c>
       <c r="G254">
-        <v>0.3400298457395232</v>
+        <v>0.3355995429985211</v>
       </c>
     </row>
     <row r="255">
@@ -8770,7 +8770,7 @@
         </is>
       </c>
       <c r="G255">
-        <v>0.3589203927250522</v>
+        <v>0.3542439620539944</v>
       </c>
     </row>
     <row r="256">
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="G256">
-        <v>0.5429793471496651</v>
+        <v>0.5377383138118966</v>
       </c>
     </row>
     <row r="257">
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="G257">
-        <v>0.5731448664357575</v>
+        <v>0.567612664579224</v>
       </c>
     </row>
     <row r="258">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="G258">
-        <v>0.7871918141050661</v>
+        <v>0.7804880447680634</v>
       </c>
     </row>
     <row r="259">
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="G259">
-        <v>0.8309246926664583</v>
+        <v>0.8238484916996225</v>
       </c>
     </row>
     <row r="260">
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="G260">
-        <v>1.070914910295983</v>
+        <v>1.062439704100246</v>
       </c>
     </row>
     <row r="261">
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="G261">
-        <v>1.130410183090204</v>
+        <v>1.121464132105815</v>
       </c>
     </row>
     <row r="262">
@@ -9001,7 +9001,7 @@
         </is>
       </c>
       <c r="G262">
-        <v>1.440218896910968</v>
+        <v>1.429030652670627</v>
       </c>
     </row>
     <row r="263">
@@ -9034,7 +9034,7 @@
         </is>
       </c>
       <c r="G263">
-        <v>1.520231057850467</v>
+        <v>1.508421244485661</v>
       </c>
     </row>
     <row r="264">
@@ -9067,7 +9067,7 @@
         </is>
       </c>
       <c r="G264">
-        <v>1.919235859429125</v>
+        <v>1.904409605215069</v>
       </c>
     </row>
     <row r="265">
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="G265">
-        <v>2.025860073841854</v>
+        <v>2.010210138838127</v>
       </c>
     </row>
     <row r="266">
@@ -9133,7 +9133,7 @@
         </is>
       </c>
       <c r="G266">
-        <v>2.390323508764849</v>
+        <v>2.371015023775159</v>
       </c>
     </row>
     <row r="267">
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="G267">
-        <v>2.523119259251785</v>
+        <v>2.502738080651556</v>
       </c>
     </row>
     <row r="268">
@@ -9199,7 +9199,7 @@
         </is>
       </c>
       <c r="G268">
-        <v>2.969149286762087</v>
+        <v>2.943804947431055</v>
       </c>
     </row>
     <row r="269">
@@ -9232,7 +9232,7 @@
         </is>
       </c>
       <c r="G269">
-        <v>3.134102024915534</v>
+        <v>3.107349666732782</v>
       </c>
     </row>
     <row r="270">
@@ -9265,7 +9265,7 @@
         </is>
       </c>
       <c r="G270">
-        <v>3.659707576306533</v>
+        <v>3.625897308914192</v>
       </c>
     </row>
     <row r="271">
@@ -9298,7 +9298,7 @@
         </is>
       </c>
       <c r="G271">
-        <v>3.863024663879119</v>
+        <v>3.827336048298315</v>
       </c>
     </row>
     <row r="272">
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="G272">
-        <v>4.321175962412599</v>
+        <v>4.330668125728561</v>
       </c>
     </row>
     <row r="273">
@@ -9364,7 +9364,7 @@
         </is>
       </c>
       <c r="G273">
-        <v>5.025739530242362</v>
+        <v>4.976256390135966</v>
       </c>
     </row>
     <row r="274">
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="G274">
-        <v>4.046608093605778</v>
+        <v>4.058157260552485</v>
       </c>
     </row>
     <row r="275">
@@ -9430,7 +9430,7 @@
         </is>
       </c>
       <c r="G275">
-        <v>6.462038416862832</v>
+        <v>6.395832405336939</v>
       </c>
     </row>
     <row r="276">
@@ -9463,7 +9463,7 @@
         </is>
       </c>
       <c r="G276">
-        <v>3.798828613977776</v>
+        <v>3.813710239829477</v>
       </c>
     </row>
     <row r="277">
@@ -9496,7 +9496,7 @@
         </is>
       </c>
       <c r="G277">
-        <v>8.112246327853965</v>
+        <v>8.029330235377241</v>
       </c>
     </row>
     <row r="278">
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="G278">
-        <v>3.571473270295246</v>
+        <v>3.588790705277947</v>
       </c>
     </row>
     <row r="279">
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="G279">
-        <v>10.58642969886193</v>
+        <v>10.32783765380138</v>
       </c>
     </row>
     <row r="280">
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="G280">
-        <v>3.360766130509587</v>
+        <v>3.377232357220405</v>
       </c>
     </row>
     <row r="281">
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="G281">
-        <v>12.82431057507691</v>
+        <v>12.54082463416677</v>
       </c>
     </row>
     <row r="282">
@@ -9661,7 +9661,7 @@
         </is>
       </c>
       <c r="G282">
-        <v>3.254703370363599</v>
+        <v>3.269307770493031</v>
       </c>
     </row>
     <row r="283">
@@ -9694,7 +9694,7 @@
         </is>
       </c>
       <c r="G283">
-        <v>15.63869346234216</v>
+        <v>15.35110836101519</v>
       </c>
     </row>
     <row r="284">
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="G284">
-        <v>3.145312263384776</v>
+        <v>3.156799881529907</v>
       </c>
     </row>
     <row r="285">
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="G285">
-        <v>18.55967016405558</v>
+        <v>18.30177795082717</v>
       </c>
     </row>
     <row r="286">
@@ -9793,7 +9793,7 @@
         </is>
       </c>
       <c r="G286">
-        <v>3.034163075995247</v>
+        <v>3.042209213505712</v>
       </c>
     </row>
     <row r="287">
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="G287">
-        <v>21.6961802092755</v>
+        <v>21.49048275315962</v>
       </c>
     </row>
     <row r="288">
@@ -9859,7 +9859,7 @@
         </is>
       </c>
       <c r="G288">
-        <v>2.931376934223948</v>
+        <v>2.936592534429213</v>
       </c>
     </row>
     <row r="289">
@@ -9892,7 +9892,7 @@
         </is>
       </c>
       <c r="G289">
-        <v>25.09603114964085</v>
+        <v>24.94738258520708</v>
       </c>
     </row>
     <row r="290">
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="G290">
-        <v>2.841429598532938</v>
+        <v>2.844790252693643</v>
       </c>
     </row>
     <row r="291">
@@ -9958,7 +9958,7 @@
         </is>
       </c>
       <c r="G291">
-        <v>28.77367213115129</v>
+        <v>28.67225624048805</v>
       </c>
     </row>
     <row r="292">
@@ -9991,7 +9991,7 @@
         </is>
       </c>
       <c r="G292">
-        <v>2.762803920521708</v>
+        <v>2.76519214125662</v>
       </c>
     </row>
     <row r="293">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="G293">
-        <v>32.69803812668953</v>
+        <v>32.62938529165908</v>
       </c>
     </row>
     <row r="294">
@@ -10057,7 +10057,7 @@
         </is>
       </c>
       <c r="G294">
-        <v>2.695314446596687</v>
+        <v>2.697368325814935</v>
       </c>
     </row>
     <row r="295">
@@ -10090,7 +10090,7 @@
         </is>
       </c>
       <c r="G295">
-        <v>36.88788939401716</v>
+        <v>36.84055657149795</v>
       </c>
     </row>
     <row r="296">
@@ -10123,7 +10123,7 @@
         </is>
       </c>
       <c r="G296">
-        <v>2.635665979467242</v>
+        <v>2.637797183761587</v>
       </c>
     </row>
     <row r="297">
@@ -10156,7 +10156,7 @@
         </is>
       </c>
       <c r="G297">
-        <v>41.19066509920071</v>
+        <v>41.15783046634186</v>
       </c>
     </row>
     <row r="298">
@@ -10189,7 +10189,7 @@
         </is>
       </c>
       <c r="G298">
-        <v>2.587519538933417</v>
+        <v>2.590020351996786</v>
       </c>
     </row>
     <row r="299">
@@ -10222,7 +10222,7 @@
         </is>
       </c>
       <c r="G299">
-        <v>45.6284185018951</v>
+        <v>45.60704045937369</v>
       </c>
     </row>
     <row r="300">
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="G300">
-        <v>2.54794757069351</v>
+        <v>2.550991103221939</v>
       </c>
     </row>
     <row r="301">
@@ -10288,7 +10288,7 @@
         </is>
       </c>
       <c r="G301">
-        <v>49.92604577095309</v>
+        <v>49.91383236860011</v>
       </c>
     </row>
     <row r="302">
@@ -10321,7 +10321,7 @@
         </is>
       </c>
       <c r="G302">
-        <v>0.2311319063453116</v>
+        <v>0.2310079113750043</v>
       </c>
     </row>
     <row r="303">
@@ -10354,7 +10354,7 @@
         </is>
       </c>
       <c r="G303">
-        <v>0.2439725678089402</v>
+        <v>0.2438416842291712</v>
       </c>
     </row>
     <row r="304">
@@ -10387,7 +10387,7 @@
         </is>
       </c>
       <c r="G304">
-        <v>0.4032982597121164</v>
+        <v>0.398134112927106</v>
       </c>
     </row>
     <row r="305">
@@ -10420,7 +10420,7 @@
         </is>
       </c>
       <c r="G305">
-        <v>0.4257037185850114</v>
+        <v>0.4202526747563901</v>
       </c>
     </row>
     <row r="306">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="G306">
-        <v>0.6711372944499092</v>
+        <v>0.6646500104930481</v>
       </c>
     </row>
     <row r="307">
@@ -10486,7 +10486,7 @@
         </is>
       </c>
       <c r="G307">
-        <v>0.7084226996971269</v>
+        <v>0.7015750110759957</v>
       </c>
     </row>
     <row r="308">
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="G308">
-        <v>1.014360253323422</v>
+        <v>1.005570777015605</v>
       </c>
     </row>
     <row r="309">
@@ -10552,7 +10552,7 @@
         </is>
       </c>
       <c r="G309">
-        <v>1.070713600730278</v>
+        <v>1.061435820183138</v>
       </c>
     </row>
     <row r="310">
@@ -10585,7 +10585,7 @@
         </is>
       </c>
       <c r="G310">
-        <v>1.435705630437437</v>
+        <v>1.423963449316474</v>
       </c>
     </row>
     <row r="311">
@@ -10618,7 +10618,7 @@
         </is>
       </c>
       <c r="G311">
-        <v>1.515467054350628</v>
+        <v>1.503072529834055</v>
       </c>
     </row>
     <row r="312">
@@ -10651,7 +10651,7 @@
         </is>
       </c>
       <c r="G312">
-        <v>1.999177736006412</v>
+        <v>1.982849933118679</v>
       </c>
     </row>
     <row r="313">
@@ -10684,7 +10684,7 @@
         </is>
       </c>
       <c r="G313">
-        <v>2.110243165784546</v>
+        <v>2.093008262736383</v>
       </c>
     </row>
     <row r="314">
@@ -10717,7 +10717,7 @@
         </is>
       </c>
       <c r="G314">
-        <v>2.764438375154908</v>
+        <v>2.741624217610178</v>
       </c>
     </row>
     <row r="315">
@@ -10750,7 +10750,7 @@
         </is>
       </c>
       <c r="G315">
-        <v>2.918018284885735</v>
+        <v>2.893936674144077</v>
       </c>
     </row>
     <row r="316">
@@ -10783,7 +10783,7 @@
         </is>
       </c>
       <c r="G316">
-        <v>3.565963656898954</v>
+        <v>3.534634543072005</v>
       </c>
     </row>
     <row r="317">
@@ -10816,7 +10816,7 @@
         </is>
       </c>
       <c r="G317">
-        <v>3.764072748948895</v>
+        <v>3.731003128798227</v>
       </c>
     </row>
     <row r="318">
@@ -10849,7 +10849,7 @@
         </is>
       </c>
       <c r="G318">
-        <v>4.571622402224026</v>
+        <v>4.528299550220646</v>
       </c>
     </row>
     <row r="319">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="G319">
-        <v>4.825601424569805</v>
+        <v>4.779871747455122</v>
       </c>
     </row>
     <row r="320">
@@ -10915,7 +10915,7 @@
         </is>
       </c>
       <c r="G320">
-        <v>5.812880502563455</v>
+        <v>5.752026025822279</v>
       </c>
     </row>
     <row r="321">
@@ -10948,7 +10948,7 @@
         </is>
       </c>
       <c r="G321">
-        <v>6.135818308261426</v>
+        <v>6.071583027256849</v>
       </c>
     </row>
     <row r="322">
@@ -10981,7 +10981,7 @@
         </is>
       </c>
       <c r="G322">
-        <v>7.974253171620865</v>
+        <v>7.883463328465963</v>
       </c>
     </row>
     <row r="323">
@@ -11014,7 +11014,7 @@
         </is>
       </c>
       <c r="G323">
-        <v>7.974253171620865</v>
+        <v>7.883463328465963</v>
       </c>
     </row>
     <row r="324">
@@ -11047,7 +11047,7 @@
         </is>
       </c>
       <c r="G324">
-        <v>9.357088739768495</v>
+        <v>9.384504038811265</v>
       </c>
     </row>
     <row r="325">
@@ -11080,7 +11080,7 @@
         </is>
       </c>
       <c r="G325">
-        <v>10.23695347176318</v>
+        <v>10.11305172392941</v>
       </c>
     </row>
     <row r="326">
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="G326">
-        <v>8.88123812871369</v>
+        <v>8.916913597368001</v>
       </c>
     </row>
     <row r="327">
@@ -11146,7 +11146,7 @@
         </is>
       </c>
       <c r="G327">
-        <v>12.81177904888525</v>
+        <v>12.65244122953335</v>
       </c>
     </row>
     <row r="328">
@@ -11179,7 +11179,7 @@
         </is>
       </c>
       <c r="G328">
-        <v>8.438290536536035</v>
+        <v>8.480180673294207</v>
       </c>
     </row>
     <row r="329">
@@ -11212,7 +11212,7 @@
         </is>
       </c>
       <c r="G329">
-        <v>16.79029489869398</v>
+        <v>16.29746323769029</v>
       </c>
     </row>
     <row r="330">
@@ -11245,7 +11245,7 @@
         </is>
       </c>
       <c r="G330">
-        <v>8.034607056594735</v>
+        <v>8.075212092535052</v>
       </c>
     </row>
     <row r="331">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="G331">
-        <v>20.15008164129947</v>
+        <v>19.59980905419699</v>
       </c>
     </row>
     <row r="332">
@@ -11311,7 +11311,7 @@
         </is>
       </c>
       <c r="G332">
-        <v>7.763060974994461</v>
+        <v>7.799272849802777</v>
       </c>
     </row>
     <row r="333">
@@ -11344,7 +11344,7 @@
         </is>
       </c>
       <c r="G333">
-        <v>23.87958719263441</v>
+        <v>23.31876015270272</v>
       </c>
     </row>
     <row r="334">
@@ -11377,7 +11377,7 @@
         </is>
       </c>
       <c r="G334">
-        <v>7.47711863582637</v>
+        <v>7.505760652925797</v>
       </c>
     </row>
     <row r="335">
@@ -11410,7 +11410,7 @@
         </is>
       </c>
       <c r="G335">
-        <v>27.4181211573443</v>
+        <v>26.91348296833306</v>
       </c>
     </row>
     <row r="336">
@@ -11443,7 +11443,7 @@
         </is>
       </c>
       <c r="G336">
-        <v>7.179205040530114</v>
+        <v>7.199309133078239</v>
       </c>
     </row>
     <row r="337">
@@ -11476,7 +11476,7 @@
         </is>
       </c>
       <c r="G337">
-        <v>30.90768109131687</v>
+        <v>30.50464234824936</v>
       </c>
     </row>
     <row r="338">
@@ -11509,7 +11509,7 @@
         </is>
       </c>
       <c r="G338">
-        <v>6.904713616766138</v>
+        <v>6.917747805770472</v>
       </c>
     </row>
     <row r="339">
@@ -11542,7 +11542,7 @@
         </is>
       </c>
       <c r="G339">
-        <v>34.44298709068852</v>
+        <v>34.15230558216686</v>
       </c>
     </row>
     <row r="340">
@@ -11575,7 +11575,7 @@
         </is>
       </c>
       <c r="G340">
-        <v>6.665007272812956</v>
+        <v>6.67337769715312</v>
       </c>
     </row>
     <row r="341">
@@ -11608,7 +11608,7 @@
         </is>
       </c>
       <c r="G341">
-        <v>38.07760586241294</v>
+        <v>37.88062963995343</v>
       </c>
     </row>
     <row r="342">
@@ -11641,7 +11641,7 @@
         </is>
       </c>
       <c r="G342">
-        <v>6.457098531414454</v>
+        <v>6.463005932852303</v>
       </c>
     </row>
     <row r="343">
@@ -11674,7 +11674,7 @@
         </is>
       </c>
       <c r="G343">
-        <v>41.78199479805615</v>
+        <v>41.65029475716337</v>
       </c>
     </row>
     <row r="344">
@@ -11707,7 +11707,7 @@
         </is>
       </c>
       <c r="G344">
-        <v>6.278370667721295</v>
+        <v>6.283411153070648</v>
       </c>
     </row>
     <row r="345">
@@ -11740,7 +11740,7 @@
         </is>
       </c>
       <c r="G345">
-        <v>45.56422797057621</v>
+        <v>45.47467228875502</v>
       </c>
     </row>
     <row r="346">
@@ -11773,7 +11773,7 @@
         </is>
       </c>
       <c r="G346">
-        <v>6.11984648949172</v>
+        <v>6.125055445103327</v>
       </c>
     </row>
     <row r="347">
@@ -11806,7 +11806,7 @@
         </is>
       </c>
       <c r="G347">
-        <v>49.23135364253769</v>
+        <v>49.1698661618425</v>
       </c>
     </row>
     <row r="348">
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="G348">
-        <v>5.990041097133946</v>
+        <v>5.996144274264338</v>
       </c>
     </row>
     <row r="349">
@@ -11872,7 +11872,7 @@
         </is>
       </c>
       <c r="G349">
-        <v>52.83704808839518</v>
+        <v>52.79651711289982</v>
       </c>
     </row>
     <row r="350">
@@ -11905,7 +11905,7 @@
         </is>
       </c>
       <c r="G350">
-        <v>5.881876876951535</v>
+        <v>5.889311799306644</v>
       </c>
     </row>
     <row r="351">
@@ -11938,7 +11938,7 @@
         </is>
       </c>
       <c r="G351">
-        <v>56.20961683476609</v>
+        <v>56.18508727713364</v>
       </c>
     </row>
     <row r="352">
@@ -11971,7 +11971,7 @@
         </is>
       </c>
       <c r="G352">
-        <v>0.2290691830594174</v>
+        <v>0.228946325959784</v>
       </c>
     </row>
     <row r="353">
@@ -12004,7 +12004,7 @@
         </is>
       </c>
       <c r="G353">
-        <v>0.2417952487849409</v>
+        <v>0.241665566290883</v>
       </c>
     </row>
     <row r="354">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="G354">
-        <v>0.3951345569475326</v>
+        <v>0.3900761099420192</v>
       </c>
     </row>
     <row r="355">
@@ -12070,7 +12070,7 @@
         </is>
       </c>
       <c r="G355">
-        <v>0.4170864767779512</v>
+        <v>0.4117470049387982</v>
       </c>
     </row>
     <row r="356">
@@ -12103,7 +12103,7 @@
         </is>
       </c>
       <c r="G356">
-        <v>0.6522627361914134</v>
+        <v>0.6459628899315433</v>
       </c>
     </row>
     <row r="357">
@@ -12136,7 +12136,7 @@
         </is>
       </c>
       <c r="G357">
-        <v>0.6884995548687142</v>
+        <v>0.6818497171499625</v>
       </c>
     </row>
     <row r="358">
@@ -12169,7 +12169,7 @@
         </is>
       </c>
       <c r="G358">
-        <v>0.9788061594970617</v>
+        <v>0.9703360861218499</v>
       </c>
     </row>
     <row r="359">
@@ -12202,7 +12202,7 @@
         </is>
       </c>
       <c r="G359">
-        <v>1.03318427946912</v>
+        <v>1.024243646461953</v>
       </c>
     </row>
     <row r="360">
@@ -12235,7 +12235,7 @@
         </is>
       </c>
       <c r="G360">
-        <v>1.377539500156794</v>
+        <v>1.366295319664785</v>
       </c>
     </row>
     <row r="361">
@@ -12268,7 +12268,7 @@
         </is>
       </c>
       <c r="G361">
-        <v>1.454069472387726</v>
+        <v>1.442200615201717</v>
       </c>
     </row>
     <row r="362">
@@ -12301,7 +12301,7 @@
         </is>
       </c>
       <c r="G362">
-        <v>1.911436517237798</v>
+        <v>1.895869199283584</v>
       </c>
     </row>
     <row r="363">
@@ -12334,7 +12334,7 @@
         </is>
       </c>
       <c r="G363">
-        <v>2.01762743486212</v>
+        <v>2.00119526591045</v>
       </c>
     </row>
     <row r="364">
@@ -12367,7 +12367,7 @@
         </is>
       </c>
       <c r="G364">
-        <v>2.631665804022867</v>
+        <v>2.610027478153394</v>
       </c>
     </row>
     <row r="365">
@@ -12400,7 +12400,7 @@
         </is>
       </c>
       <c r="G365">
-        <v>2.777869459801915</v>
+        <v>2.755029004717471</v>
       </c>
     </row>
     <row r="366">
@@ -12433,7 +12433,7 @@
         </is>
       </c>
       <c r="G366">
-        <v>3.377972336034343</v>
+        <v>3.34843431989015</v>
       </c>
     </row>
     <row r="367">
@@ -12466,7 +12466,7 @@
         </is>
       </c>
       <c r="G367">
-        <v>3.565637465814027</v>
+        <v>3.534458448772936</v>
       </c>
     </row>
     <row r="368">
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="G368">
-        <v>4.312331644487244</v>
+        <v>4.271713251341921</v>
       </c>
     </row>
     <row r="369">
@@ -12532,7 +12532,7 @@
         </is>
       </c>
       <c r="G369">
-        <v>4.551905624736538</v>
+        <v>4.509030654194248</v>
       </c>
     </row>
     <row r="370">
@@ -12565,7 +12565,7 @@
         </is>
       </c>
       <c r="G370">
-        <v>5.463449503092524</v>
+        <v>5.406690540568286</v>
       </c>
     </row>
     <row r="371">
@@ -12598,7 +12598,7 @@
         </is>
       </c>
       <c r="G371">
-        <v>5.766974475486553</v>
+        <v>5.707062237266524</v>
       </c>
     </row>
     <row r="372">
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="G372">
-        <v>7.479165765913693</v>
+        <v>7.394822500799806</v>
       </c>
     </row>
     <row r="373">
@@ -12664,7 +12664,7 @@
         </is>
       </c>
       <c r="G373">
-        <v>7.479165765913693</v>
+        <v>7.394822500799806</v>
       </c>
     </row>
     <row r="374">
@@ -12697,7 +12697,7 @@
         </is>
       </c>
       <c r="G374">
-        <v>8.727561081484286</v>
+        <v>8.753842046092501</v>
       </c>
     </row>
     <row r="375">
@@ -12730,7 +12730,7 @@
         </is>
       </c>
       <c r="G375">
-        <v>9.591876501018232</v>
+        <v>9.477153381062832</v>
       </c>
     </row>
     <row r="376">
@@ -12763,7 +12763,7 @@
         </is>
       </c>
       <c r="G376">
-        <v>8.27154645467707</v>
+        <v>8.305725049023717</v>
       </c>
     </row>
     <row r="377">
@@ -12796,7 +12796,7 @@
         </is>
       </c>
       <c r="G377">
-        <v>11.99819553235591</v>
+        <v>11.85128864781585</v>
       </c>
     </row>
     <row r="378">
@@ -12829,7 +12829,7 @@
         </is>
       </c>
       <c r="G378">
-        <v>7.852619450675141</v>
+        <v>7.893142750712648</v>
       </c>
     </row>
     <row r="379">
@@ -12862,7 +12862,7 @@
         </is>
       </c>
       <c r="G379">
-        <v>15.72223294200864</v>
+        <v>15.26687853049139</v>
       </c>
     </row>
     <row r="380">
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="G380">
-        <v>7.458423034353692</v>
+        <v>7.497790926311261</v>
       </c>
     </row>
     <row r="381">
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="G381">
-        <v>18.85347949531345</v>
+        <v>18.34718958123155</v>
       </c>
     </row>
     <row r="382">
@@ -12961,7 +12961,7 @@
         </is>
       </c>
       <c r="G382">
-        <v>7.214952936867284</v>
+        <v>7.250285044342632</v>
       </c>
     </row>
     <row r="383">
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="G383">
-        <v>22.42520419159578</v>
+        <v>21.90960024542511</v>
       </c>
     </row>
     <row r="384">
@@ -13027,7 +13027,7 @@
         </is>
       </c>
       <c r="G384">
-        <v>6.957914809971204</v>
+        <v>6.986063009005503</v>
       </c>
     </row>
     <row r="385">
@@ -13060,7 +13060,7 @@
         </is>
       </c>
       <c r="G385">
-        <v>25.86094863278206</v>
+        <v>25.39737594528172</v>
       </c>
     </row>
     <row r="386">
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="G386">
-        <v>6.690939985014658</v>
+        <v>6.71085803603258</v>
       </c>
     </row>
     <row r="387">
@@ -13126,7 +13126,7 @@
         </is>
       </c>
       <c r="G387">
-        <v>29.30087935513832</v>
+        <v>28.93083209914568</v>
       </c>
     </row>
     <row r="388">
@@ -13159,7 +13159,7 @@
         </is>
       </c>
       <c r="G388">
-        <v>6.44571236396366</v>
+        <v>6.458717207091162</v>
       </c>
     </row>
     <row r="389">
@@ -13192,7 +13192,7 @@
         </is>
       </c>
       <c r="G389">
-        <v>32.82838868238896</v>
+        <v>32.56153836068042</v>
       </c>
     </row>
     <row r="390">
@@ -13225,7 +13225,7 @@
         </is>
       </c>
       <c r="G390">
-        <v>6.23190259000358</v>
+        <v>6.24028181970286</v>
       </c>
     </row>
     <row r="391">
@@ -13258,7 +13258,7 @@
         </is>
       </c>
       <c r="G391">
-        <v>36.48232478726942</v>
+        <v>36.30142464822711</v>
       </c>
     </row>
     <row r="392">
@@ -13291,7 +13291,7 @@
         </is>
       </c>
       <c r="G392">
-        <v>6.046740591716242</v>
+        <v>6.05263507683388</v>
       </c>
     </row>
     <row r="393">
@@ -13324,7 +13324,7 @@
         </is>
       </c>
       <c r="G393">
-        <v>40.23015647928738</v>
+        <v>40.10909342215223</v>
       </c>
     </row>
     <row r="394">
@@ -13357,7 +13357,7 @@
         </is>
       </c>
       <c r="G394">
-        <v>5.888403940621869</v>
+        <v>5.893383303245954</v>
       </c>
     </row>
     <row r="395">
@@ -13390,7 +13390,7 @@
         </is>
       </c>
       <c r="G395">
-        <v>44.0839422645608</v>
+        <v>44.00155284487839</v>
       </c>
     </row>
     <row r="396">
@@ -13423,7 +13423,7 @@
         </is>
       </c>
       <c r="G396">
-        <v>5.748995906917682</v>
+        <v>5.754080925941472</v>
       </c>
     </row>
     <row r="397">
@@ -13456,7 +13456,7 @@
         </is>
       </c>
       <c r="G397">
-        <v>47.85924782464569</v>
+        <v>47.80269458175896</v>
       </c>
     </row>
     <row r="398">
@@ -13489,7 +13489,7 @@
         </is>
       </c>
       <c r="G398">
-        <v>5.635876795647937</v>
+        <v>5.641780699007891</v>
       </c>
     </row>
     <row r="399">
@@ -13522,7 +13522,7 @@
         </is>
       </c>
       <c r="G399">
-        <v>51.60039914932519</v>
+        <v>51.56328641649525</v>
       </c>
     </row>
     <row r="400">
@@ -13555,7 +13555,7 @@
         </is>
       </c>
       <c r="G400">
-        <v>5.542956761272766</v>
+        <v>5.55011213695389</v>
       </c>
     </row>
     <row r="401">
@@ -13588,7 +13588,7 @@
         </is>
       </c>
       <c r="G401">
-        <v>55.1358052621439</v>
+        <v>55.1136307331177</v>
       </c>
     </row>
     <row r="402">
@@ -13654,7 +13654,7 @@
         </is>
       </c>
       <c r="G403">
-        <v>0.2293977400635359</v>
+        <v>0.2294124205295214</v>
       </c>
     </row>
     <row r="404">
@@ -13720,7 +13720,7 @@
         </is>
       </c>
       <c r="G405">
-        <v>0.3629384697366069</v>
+        <v>0.3582050844624462</v>
       </c>
     </row>
     <row r="406">
@@ -13786,7 +13786,7 @@
         </is>
       </c>
       <c r="G407">
-        <v>0.5635469579022971</v>
+        <v>0.5579213665053604</v>
       </c>
     </row>
     <row r="408">
@@ -13852,7 +13852,7 @@
         </is>
       </c>
       <c r="G409">
-        <v>0.8085235305311611</v>
+        <v>0.8012973494517479</v>
       </c>
     </row>
     <row r="410">
@@ -13918,7 +13918,7 @@
         </is>
       </c>
       <c r="G411">
-        <v>1.094117151810209</v>
+        <v>1.084938915725058</v>
       </c>
     </row>
     <row r="412">
@@ -13984,7 +13984,7 @@
         </is>
       </c>
       <c r="G413">
-        <v>1.469693626927704</v>
+        <v>1.457499038151902</v>
       </c>
     </row>
     <row r="414">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="G415">
-        <v>1.964838711928504</v>
+        <v>1.948590729102619</v>
       </c>
     </row>
     <row r="416">
@@ -14116,7 +14116,7 @@
         </is>
       </c>
       <c r="G417">
-        <v>2.452861944234395</v>
+        <v>2.431585840493496</v>
       </c>
     </row>
     <row r="418">
@@ -14182,7 +14182,7 @@
         </is>
       </c>
       <c r="G419">
-        <v>3.054542822202687</v>
+        <v>3.026431100595146</v>
       </c>
     </row>
     <row r="420">
@@ -14248,7 +14248,7 @@
         </is>
       </c>
       <c r="G421">
-        <v>3.783589912058523</v>
+        <v>3.745876227298511</v>
       </c>
     </row>
     <row r="422">
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="G422">
-        <v>4.27769676980954</v>
+        <v>4.283987695780719</v>
       </c>
     </row>
     <row r="423">
@@ -14314,7 +14314,7 @@
         </is>
       </c>
       <c r="G423">
-        <v>4.953406341322516</v>
+        <v>4.900820006355162</v>
       </c>
     </row>
     <row r="424">
@@ -14347,7 +14347,7 @@
         </is>
       </c>
       <c r="G424">
-        <v>4.034006902765065</v>
+        <v>4.042538284115173</v>
       </c>
     </row>
     <row r="425">
@@ -14380,7 +14380,7 @@
         </is>
       </c>
       <c r="G425">
-        <v>6.408396665810893</v>
+        <v>6.337645842070129</v>
       </c>
     </row>
     <row r="426">
@@ -14413,7 +14413,7 @@
         </is>
       </c>
       <c r="G426">
-        <v>3.810082176372553</v>
+        <v>3.822152239612086</v>
       </c>
     </row>
     <row r="427">
@@ -14446,7 +14446,7 @@
         </is>
       </c>
       <c r="G427">
-        <v>8.085519148552345</v>
+        <v>7.996256675253396</v>
       </c>
     </row>
     <row r="428">
@@ -14479,7 +14479,7 @@
         </is>
       </c>
       <c r="G428">
-        <v>3.605876105623287</v>
+        <v>3.617637282924947</v>
       </c>
     </row>
     <row r="429">
@@ -14512,7 +14512,7 @@
         </is>
       </c>
       <c r="G429">
-        <v>10.61325205921854</v>
+        <v>10.33550653042941</v>
       </c>
     </row>
     <row r="430">
@@ -14545,7 +14545,7 @@
         </is>
       </c>
       <c r="G430">
-        <v>3.401997239699184</v>
+        <v>3.413527762473103</v>
       </c>
     </row>
     <row r="431">
@@ -14578,7 +14578,7 @@
         </is>
       </c>
       <c r="G431">
-        <v>12.8676260884507</v>
+        <v>12.56132701038079</v>
       </c>
     </row>
     <row r="432">
@@ -14611,7 +14611,7 @@
         </is>
       </c>
       <c r="G432">
-        <v>3.287336097398184</v>
+        <v>3.297781777136617</v>
       </c>
     </row>
     <row r="433">
@@ -14644,7 +14644,7 @@
         </is>
       </c>
       <c r="G433">
-        <v>15.61756746945465</v>
+        <v>15.30657295490385</v>
       </c>
     </row>
     <row r="434">
@@ -14677,7 +14677,7 @@
         </is>
       </c>
       <c r="G434">
-        <v>3.170795220639549</v>
+        <v>3.179155363947498</v>
       </c>
     </row>
     <row r="435">
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="G435">
-        <v>18.44199119259581</v>
+        <v>18.16304710462448</v>
       </c>
     </row>
     <row r="436">
@@ -14743,7 +14743,7 @@
         </is>
       </c>
       <c r="G436">
-        <v>3.055312334855808</v>
+        <v>3.061276863946061</v>
       </c>
     </row>
     <row r="437">
@@ -14776,7 +14776,7 @@
         </is>
       </c>
       <c r="G437">
-        <v>21.45934179718597</v>
+        <v>21.23691149469611</v>
       </c>
     </row>
     <row r="438">
@@ -14809,7 +14809,7 @@
         </is>
       </c>
       <c r="G438">
-        <v>2.951143987092588</v>
+        <v>2.955113795363758</v>
       </c>
     </row>
     <row r="439">
@@ -14842,7 +14842,7 @@
         </is>
       </c>
       <c r="G439">
-        <v>24.72595693732694</v>
+        <v>24.56536979006918</v>
       </c>
     </row>
     <row r="440">
@@ -14875,7 +14875,7 @@
         </is>
       </c>
       <c r="G440">
-        <v>2.861434986450563</v>
+        <v>2.864091381366241</v>
       </c>
     </row>
     <row r="441">
@@ -14908,7 +14908,7 @@
         </is>
       </c>
       <c r="G441">
-        <v>28.25708600305677</v>
+        <v>28.14772257910466</v>
       </c>
     </row>
     <row r="442">
@@ -14941,7 +14941,7 @@
         </is>
       </c>
       <c r="G442">
-        <v>2.783718586200133</v>
+        <v>2.785708680482502</v>
       </c>
     </row>
     <row r="443">
@@ -14974,7 +14974,7 @@
         </is>
       </c>
       <c r="G443">
-        <v>32.01858957974637</v>
+        <v>31.94475090867721</v>
       </c>
     </row>
     <row r="444">
@@ -15007,7 +15007,7 @@
         </is>
       </c>
       <c r="G444">
-        <v>2.717444243103058</v>
+        <v>2.71926510504928</v>
       </c>
     </row>
     <row r="445">
@@ -15040,7 +15040,7 @@
         </is>
       </c>
       <c r="G445">
-        <v>36.02443470063002</v>
+        <v>35.973656403875</v>
       </c>
     </row>
     <row r="446">
@@ -15073,7 +15073,7 @@
         </is>
       </c>
       <c r="G446">
-        <v>2.658878002409413</v>
+        <v>2.660868117153683</v>
       </c>
     </row>
     <row r="447">
@@ -15106,7 +15106,7 @@
         </is>
       </c>
       <c r="G447">
-        <v>40.12099316414725</v>
+        <v>40.08582199880939</v>
       </c>
     </row>
     <row r="448">
@@ -15139,7 +15139,7 @@
         </is>
       </c>
       <c r="G448">
-        <v>2.611353924530524</v>
+        <v>2.613770166758211</v>
       </c>
     </row>
     <row r="449">
@@ -15172,7 +15172,7 @@
         </is>
       </c>
       <c r="G449">
-        <v>44.32342539375607</v>
+        <v>44.30046272398703</v>
       </c>
     </row>
     <row r="450">
@@ -15205,7 +15205,7 @@
         </is>
       </c>
       <c r="G450">
-        <v>2.571784971883957</v>
+        <v>2.574780266099585</v>
       </c>
     </row>
     <row r="451">
@@ -15238,7 +15238,7 @@
         </is>
       </c>
       <c r="G451">
-        <v>48.36664708774553</v>
+        <v>48.35339012401388</v>
       </c>
     </row>
     <row r="452">
@@ -15304,7 +15304,7 @@
         </is>
       </c>
       <c r="G453">
-        <v>0.2290507634693349</v>
+        <v>0.2290654262542818</v>
       </c>
     </row>
     <row r="454">
@@ -15370,7 +15370,7 @@
         </is>
       </c>
       <c r="G455">
-        <v>0.3616892338412062</v>
+        <v>0.3569723144266885</v>
       </c>
     </row>
     <row r="456">
@@ -15436,7 +15436,7 @@
         </is>
       </c>
       <c r="G457">
-        <v>0.5608529486112087</v>
+        <v>0.5552550064513214</v>
       </c>
     </row>
     <row r="458">
@@ -15502,7 +15502,7 @@
         </is>
       </c>
       <c r="G459">
-        <v>0.8037012636294555</v>
+        <v>0.7965198606662495</v>
       </c>
     </row>
     <row r="460">
@@ -15568,7 +15568,7 @@
         </is>
       </c>
       <c r="G461">
-        <v>1.086614591219456</v>
+        <v>1.077502511778497</v>
       </c>
     </row>
     <row r="462">
@@ -15634,7 +15634,7 @@
         </is>
       </c>
       <c r="G463">
-        <v>1.45878183070325</v>
+        <v>1.446683923858741</v>
       </c>
     </row>
     <row r="464">
@@ -15700,7 +15700,7 @@
         </is>
       </c>
       <c r="G465">
-        <v>1.948842318599866</v>
+        <v>1.932737388673887</v>
       </c>
     </row>
     <row r="466">
@@ -15766,7 +15766,7 @@
         </is>
       </c>
       <c r="G467">
-        <v>2.430925512153777</v>
+        <v>2.409857684283583</v>
       </c>
     </row>
     <row r="468">
@@ -15832,7 +15832,7 @@
         </is>
       </c>
       <c r="G469">
-        <v>3.025114626165646</v>
+        <v>2.997304161613485</v>
       </c>
     </row>
     <row r="470">
@@ -15898,7 +15898,7 @@
         </is>
       </c>
       <c r="G471">
-        <v>3.744894184715774</v>
+        <v>3.707617610519624</v>
       </c>
     </row>
     <row r="472">
@@ -15931,7 +15931,7 @@
         </is>
       </c>
       <c r="G472">
-        <v>4.213834901444895</v>
+        <v>4.219895873600175</v>
       </c>
     </row>
     <row r="473">
@@ -15964,7 +15964,7 @@
         </is>
       </c>
       <c r="G473">
-        <v>4.901089253166218</v>
+        <v>4.84914712188673</v>
       </c>
     </row>
     <row r="474">
@@ -15997,7 +15997,7 @@
         </is>
       </c>
       <c r="G474">
-        <v>3.969614049806684</v>
+        <v>3.977850114604294</v>
       </c>
     </row>
     <row r="475">
@@ -16030,7 +16030,7 @@
         </is>
       </c>
       <c r="G475">
-        <v>6.339771643947858</v>
+        <v>6.269926632115438</v>
       </c>
     </row>
     <row r="476">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="G476">
-        <v>3.744952001811094</v>
+        <v>3.756637383230629</v>
       </c>
     </row>
     <row r="477">
@@ -16096,7 +16096,7 @@
         </is>
       </c>
       <c r="G477">
-        <v>7.998460057752125</v>
+        <v>7.910403357090777</v>
       </c>
     </row>
     <row r="478">
@@ -16129,7 +16129,7 @@
         </is>
       </c>
       <c r="G478">
-        <v>3.541326087943717</v>
+        <v>3.552387567508794</v>
       </c>
     </row>
     <row r="479">
@@ -16162,7 +16162,7 @@
         </is>
       </c>
       <c r="G479">
-        <v>10.49919376271853</v>
+        <v>10.22510990008254</v>
       </c>
     </row>
     <row r="480">
@@ -16195,7 +16195,7 @@
         </is>
       </c>
       <c r="G480">
-        <v>3.334591965041383</v>
+        <v>3.345370415583486</v>
       </c>
     </row>
     <row r="481">
@@ -16228,7 +16228,7 @@
         </is>
       </c>
       <c r="G481">
-        <v>12.72737192715956</v>
+        <v>12.42534459458371</v>
       </c>
     </row>
     <row r="482">
@@ -16261,7 +16261,7 @@
         </is>
       </c>
       <c r="G482">
-        <v>3.216102844032203</v>
+        <v>3.225779028948215</v>
       </c>
     </row>
     <row r="483">
@@ -16294,7 +16294,7 @@
         </is>
       </c>
       <c r="G483">
-        <v>15.45713940506895</v>
+        <v>15.15052784031771</v>
       </c>
     </row>
     <row r="484">
@@ -16327,7 +16327,7 @@
         </is>
       </c>
       <c r="G484">
-        <v>3.094741313020232</v>
+        <v>3.102400138130204</v>
       </c>
     </row>
     <row r="485">
@@ -16360,7 +16360,7 @@
         </is>
       </c>
       <c r="G485">
-        <v>18.26617169351931</v>
+        <v>17.99119811994613</v>
       </c>
     </row>
     <row r="486">
@@ -16393,7 +16393,7 @@
         </is>
       </c>
       <c r="G486">
-        <v>2.974117273050036</v>
+        <v>2.979521731766112</v>
       </c>
     </row>
     <row r="487">
@@ -16426,7 +16426,7 @@
         </is>
       </c>
       <c r="G487">
-        <v>21.27282113846628</v>
+        <v>21.05357555843891</v>
       </c>
     </row>
     <row r="488">
@@ -16459,7 +16459,7 @@
         </is>
       </c>
       <c r="G488">
-        <v>2.864733572764467</v>
+        <v>2.86830514370841</v>
       </c>
     </row>
     <row r="489">
@@ -16492,7 +16492,7 @@
         </is>
       </c>
       <c r="G489">
-        <v>24.53269685084488</v>
+        <v>24.37440728811358</v>
       </c>
     </row>
     <row r="490">
@@ -16525,7 +16525,7 @@
         </is>
       </c>
       <c r="G490">
-        <v>2.770120009200117</v>
+        <v>2.77251306457563</v>
       </c>
     </row>
     <row r="491">
@@ -16558,7 +16558,7 @@
         </is>
       </c>
       <c r="G491">
-        <v>28.06008243681031</v>
+        <v>27.95226676245363</v>
       </c>
     </row>
     <row r="492">
@@ -16591,7 +16591,7 @@
         </is>
       </c>
       <c r="G492">
-        <v>2.68787313005175</v>
+        <v>2.689688387745078</v>
       </c>
     </row>
     <row r="493">
@@ -16624,7 +16624,7 @@
         </is>
       </c>
       <c r="G493">
-        <v>31.82115577130649</v>
+        <v>31.7483385192116</v>
       </c>
     </row>
     <row r="494">
@@ -16657,7 +16657,7 @@
         </is>
       </c>
       <c r="G494">
-        <v>2.617241500024247</v>
+        <v>2.618934858660508</v>
       </c>
     </row>
     <row r="495">
@@ -16690,7 +16690,7 @@
         </is>
       </c>
       <c r="G495">
-        <v>35.83075347458372</v>
+        <v>35.78065895203035</v>
       </c>
     </row>
     <row r="496">
@@ -16723,7 +16723,7 @@
         </is>
       </c>
       <c r="G496">
-        <v>2.554601463145614</v>
+        <v>2.55648348321795</v>
       </c>
     </row>
     <row r="497">
@@ -16756,7 +16756,7 @@
         </is>
       </c>
       <c r="G497">
-        <v>39.93667150969818</v>
+        <v>39.90196516359021</v>
       </c>
     </row>
     <row r="498">
@@ -16789,7 +16789,7 @@
         </is>
       </c>
       <c r="G498">
-        <v>2.503048563667148</v>
+        <v>2.505356711258602</v>
       </c>
     </row>
     <row r="499">
@@ -16822,7 +16822,7 @@
         </is>
       </c>
       <c r="G499">
-        <v>44.15332871494492</v>
+        <v>44.13068044367755</v>
       </c>
     </row>
     <row r="500">
@@ -16855,7 +16855,7 @@
         </is>
       </c>
       <c r="G500">
-        <v>2.459841741658983</v>
+        <v>2.462716402187743</v>
       </c>
     </row>
     <row r="501">
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="G501">
-        <v>48.21563584698065</v>
+        <v>48.20258836323561</v>
       </c>
     </row>
     <row r="502">
@@ -16954,7 +16954,7 @@
         </is>
       </c>
       <c r="G503">
-        <v>0.2563151345559512</v>
+        <v>0.2563314790355224</v>
       </c>
     </row>
     <row r="504">
@@ -17020,7 +17020,7 @@
         </is>
       </c>
       <c r="G505">
-        <v>0.4229305536688239</v>
+        <v>0.4175175823956642</v>
       </c>
     </row>
     <row r="506">
@@ -17086,7 +17086,7 @@
         </is>
       </c>
       <c r="G507">
-        <v>0.6799675184760376</v>
+        <v>0.6731937514433675</v>
       </c>
     </row>
     <row r="508">
@@ -17152,7 +17152,7 @@
         </is>
       </c>
       <c r="G509">
-        <v>1.011485995336824</v>
+        <v>1.002338870561357</v>
       </c>
     </row>
     <row r="510">
@@ -17218,7 +17218,7 @@
         </is>
       </c>
       <c r="G511">
-        <v>1.417320146765808</v>
+        <v>1.405119900364816</v>
       </c>
     </row>
     <row r="512">
@@ -17284,7 +17284,7 @@
         </is>
       </c>
       <c r="G513">
-        <v>1.966840375424364</v>
+        <v>1.949839065005804</v>
       </c>
     </row>
     <row r="514">
@@ -17350,7 +17350,7 @@
         </is>
       </c>
       <c r="G515">
-        <v>2.720131383473094</v>
+        <v>2.69637398612322</v>
       </c>
     </row>
     <row r="516">
@@ -17416,7 +17416,7 @@
         </is>
       </c>
       <c r="G517">
-        <v>3.503688267633892</v>
+        <v>3.471086148511527</v>
       </c>
     </row>
     <row r="518">
@@ -17482,7 +17482,7 @@
         </is>
       </c>
       <c r="G519">
-        <v>4.489075206445429</v>
+        <v>4.443962104902273</v>
       </c>
     </row>
     <row r="520">
@@ -17548,7 +17548,7 @@
         </is>
       </c>
       <c r="G521">
-        <v>5.721753318024005</v>
+        <v>5.658387304251537</v>
       </c>
     </row>
     <row r="522">
@@ -17581,7 +17581,7 @@
         </is>
       </c>
       <c r="G522">
-        <v>7.47443862566248</v>
+        <v>7.384790947159601</v>
       </c>
     </row>
     <row r="523">
@@ -17614,7 +17614,7 @@
         </is>
       </c>
       <c r="G523">
-        <v>7.47443862566248</v>
+        <v>7.384790947159601</v>
       </c>
     </row>
     <row r="524">
@@ -17647,7 +17647,7 @@
         </is>
       </c>
       <c r="G524">
-        <v>8.823225516481816</v>
+        <v>8.843825883893734</v>
       </c>
     </row>
     <row r="525">
@@ -17680,7 +17680,7 @@
         </is>
       </c>
       <c r="G525">
-        <v>9.65304210217422</v>
+        <v>9.530524624822052</v>
       </c>
     </row>
     <row r="526">
@@ -17713,7 +17713,7 @@
         </is>
       </c>
       <c r="G526">
-        <v>8.417084780951539</v>
+        <v>8.446148382131399</v>
       </c>
     </row>
     <row r="527">
@@ -17746,7 +17746,7 @@
         </is>
       </c>
       <c r="G527">
-        <v>12.14291665088932</v>
+        <v>11.98513272313019</v>
       </c>
     </row>
     <row r="528">
@@ -17779,7 +17779,7 @@
         </is>
       </c>
       <c r="G528">
-        <v>8.039954930593064</v>
+        <v>8.069697035869535</v>
       </c>
     </row>
     <row r="529">
@@ -17812,7 +17812,7 @@
         </is>
       </c>
       <c r="G529">
-        <v>15.9992687184652</v>
+        <v>15.51004769309174</v>
       </c>
     </row>
     <row r="530">
@@ -17845,7 +17845,7 @@
         </is>
       </c>
       <c r="G530">
-        <v>7.649241383730479</v>
+        <v>7.678435624839866</v>
       </c>
     </row>
     <row r="531">
@@ -17878,7 +17878,7 @@
         </is>
       </c>
       <c r="G531">
-        <v>19.18597493127409</v>
+        <v>18.63900033095704</v>
       </c>
     </row>
     <row r="532">
@@ -17911,7 +17911,7 @@
         </is>
       </c>
       <c r="G532">
-        <v>7.374561461566484</v>
+        <v>7.400779936264453</v>
       </c>
     </row>
     <row r="533">
@@ -17944,7 +17944,7 @@
         </is>
       </c>
       <c r="G533">
-        <v>22.68777466362393</v>
+        <v>22.13041907329317</v>
       </c>
     </row>
     <row r="534">
@@ -17977,7 +17977,7 @@
         </is>
       </c>
       <c r="G534">
-        <v>7.088190273490412</v>
+        <v>7.109028644136203</v>
       </c>
     </row>
     <row r="535">
@@ -18010,7 +18010,7 @@
         </is>
       </c>
       <c r="G535">
-        <v>25.99601788042769</v>
+        <v>25.49486458009981</v>
       </c>
     </row>
     <row r="536">
@@ -18043,7 +18043,7 @@
         </is>
       </c>
       <c r="G536">
-        <v>6.79811761601975</v>
+        <v>6.812857339060849</v>
       </c>
     </row>
     <row r="537">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="G537">
-        <v>29.27201472441386</v>
+        <v>28.87205872732918</v>
       </c>
     </row>
     <row r="538">
@@ -18109,7 +18109,7 @@
         </is>
       </c>
       <c r="G538">
-        <v>6.537477442179668</v>
+        <v>6.54720037763609</v>
       </c>
     </row>
     <row r="539">
@@ -18142,7 +18142,7 @@
         </is>
       </c>
       <c r="G539">
-        <v>32.61702613945218</v>
+        <v>32.32880269154972</v>
       </c>
     </row>
     <row r="540">
@@ -18175,7 +18175,7 @@
         </is>
       </c>
       <c r="G540">
-        <v>6.313586906148721</v>
+        <v>6.320016741158947</v>
       </c>
     </row>
     <row r="541">
@@ -18208,7 +18208,7 @@
         </is>
       </c>
       <c r="G541">
-        <v>36.07686114262465</v>
+        <v>35.88170620305203</v>
       </c>
     </row>
     <row r="542">
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="G542">
-        <v>6.121474031582775</v>
+        <v>6.126221522222252</v>
       </c>
     </row>
     <row r="543">
@@ -18274,7 +18274,7 @@
         </is>
       </c>
       <c r="G543">
-        <v>39.61824919350334</v>
+        <v>39.48786075982002</v>
       </c>
     </row>
     <row r="544">
@@ -18307,7 +18307,7 @@
         </is>
       </c>
       <c r="G544">
-        <v>5.958154775663837</v>
+        <v>5.962441471067898</v>
       </c>
     </row>
     <row r="545">
@@ -18340,7 +18340,7 @@
         </is>
       </c>
       <c r="G545">
-        <v>43.24931808210231</v>
+        <v>43.16070811349565</v>
       </c>
     </row>
     <row r="546">
@@ -18373,7 +18373,7 @@
         </is>
       </c>
       <c r="G546">
-        <v>5.814567910099806</v>
+        <v>5.819223111956092</v>
       </c>
     </row>
     <row r="547">
@@ -18406,7 +18406,7 @@
         </is>
       </c>
       <c r="G547">
-        <v>46.78558189411481</v>
+        <v>46.72478130820934</v>
       </c>
     </row>
     <row r="548">
@@ -18439,7 +18439,7 @@
         </is>
       </c>
       <c r="G548">
-        <v>5.697188690900354</v>
+        <v>5.702828192140123</v>
       </c>
     </row>
     <row r="549">
@@ -18472,7 +18472,7 @@
         </is>
       </c>
       <c r="G549">
-        <v>50.26494850599199</v>
+        <v>50.22492648220857</v>
       </c>
     </row>
     <row r="550">
@@ -18505,7 +18505,7 @@
         </is>
       </c>
       <c r="G550">
-        <v>5.599899184252443</v>
+        <v>5.60689833992995</v>
       </c>
     </row>
     <row r="551">
@@ -18538,7 +18538,7 @@
         </is>
       </c>
       <c r="G551">
-        <v>53.52699496096538</v>
+        <v>53.50286895430742</v>
       </c>
     </row>
     <row r="552">
@@ -18604,7 +18604,7 @@
         </is>
       </c>
       <c r="G553">
-        <v>0.2559290255902416</v>
+        <v>0.2559453505864326</v>
       </c>
     </row>
     <row r="554">
@@ -18670,7 +18670,7 @@
         </is>
       </c>
       <c r="G555">
-        <v>0.4214832629439507</v>
+        <v>0.4160890099766871</v>
       </c>
     </row>
     <row r="556">
@@ -18736,7 +18736,7 @@
         </is>
       </c>
       <c r="G557">
-        <v>0.6767365887397302</v>
+        <v>0.6699958629286715</v>
       </c>
     </row>
     <row r="558">
@@ -18802,7 +18802,7 @@
         </is>
       </c>
       <c r="G559">
-        <v>1.005491515232725</v>
+        <v>0.9964005634842907</v>
       </c>
     </row>
     <row r="560">
@@ -18868,7 +18868,7 @@
         </is>
       </c>
       <c r="G561">
-        <v>1.407665320253318</v>
+        <v>1.395552068320111</v>
       </c>
     </row>
     <row r="562">
@@ -18934,7 +18934,7 @@
         </is>
       </c>
       <c r="G563">
-        <v>1.95234407600146</v>
+        <v>1.935475748904876</v>
       </c>
     </row>
     <row r="564">
@@ -19000,7 +19000,7 @@
         </is>
       </c>
       <c r="G565">
-        <v>2.698154991715476</v>
+        <v>2.674603502989296</v>
       </c>
     </row>
     <row r="566">
@@ -19066,7 +19066,7 @@
         </is>
       </c>
       <c r="G567">
-        <v>3.472607266504217</v>
+        <v>3.440318648155257</v>
       </c>
     </row>
     <row r="568">
@@ -19132,7 +19132,7 @@
         </is>
       </c>
       <c r="G569">
-        <v>4.446200638206037</v>
+        <v>4.401561420957814</v>
       </c>
     </row>
     <row r="570">
@@ -19198,7 +19198,7 @@
         </is>
       </c>
       <c r="G571">
-        <v>5.663763669685858</v>
+        <v>5.601115772348806</v>
       </c>
     </row>
     <row r="572">
@@ -19231,7 +19231,7 @@
         </is>
       </c>
       <c r="G572">
-        <v>7.396100026775613</v>
+        <v>7.307524869064314</v>
       </c>
     </row>
     <row r="573">
@@ -19264,7 +19264,7 @@
         </is>
       </c>
       <c r="G573">
-        <v>7.396100026775613</v>
+        <v>7.307524869064314</v>
       </c>
     </row>
     <row r="574">
@@ -19297,7 +19297,7 @@
         </is>
       </c>
       <c r="G574">
-        <v>8.689561488092179</v>
+        <v>8.709503823062645</v>
       </c>
     </row>
     <row r="575">
@@ -19330,7 +19330,7 @@
         </is>
       </c>
       <c r="G575">
-        <v>9.550270971668803</v>
+        <v>9.429282839102356</v>
       </c>
     </row>
     <row r="576">
@@ -19363,7 +19363,7 @@
         </is>
       </c>
       <c r="G576">
-        <v>8.281015372909215</v>
+        <v>8.309205147653385</v>
       </c>
     </row>
     <row r="577">
@@ -19396,7 +19396,7 @@
         </is>
       </c>
       <c r="G577">
-        <v>12.01263923813906</v>
+        <v>11.85692639002939</v>
       </c>
     </row>
     <row r="578">
@@ -19429,7 +19429,7 @@
         </is>
       </c>
       <c r="G578">
-        <v>7.90442056205679</v>
+        <v>7.932555747171229</v>
       </c>
     </row>
     <row r="579">
@@ -19462,7 +19462,7 @@
         </is>
       </c>
       <c r="G579">
-        <v>15.82750641208518</v>
+        <v>15.344564167967</v>
       </c>
     </row>
     <row r="580">
@@ -19495,7 +19495,7 @@
         </is>
       </c>
       <c r="G580">
-        <v>7.506355345701489</v>
+        <v>7.533757186033932</v>
       </c>
     </row>
     <row r="581">
@@ -19528,7 +19528,7 @@
         </is>
       </c>
       <c r="G581">
-        <v>18.97697544045399</v>
+        <v>18.43740773528621</v>
       </c>
     </row>
     <row r="582">
@@ -19561,7 +19561,7 @@
         </is>
       </c>
       <c r="G582">
-        <v>7.223340743849765</v>
+        <v>7.247658409033657</v>
       </c>
     </row>
     <row r="583">
@@ -19594,7 +19594,7 @@
         </is>
       </c>
       <c r="G583">
-        <v>22.45447101667784</v>
+        <v>21.90472712958546</v>
       </c>
     </row>
     <row r="584">
@@ -19627,7 +19627,7 @@
         </is>
       </c>
       <c r="G584">
-        <v>6.926367817311409</v>
+        <v>6.945405922544308</v>
       </c>
     </row>
     <row r="585">
@@ -19660,7 +19660,7 @@
         </is>
       </c>
       <c r="G585">
-        <v>25.7477184210972</v>
+        <v>25.2534698722057</v>
       </c>
     </row>
     <row r="586">
@@ -19693,7 +19693,7 @@
         </is>
       </c>
       <c r="G586">
-        <v>6.625056520550425</v>
+        <v>6.63830468503028</v>
       </c>
     </row>
     <row r="587">
@@ -19726,7 +19726,7 @@
         </is>
       </c>
       <c r="G587">
-        <v>29.0172760070658</v>
+        <v>28.62286227885293</v>
       </c>
     </row>
     <row r="588">
@@ -19759,7 +19759,7 @@
         </is>
       </c>
       <c r="G588">
-        <v>6.353034658197022</v>
+        <v>6.361660456989497</v>
       </c>
     </row>
     <row r="589">
@@ -19792,7 +19792,7 @@
         </is>
       </c>
       <c r="G589">
-        <v>32.36222410540564</v>
+        <v>32.07800058732183</v>
       </c>
     </row>
     <row r="590">
@@ -19825,7 +19825,7 @@
         </is>
       </c>
       <c r="G590">
-        <v>6.118610962631994</v>
+        <v>6.124294709917702</v>
       </c>
     </row>
     <row r="591">
@@ -19858,7 +19858,7 @@
         </is>
       </c>
       <c r="G591">
-        <v>35.82593503527032</v>
+        <v>35.63347618065891</v>
       </c>
     </row>
     <row r="592">
@@ -19891,7 +19891,7 @@
         </is>
       </c>
       <c r="G592">
-        <v>5.91698406689494</v>
+        <v>5.921227356685957</v>
       </c>
     </row>
     <row r="593">
@@ -19924,7 +19924,7 @@
         </is>
       </c>
       <c r="G593">
-        <v>39.37470886756036</v>
+        <v>39.24610300577145</v>
       </c>
     </row>
     <row r="594">
@@ -19957,7 +19957,7 @@
         </is>
       </c>
       <c r="G594">
-        <v>5.744743130398372</v>
+        <v>5.748662891409075</v>
       </c>
     </row>
     <row r="595">
@@ -19990,7 +19990,7 @@
         </is>
       </c>
       <c r="G595">
-        <v>43.01725768135651</v>
+        <v>42.92984760485431</v>
       </c>
     </row>
     <row r="596">
@@ -20023,7 +20023,7 @@
         </is>
       </c>
       <c r="G596">
-        <v>5.592995119573779</v>
+        <v>5.597347933772927</v>
       </c>
     </row>
     <row r="597">
@@ -20056,7 +20056,7 @@
         </is>
       </c>
       <c r="G597">
-        <v>46.57043550034856</v>
+        <v>46.51045990798026</v>
       </c>
     </row>
     <row r="598">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="G598">
-        <v>5.46763051160211</v>
+        <v>5.472982752060171</v>
       </c>
     </row>
     <row r="599">
@@ -20122,7 +20122,7 @@
         </is>
       </c>
       <c r="G599">
-        <v>50.07086240958692</v>
+        <v>50.03140973295568</v>
       </c>
     </row>
     <row r="600">
@@ -20155,7 +20155,7 @@
         </is>
       </c>
       <c r="G600">
-        <v>5.363045427249405</v>
+        <v>5.369740271459341</v>
       </c>
     </row>
     <row r="601">
@@ -20188,7 +20188,7 @@
         </is>
       </c>
       <c r="G601">
-        <v>53.35804730709032</v>
+        <v>53.33431054895526</v>
       </c>
     </row>
     <row r="602">
@@ -20254,7 +20254,7 @@
         </is>
       </c>
       <c r="G603">
-        <v>0.2260900351440297</v>
+        <v>0.2259681713481369</v>
       </c>
     </row>
     <row r="604">
@@ -20320,7 +20320,7 @@
         </is>
       </c>
       <c r="G605">
-        <v>0.3410370641811117</v>
+        <v>0.336720505612722</v>
       </c>
     </row>
     <row r="606">
@@ -20386,7 +20386,7 @@
         </is>
       </c>
       <c r="G607">
-        <v>0.5179917672196767</v>
+        <v>0.5128644391520745</v>
       </c>
     </row>
     <row r="608">
@@ -20452,7 +20452,7 @@
         </is>
       </c>
       <c r="G609">
-        <v>0.7340672896557504</v>
+        <v>0.7274623176632317</v>
       </c>
     </row>
     <row r="610">
@@ -20518,7 +20518,7 @@
         </is>
       </c>
       <c r="G611">
-        <v>0.9856087322663011</v>
+        <v>0.9772002159713702</v>
       </c>
     </row>
     <row r="612">
@@ -20584,7 +20584,7 @@
         </is>
       </c>
       <c r="G613">
-        <v>1.317019991886423</v>
+        <v>1.305808723901205</v>
       </c>
     </row>
     <row r="614">
@@ -20650,7 +20650,7 @@
         </is>
       </c>
       <c r="G615">
-        <v>1.755128193720865</v>
+        <v>1.740170192850678</v>
       </c>
     </row>
     <row r="616">
@@ -20716,7 +20716,7 @@
         </is>
       </c>
       <c r="G617">
-        <v>2.184028599319539</v>
+        <v>2.164423875246723</v>
       </c>
     </row>
     <row r="618">
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G619">
-        <v>2.713805692134728</v>
+        <v>2.687900223308385</v>
       </c>
     </row>
     <row r="620">
@@ -20848,7 +20848,7 @@
         </is>
       </c>
       <c r="G621">
-        <v>3.362622694972138</v>
+        <v>3.327803859241403</v>
       </c>
     </row>
     <row r="622">
@@ -20881,7 +20881,7 @@
         </is>
       </c>
       <c r="G622">
-        <v>3.810334367303282</v>
+        <v>3.814259656313478</v>
       </c>
     </row>
     <row r="623">
@@ -20914,7 +20914,7 @@
         </is>
       </c>
       <c r="G623">
-        <v>4.411992579816701</v>
+        <v>4.363251390211235</v>
       </c>
     </row>
     <row r="624">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="G624">
-        <v>3.605676086817407</v>
+        <v>3.61165414436982</v>
       </c>
     </row>
     <row r="625">
@@ -20980,7 +20980,7 @@
         </is>
       </c>
       <c r="G625">
-        <v>5.727132983568081</v>
+        <v>5.661339435769717</v>
       </c>
     </row>
     <row r="626">
@@ -21013,7 +21013,7 @@
         </is>
       </c>
       <c r="G626">
-        <v>3.417758478719084</v>
+        <v>3.42699600075485</v>
       </c>
     </row>
     <row r="627">
@@ -21046,7 +21046,7 @@
         </is>
       </c>
       <c r="G627">
-        <v>7.251433106532577</v>
+        <v>7.168073283617823</v>
       </c>
     </row>
     <row r="628">
@@ -21079,7 +21079,7 @@
         </is>
       </c>
       <c r="G628">
-        <v>3.252942044435037</v>
+        <v>3.260254553666738</v>
       </c>
     </row>
     <row r="629">
@@ -21112,7 +21112,7 @@
         </is>
       </c>
       <c r="G629">
-        <v>9.571890761033339</v>
+        <v>9.31201676120665</v>
       </c>
     </row>
     <row r="630">
@@ -21145,7 +21145,7 @@
         </is>
       </c>
       <c r="G630">
-        <v>3.068481754754713</v>
+        <v>3.075978544574702</v>
       </c>
     </row>
     <row r="631">
@@ -21178,7 +21178,7 @@
         </is>
       </c>
       <c r="G631">
-        <v>11.60258881176214</v>
+        <v>11.31575603412948</v>
       </c>
     </row>
     <row r="632">
@@ -21211,7 +21211,7 @@
         </is>
       </c>
       <c r="G632">
-        <v>2.962682378031695</v>
+        <v>2.969710135037086</v>
       </c>
     </row>
     <row r="633">
@@ -21244,7 +21244,7 @@
         </is>
       </c>
       <c r="G633">
-        <v>14.0704433550439</v>
+        <v>13.77921399201776</v>
       </c>
     </row>
     <row r="634">
@@ -21277,7 +21277,7 @@
         </is>
       </c>
       <c r="G634">
-        <v>2.855303403132261</v>
+        <v>2.861073757698782</v>
       </c>
     </row>
     <row r="635">
@@ -21310,7 +21310,7 @@
         </is>
       </c>
       <c r="G635">
-        <v>16.60107694835431</v>
+        <v>16.33996099889498</v>
       </c>
     </row>
     <row r="636">
@@ -21343,7 +21343,7 @@
         </is>
       </c>
       <c r="G636">
-        <v>2.74925438326023</v>
+        <v>2.753458190382847</v>
       </c>
     </row>
     <row r="637">
@@ -21376,7 +21376,7 @@
         </is>
       </c>
       <c r="G637">
-        <v>19.3024300780739</v>
+        <v>19.09430696226077</v>
       </c>
     </row>
     <row r="638">
@@ -21409,7 +21409,7 @@
         </is>
       </c>
       <c r="G638">
-        <v>2.654171849369486</v>
+        <v>2.657042555431846</v>
       </c>
     </row>
     <row r="639">
@@ -21442,7 +21442,7 @@
         </is>
       </c>
       <c r="G639">
-        <v>22.2290700284058</v>
+        <v>22.07889746906046</v>
       </c>
     </row>
     <row r="640">
@@ -21475,7 +21475,7 @@
         </is>
       </c>
       <c r="G640">
-        <v>2.57249026211125</v>
+        <v>2.574478462455135</v>
       </c>
     </row>
     <row r="641">
@@ -21508,7 +21508,7 @@
         </is>
       </c>
       <c r="G641">
-        <v>25.39341648322008</v>
+        <v>25.29121500955892</v>
       </c>
     </row>
     <row r="642">
@@ -21541,7 +21541,7 @@
         </is>
       </c>
       <c r="G642">
-        <v>2.501991652835595</v>
+        <v>2.50355214139504</v>
       </c>
     </row>
     <row r="643">
@@ -21574,7 +21574,7 @@
         </is>
       </c>
       <c r="G643">
-        <v>28.76616639909226</v>
+        <v>28.6972178780517</v>
       </c>
     </row>
     <row r="644">
@@ -21607,7 +21607,7 @@
         </is>
       </c>
       <c r="G644">
-        <v>2.442160840296356</v>
+        <v>2.443663399700045</v>
       </c>
     </row>
     <row r="645">
@@ -21640,7 +21640,7 @@
         </is>
       </c>
       <c r="G645">
-        <v>32.36136264243058</v>
+        <v>32.31398209287262</v>
       </c>
     </row>
     <row r="646">
@@ -21673,7 +21673,7 @@
         </is>
       </c>
       <c r="G646">
-        <v>2.389503547943892</v>
+        <v>2.391211871255858</v>
       </c>
     </row>
     <row r="647">
@@ -21706,7 +21706,7 @@
         </is>
       </c>
       <c r="G647">
-        <v>36.04074271740142</v>
+        <v>36.00794558122187</v>
       </c>
     </row>
     <row r="648">
@@ -21739,7 +21739,7 @@
         </is>
       </c>
       <c r="G648">
-        <v>2.346570891067563</v>
+        <v>2.348695892386286</v>
       </c>
     </row>
     <row r="649">
@@ -21772,7 +21772,7 @@
         </is>
       </c>
       <c r="G649">
-        <v>39.81185777920352</v>
+        <v>39.79045431665772</v>
       </c>
     </row>
     <row r="650">
@@ -21805,7 +21805,7 @@
         </is>
       </c>
       <c r="G650">
-        <v>2.310497888238721</v>
+        <v>2.313165283199609</v>
       </c>
     </row>
     <row r="651">
@@ -21838,7 +21838,7 @@
         </is>
       </c>
       <c r="G651">
-        <v>43.43360110167529</v>
+        <v>43.421260580286</v>
       </c>
     </row>
     <row r="652">
@@ -21904,7 +21904,7 @@
         </is>
       </c>
       <c r="G653">
-        <v>0.2268653315204573</v>
+        <v>0.2267430407781289</v>
       </c>
     </row>
     <row r="654">
@@ -21970,7 +21970,7 @@
         </is>
       </c>
       <c r="G655">
-        <v>0.3436610736117204</v>
+        <v>0.3393109480466385</v>
       </c>
     </row>
     <row r="656">
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G657">
-        <v>0.5234506403483817</v>
+        <v>0.5182677551880205</v>
       </c>
     </row>
     <row r="658">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="G659">
-        <v>0.7432472907534747</v>
+        <v>0.7365563297429277</v>
       </c>
     </row>
     <row r="660">
@@ -22168,7 +22168,7 @@
         </is>
       </c>
       <c r="G661">
-        <v>0.9995135601013391</v>
+        <v>0.9909799213323229</v>
       </c>
     </row>
     <row r="662">
@@ -22234,7 +22234,7 @@
         </is>
       </c>
       <c r="G663">
-        <v>1.336909318601438</v>
+        <v>1.325516478778955</v>
       </c>
     </row>
     <row r="664">
@@ -22300,7 +22300,7 @@
         </is>
       </c>
       <c r="G665">
-        <v>1.784033154625956</v>
+        <v>1.768807554500941</v>
       </c>
     </row>
     <row r="666">
@@ -22366,7 +22366,7 @@
         </is>
       </c>
       <c r="G667">
-        <v>2.223252883010858</v>
+        <v>2.203260817815875</v>
       </c>
     </row>
     <row r="668">
@@ -22432,7 +22432,7 @@
         </is>
       </c>
       <c r="G669">
-        <v>2.765845730918408</v>
+        <v>2.739384290578498</v>
       </c>
     </row>
     <row r="670">
@@ -22498,7 +22498,7 @@
         </is>
       </c>
       <c r="G671">
-        <v>3.43033627858537</v>
+        <v>3.394716978617363</v>
       </c>
     </row>
     <row r="672">
@@ -22531,7 +22531,7 @@
         </is>
       </c>
       <c r="G672">
-        <v>3.871353403662022</v>
+        <v>3.874997178862004</v>
       </c>
     </row>
     <row r="673">
@@ -22564,7 +22564,7 @@
         </is>
       </c>
       <c r="G673">
-        <v>4.502511802523642</v>
+        <v>4.452599936071224</v>
       </c>
     </row>
     <row r="674">
@@ -22597,7 +22597,7 @@
         </is>
       </c>
       <c r="G674">
-        <v>3.659832033796696</v>
+        <v>3.665486966339351</v>
       </c>
     </row>
     <row r="675">
@@ -22630,7 +22630,7 @@
         </is>
       </c>
       <c r="G675">
-        <v>5.844175048384299</v>
+        <v>5.776753691413618</v>
       </c>
     </row>
     <row r="676">
@@ -22663,7 +22663,7 @@
         </is>
       </c>
       <c r="G676">
-        <v>3.464073919483894</v>
+        <v>3.472944498331684</v>
       </c>
     </row>
     <row r="677">
@@ -22696,7 +22696,7 @@
         </is>
       </c>
       <c r="G677">
-        <v>7.396985303411305</v>
+        <v>7.311489298374553</v>
       </c>
     </row>
     <row r="678">
@@ -22729,7 +22729,7 @@
         </is>
       </c>
       <c r="G678">
-        <v>3.292240443922951</v>
+        <v>3.298514732853032</v>
       </c>
     </row>
     <row r="679">
@@ -22762,7 +22762,7 @@
         </is>
       </c>
       <c r="G679">
-        <v>9.758061895652661</v>
+        <v>9.491826306978002</v>
       </c>
     </row>
     <row r="680">
@@ -22795,7 +22795,7 @@
         </is>
       </c>
       <c r="G680">
-        <v>3.100615364686571</v>
+        <v>3.106983824640432</v>
       </c>
     </row>
     <row r="681">
@@ -22828,7 +22828,7 @@
         </is>
       </c>
       <c r="G681">
-        <v>11.83064739338767</v>
+        <v>11.53636685470004</v>
       </c>
     </row>
     <row r="682">
@@ -22861,7 +22861,7 @@
         </is>
       </c>
       <c r="G682">
-        <v>2.982164412076369</v>
+        <v>2.988007395210571</v>
       </c>
     </row>
     <row r="683">
@@ -22894,7 +22894,7 @@
         </is>
       </c>
       <c r="G683">
-        <v>14.32785213030515</v>
+        <v>14.0289766712819</v>
       </c>
     </row>
     <row r="684">
@@ -22927,7 +22927,7 @@
         </is>
       </c>
       <c r="G684">
-        <v>2.860636901779545</v>
+        <v>2.865303827162806</v>
       </c>
     </row>
     <row r="685">
@@ -22960,7 +22960,7 @@
         </is>
       </c>
       <c r="G685">
-        <v>16.87820508618625</v>
+        <v>16.61016144120545</v>
       </c>
     </row>
     <row r="686">
@@ -22993,7 +22993,7 @@
         </is>
       </c>
       <c r="G686">
-        <v>2.740029927875128</v>
+        <v>2.743340848079608</v>
       </c>
     </row>
     <row r="687">
@@ -23026,7 +23026,7 @@
         </is>
       </c>
       <c r="G687">
-        <v>19.5908570283846</v>
+        <v>19.37717852619144</v>
       </c>
     </row>
     <row r="688">
@@ -23059,7 +23059,7 @@
         </is>
       </c>
       <c r="G688">
-        <v>2.631003483730046</v>
+        <v>2.633239264116023</v>
       </c>
     </row>
     <row r="689">
@@ -23092,7 +23092,7 @@
         </is>
       </c>
       <c r="G689">
-        <v>22.52193508282152</v>
+        <v>22.36775768546766</v>
       </c>
     </row>
     <row r="690">
@@ -23125,7 +23125,7 @@
         </is>
       </c>
       <c r="G690">
-        <v>2.536818146352411</v>
+        <v>2.538393585870577</v>
       </c>
     </row>
     <row r="691">
@@ -23158,7 +23158,7 @@
         </is>
       </c>
       <c r="G691">
-        <v>25.68597866413768</v>
+        <v>25.58108281680311</v>
       </c>
     </row>
     <row r="692">
@@ -23191,7 +23191,7 @@
         </is>
       </c>
       <c r="G692">
-        <v>2.455148526934187</v>
+        <v>2.456446841216807</v>
       </c>
     </row>
     <row r="693">
@@ -23224,7 +23224,7 @@
         </is>
       </c>
       <c r="G693">
-        <v>29.0533095986813</v>
+        <v>28.98258567495446</v>
       </c>
     </row>
     <row r="694">
@@ -23257,7 +23257,7 @@
         </is>
       </c>
       <c r="G694">
-        <v>2.384993897769054</v>
+        <v>2.386321480272106</v>
       </c>
     </row>
     <row r="695">
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G695">
-        <v>32.63666281021192</v>
+        <v>32.58809454229865</v>
       </c>
     </row>
     <row r="696">
@@ -23323,7 +23323,7 @@
         </is>
       </c>
       <c r="G696">
-        <v>2.322773662674472</v>
+        <v>2.324352367568829</v>
       </c>
     </row>
     <row r="697">
@@ -23356,7 +23356,7 @@
         </is>
       </c>
       <c r="G697">
-        <v>36.29590653662852</v>
+        <v>36.26230071493482</v>
       </c>
     </row>
     <row r="698">
@@ -23389,7 +23389,7 @@
         </is>
       </c>
       <c r="G698">
-        <v>2.270917869715544</v>
+        <v>2.272931258959634</v>
       </c>
     </row>
     <row r="699">
@@ -23422,7 +23422,7 @@
         </is>
       </c>
       <c r="G699">
-        <v>40.04009325395493</v>
+        <v>40.01813927988974</v>
       </c>
     </row>
     <row r="700">
@@ -23455,7 +23455,7 @@
         </is>
       </c>
       <c r="G700">
-        <v>2.226893806323707</v>
+        <v>2.2294495550165</v>
       </c>
     </row>
     <row r="701">
@@ -23488,7 +23488,7 @@
         </is>
       </c>
       <c r="G701">
-        <v>43.62912646414691</v>
+        <v>43.61641432418094</v>
       </c>
     </row>
     <row r="702">
@@ -23554,7 +23554,7 @@
         </is>
       </c>
       <c r="G703">
-        <v>0.2526691426274195</v>
+        <v>0.2525240356720218</v>
       </c>
     </row>
     <row r="704">
@@ -23620,7 +23620,7 @@
         </is>
       </c>
       <c r="G705">
-        <v>0.3981219880903308</v>
+        <v>0.3931813028235255</v>
       </c>
     </row>
     <row r="706">
@@ -23686,7 +23686,7 @@
         </is>
       </c>
       <c r="G707">
-        <v>0.6273593618402071</v>
+        <v>0.6211790865288419</v>
       </c>
     </row>
     <row r="708">
@@ -23752,7 +23752,7 @@
         </is>
       </c>
       <c r="G709">
-        <v>0.9225343551158641</v>
+        <v>0.9141640352906693</v>
       </c>
     </row>
     <row r="710">
@@ -23818,7 +23818,7 @@
         </is>
       </c>
       <c r="G711">
-        <v>1.284329417693167</v>
+        <v>1.27313805949074</v>
       </c>
     </row>
     <row r="712">
@@ -23884,7 +23884,7 @@
         </is>
       </c>
       <c r="G713">
-        <v>1.774454550176239</v>
+        <v>1.758802718971346</v>
       </c>
     </row>
     <row r="714">
@@ -23950,7 +23950,7 @@
         </is>
       </c>
       <c r="G715">
-        <v>2.447959765905166</v>
+        <v>2.426057355718959</v>
       </c>
     </row>
     <row r="716">
@@ -24016,7 +24016,7 @@
         </is>
       </c>
       <c r="G717">
-        <v>3.145402741670251</v>
+        <v>3.115318764086279</v>
       </c>
     </row>
     <row r="718">
@@ -24082,7 +24082,7 @@
         </is>
       </c>
       <c r="G719">
-        <v>4.024345408327055</v>
+        <v>3.982716925702114</v>
       </c>
     </row>
     <row r="720">
@@ -24148,7 +24148,7 @@
         </is>
       </c>
       <c r="G721">
-        <v>5.134886830780942</v>
+        <v>5.076314689561767</v>
       </c>
     </row>
     <row r="722">
@@ -24181,7 +24181,7 @@
         </is>
       </c>
       <c r="G722">
-        <v>6.725622290778226</v>
+        <v>6.642457661641007</v>
       </c>
     </row>
     <row r="723">
@@ -24214,7 +24214,7 @@
         </is>
       </c>
       <c r="G723">
-        <v>6.725622290778226</v>
+        <v>6.642457661641007</v>
       </c>
     </row>
     <row r="724">
@@ -24247,7 +24247,7 @@
         </is>
       </c>
       <c r="G724">
-        <v>7.968539929015289</v>
+        <v>7.984023617667005</v>
       </c>
     </row>
     <row r="725">
@@ -24280,7 +24280,7 @@
         </is>
       </c>
       <c r="G725">
-        <v>8.717794728754752</v>
+        <v>8.603812840150514</v>
       </c>
     </row>
     <row r="726">
@@ -24313,7 +24313,7 @@
         </is>
       </c>
       <c r="G726">
-        <v>7.630020884916096</v>
+        <v>7.653339262743593</v>
       </c>
     </row>
     <row r="727">
@@ -24346,7 +24346,7 @@
         </is>
       </c>
       <c r="G727">
-        <v>11.00662054939704</v>
+        <v>10.85933791405787</v>
       </c>
     </row>
     <row r="728">
@@ -24379,7 +24379,7 @@
         </is>
       </c>
       <c r="G728">
-        <v>7.326119749450712</v>
+        <v>7.346682054829332</v>
       </c>
     </row>
     <row r="729">
@@ -24412,7 +24412,7 @@
         </is>
       </c>
       <c r="G729">
-        <v>14.57690166928373</v>
+        <v>14.11867298539354</v>
       </c>
     </row>
     <row r="730">
@@ -24445,7 +24445,7 @@
         </is>
       </c>
       <c r="G730">
-        <v>6.96569811566061</v>
+        <v>6.986193692442077</v>
       </c>
     </row>
     <row r="731">
@@ -24478,7 +24478,7 @@
         </is>
       </c>
       <c r="G731">
-        <v>17.46870775248103</v>
+        <v>16.9559739590334</v>
       </c>
     </row>
     <row r="732">
@@ -24511,7 +24511,7 @@
         </is>
       </c>
       <c r="G732">
-        <v>6.705579501557669</v>
+        <v>6.724140322741504</v>
       </c>
     </row>
     <row r="733">
@@ -24544,7 +24544,7 @@
         </is>
       </c>
       <c r="G733">
-        <v>20.62582273491366</v>
+        <v>20.10339553188618</v>
       </c>
     </row>
     <row r="734">
@@ -24577,7 +24577,7 @@
         </is>
       </c>
       <c r="G734">
-        <v>6.434384140962135</v>
+        <v>6.449179182142292</v>
       </c>
     </row>
     <row r="735">
@@ -24610,7 +24610,7 @@
         </is>
       </c>
       <c r="G735">
-        <v>23.59334253001381</v>
+        <v>23.12377835134393</v>
       </c>
     </row>
     <row r="736">
@@ -24643,7 +24643,7 @@
         </is>
       </c>
       <c r="G736">
-        <v>6.160619792494486</v>
+        <v>6.171082894695941</v>
       </c>
     </row>
     <row r="737">
@@ -24676,7 +24676,7 @@
         </is>
       </c>
       <c r="G737">
-        <v>26.52110413247404</v>
+        <v>26.14650661163749</v>
       </c>
     </row>
     <row r="738">
@@ -24709,7 +24709,7 @@
         </is>
       </c>
       <c r="G738">
-        <v>5.91556080794158</v>
+        <v>5.92251533292656</v>
       </c>
     </row>
     <row r="739">
@@ -24742,7 +24742,7 @@
         </is>
       </c>
       <c r="G739">
-        <v>29.50710233218281</v>
+        <v>29.23728354677799</v>
       </c>
     </row>
     <row r="740">
@@ -24775,7 +24775,7 @@
         </is>
       </c>
       <c r="G740">
-        <v>5.705273881849362</v>
+        <v>5.709974488375721</v>
       </c>
     </row>
     <row r="741">
@@ -24808,7 +24808,7 @@
         </is>
       </c>
       <c r="G741">
-        <v>32.59264657003996</v>
+        <v>32.41005619530235</v>
       </c>
     </row>
     <row r="742">
@@ -24841,7 +24841,7 @@
         </is>
       </c>
       <c r="G742">
-        <v>5.525291717626358</v>
+        <v>5.528914909519282</v>
       </c>
     </row>
     <row r="743">
@@ -24874,7 +24874,7 @@
         </is>
       </c>
       <c r="G743">
-        <v>35.75032143756184</v>
+        <v>35.62840798611153</v>
       </c>
     </row>
     <row r="744">
@@ -24907,7 +24907,7 @@
         </is>
       </c>
       <c r="G744">
-        <v>5.372804502422491</v>
+        <v>5.376266220545642</v>
       </c>
     </row>
     <row r="745">
@@ -24940,7 +24940,7 @@
         </is>
       </c>
       <c r="G745">
-        <v>38.98970902014886</v>
+        <v>38.90691185314384</v>
       </c>
     </row>
     <row r="746">
@@ -24973,7 +24973,7 @@
         </is>
       </c>
       <c r="G746">
-        <v>5.239324753548795</v>
+        <v>5.24326816936124</v>
       </c>
     </row>
     <row r="747">
@@ -25006,7 +25006,7 @@
         </is>
       </c>
       <c r="G747">
-        <v>42.14515352742455</v>
+        <v>42.08837425718259</v>
       </c>
     </row>
     <row r="748">
@@ -25039,7 +25039,7 @@
         </is>
       </c>
       <c r="G748">
-        <v>5.129614478910797</v>
+        <v>5.134539965606113</v>
       </c>
     </row>
     <row r="749">
@@ -25072,7 +25072,7 @@
         </is>
       </c>
       <c r="G749">
-        <v>45.24437376156904</v>
+        <v>45.20701765132792</v>
       </c>
     </row>
     <row r="750">
@@ -25105,7 +25105,7 @@
         </is>
       </c>
       <c r="G750">
-        <v>5.038192623206723</v>
+        <v>5.044405157681611</v>
       </c>
     </row>
     <row r="751">
@@ -25138,7 +25138,7 @@
         </is>
       </c>
       <c r="G751">
-        <v>48.14375359738895</v>
+        <v>48.1212577423255</v>
       </c>
     </row>
     <row r="752">
@@ -25204,7 +25204,7 @@
         </is>
       </c>
       <c r="G753">
-        <v>0.2535324122477262</v>
+        <v>0.2533867992233713</v>
       </c>
     </row>
     <row r="754">
@@ -25270,7 +25270,7 @@
         </is>
       </c>
       <c r="G755">
-        <v>0.4011692245037121</v>
+        <v>0.3961903249664059</v>
       </c>
     </row>
     <row r="756">
@@ -25336,7 +25336,7 @@
         </is>
       </c>
       <c r="G757">
-        <v>0.6339360783104661</v>
+        <v>0.6276892948543901</v>
       </c>
     </row>
     <row r="758">
@@ -25402,7 +25402,7 @@
         </is>
       </c>
       <c r="G759">
-        <v>0.9340108304846075</v>
+        <v>0.9255324288352941</v>
       </c>
     </row>
     <row r="760">
@@ -25468,7 +25468,7 @@
         </is>
       </c>
       <c r="G761">
-        <v>1.302356433136255</v>
+        <v>1.29100017885743</v>
       </c>
     </row>
     <row r="762">
@@ -25534,7 +25534,7 @@
         </is>
       </c>
       <c r="G763">
-        <v>1.801105528374743</v>
+        <v>1.785203339379792</v>
       </c>
     </row>
     <row r="764">
@@ -25600,7 +25600,7 @@
         </is>
       </c>
       <c r="G765">
-        <v>2.488050036178415</v>
+        <v>2.465761441414509</v>
       </c>
     </row>
     <row r="766">
@@ -25666,7 +25666,7 @@
         </is>
       </c>
       <c r="G767">
-        <v>3.201567182311668</v>
+        <v>3.170898580302149</v>
       </c>
     </row>
     <row r="768">
@@ -25732,7 +25732,7 @@
         </is>
       </c>
       <c r="G769">
-        <v>4.101052817977547</v>
+        <v>4.058547351936207</v>
       </c>
     </row>
     <row r="770">
@@ -25798,7 +25798,7 @@
         </is>
       </c>
       <c r="G771">
-        <v>5.237668171416681</v>
+        <v>5.177777340886661</v>
       </c>
     </row>
     <row r="772">
@@ -25831,7 +25831,7 @@
         </is>
       </c>
       <c r="G772">
-        <v>6.863021653999213</v>
+        <v>6.777903129233119</v>
       </c>
     </row>
     <row r="773">
@@ -25864,7 +25864,7 @@
         </is>
       </c>
       <c r="G773">
-        <v>6.863021653999213</v>
+        <v>6.777903129233119</v>
       </c>
     </row>
     <row r="774">
@@ -25897,7 +25897,7 @@
         </is>
       </c>
       <c r="G774">
-        <v>8.094090890584202</v>
+        <v>8.108906700970548</v>
       </c>
     </row>
     <row r="775">
@@ -25930,7 +25930,7 @@
         </is>
       </c>
       <c r="G775">
-        <v>8.895625209542139</v>
+        <v>8.778889216127729</v>
       </c>
     </row>
     <row r="776">
@@ -25963,7 +25963,7 @@
         </is>
       </c>
       <c r="G776">
-        <v>7.740581462975796</v>
+        <v>7.763112018915487</v>
       </c>
     </row>
     <row r="777">
@@ -25996,7 +25996,7 @@
         </is>
       </c>
       <c r="G777">
-        <v>11.22780057964367</v>
+        <v>11.07684391780902</v>
       </c>
     </row>
     <row r="778">
@@ -26029,7 +26029,7 @@
         </is>
       </c>
       <c r="G778">
-        <v>7.423063237259063</v>
+        <v>7.441338400812059</v>
       </c>
     </row>
     <row r="779">
@@ -26062,7 +26062,7 @@
         </is>
       </c>
       <c r="G779">
-        <v>14.8617323275275</v>
+        <v>14.39256872936611</v>
       </c>
     </row>
     <row r="780">
@@ -26095,7 +26095,7 @@
         </is>
       </c>
       <c r="G780">
-        <v>7.047431916698442</v>
+        <v>7.065293625231432</v>
       </c>
     </row>
     <row r="781">
@@ -26128,7 +26128,7 @@
         </is>
       </c>
       <c r="G781">
-        <v>17.81386580197984</v>
+        <v>17.28818751918845</v>
       </c>
     </row>
     <row r="782">
@@ -26161,7 +26161,7 @@
         </is>
       </c>
       <c r="G782">
-        <v>6.758638620458429</v>
+        <v>6.774272593107399</v>
       </c>
     </row>
     <row r="783">
@@ -26194,7 +26194,7 @@
         </is>
       </c>
       <c r="G783">
-        <v>21.00591044357561</v>
+        <v>20.47017508955354</v>
       </c>
     </row>
     <row r="784">
@@ -26227,7 +26227,7 @@
         </is>
       </c>
       <c r="G784">
-        <v>6.455010099310583</v>
+        <v>6.466930346387306</v>
       </c>
     </row>
     <row r="785">
@@ -26260,7 +26260,7 @@
         </is>
       </c>
       <c r="G785">
-        <v>23.99047407321756</v>
+        <v>23.50883753013294</v>
       </c>
     </row>
     <row r="786">
@@ -26293,7 +26293,7 @@
         </is>
       </c>
       <c r="G786">
-        <v>6.147719935234092</v>
+        <v>6.155743747205182</v>
       </c>
     </row>
     <row r="787">
@@ -26326,7 +26326,7 @@
         </is>
       </c>
       <c r="G787">
-        <v>26.92038741027748</v>
+        <v>26.53610233545232</v>
       </c>
     </row>
     <row r="788">
@@ -26359,7 +26359,7 @@
         </is>
       </c>
       <c r="G788">
-        <v>5.870714330519779</v>
+        <v>5.875859008793987</v>
       </c>
     </row>
     <row r="789">
@@ -26392,7 +26392,7 @@
         </is>
       </c>
       <c r="G789">
-        <v>29.89789883410394</v>
+        <v>29.62109314232398</v>
       </c>
     </row>
     <row r="790">
@@ -26425,7 +26425,7 @@
         </is>
       </c>
       <c r="G790">
-        <v>5.632191281027171</v>
+        <v>5.635670177246438</v>
       </c>
     </row>
     <row r="791">
@@ -26458,7 +26458,7 @@
         </is>
       </c>
       <c r="G791">
-        <v>32.96916187138056</v>
+        <v>32.78186713774259</v>
       </c>
     </row>
     <row r="792">
@@ -26491,7 +26491,7 @@
         </is>
       </c>
       <c r="G792">
-        <v>5.427536374598378</v>
+        <v>5.430358002221793</v>
       </c>
     </row>
     <row r="793">
@@ -26524,7 +26524,7 @@
         </is>
       </c>
       <c r="G793">
-        <v>36.10768342720859</v>
+        <v>35.98266350930751</v>
       </c>
     </row>
     <row r="794">
@@ -26557,7 +26557,7 @@
         </is>
       </c>
       <c r="G794">
-        <v>5.252793722742776</v>
+        <v>5.255709106389241</v>
       </c>
     </row>
     <row r="795">
@@ -26590,7 +26590,7 @@
         </is>
       </c>
       <c r="G795">
-        <v>39.32218154892851</v>
+        <v>39.23729481919887</v>
       </c>
     </row>
     <row r="796">
@@ -26623,7 +26623,7 @@
         </is>
       </c>
       <c r="G796">
-        <v>5.099086386092273</v>
+        <v>5.102626104338552</v>
       </c>
     </row>
     <row r="797">
@@ -26656,7 +26656,7 @@
         </is>
       </c>
       <c r="G797">
-        <v>42.44522756411354</v>
+        <v>42.3870105437572</v>
       </c>
     </row>
     <row r="798">
@@ -26689,7 +26689,7 @@
         </is>
       </c>
       <c r="G798">
-        <v>4.970763745887935</v>
+        <v>4.975355652018988</v>
       </c>
     </row>
     <row r="799">
@@ -26722,7 +26722,7 @@
         </is>
       </c>
       <c r="G799">
-        <v>45.50681586865035</v>
+        <v>45.46846411170063</v>
       </c>
     </row>
     <row r="800">
@@ -26755,7 +26755,7 @@
         </is>
       </c>
       <c r="G800">
-        <v>4.86264121363233</v>
+        <v>4.868542514404744</v>
       </c>
     </row>
     <row r="801">
@@ -26788,7 +26788,7 @@
         </is>
       </c>
       <c r="G801">
-        <v>48.36427749935383</v>
+        <v>48.34109630596189</v>
       </c>
     </row>
     <row r="802">
@@ -26854,7 +26854,7 @@
         </is>
       </c>
       <c r="G803">
-        <v>0.3826862401076917</v>
+        <v>0.3822482724023484</v>
       </c>
     </row>
     <row r="804">
@@ -26920,7 +26920,7 @@
         </is>
       </c>
       <c r="G805">
-        <v>0.463781234898887</v>
+        <v>0.4589411687749094</v>
       </c>
     </row>
     <row r="806">
@@ -26986,7 +26986,7 @@
         </is>
       </c>
       <c r="G807">
-        <v>0.6721235454523472</v>
+        <v>0.6664865039018303</v>
       </c>
     </row>
     <row r="808">
@@ -27052,7 +27052,7 @@
         </is>
       </c>
       <c r="G809">
-        <v>0.8174880052698156</v>
+        <v>0.8107135861459727</v>
       </c>
     </row>
     <row r="810">
@@ -27118,7 +27118,7 @@
         </is>
       </c>
       <c r="G811">
-        <v>1.026546450139576</v>
+        <v>1.017743253971457</v>
       </c>
     </row>
     <row r="812">
@@ -27184,7 +27184,7 @@
         </is>
       </c>
       <c r="G813">
-        <v>1.326257749521446</v>
+        <v>1.314216029625394</v>
       </c>
     </row>
     <row r="814">
@@ -27250,7 +27250,7 @@
         </is>
       </c>
       <c r="G815">
-        <v>1.643316081247897</v>
+        <v>1.627035710384525</v>
       </c>
     </row>
     <row r="816">
@@ -27316,7 +27316,7 @@
         </is>
       </c>
       <c r="G817">
-        <v>1.952762254513866</v>
+        <v>1.931303076312427</v>
       </c>
     </row>
     <row r="818">
@@ -27382,7 +27382,7 @@
         </is>
       </c>
       <c r="G819">
-        <v>2.358293631681657</v>
+        <v>2.330965814834795</v>
       </c>
     </row>
     <row r="820">
@@ -27448,7 +27448,7 @@
         </is>
       </c>
       <c r="G821">
-        <v>2.934983308248853</v>
+        <v>2.898017610562039</v>
       </c>
     </row>
     <row r="822">
@@ -27481,7 +27481,7 @@
         </is>
       </c>
       <c r="G822">
-        <v>3.396370958786921</v>
+        <v>3.390687932877066</v>
       </c>
     </row>
     <row r="823">
@@ -27514,7 +27514,7 @@
         </is>
       </c>
       <c r="G823">
-        <v>3.93214514974623</v>
+        <v>3.878240514898067</v>
       </c>
     </row>
     <row r="824">
@@ -27547,7 +27547,7 @@
         </is>
       </c>
       <c r="G824">
-        <v>3.346161662906371</v>
+        <v>3.344060391035855</v>
       </c>
     </row>
     <row r="825">
@@ -27580,7 +27580,7 @@
         </is>
       </c>
       <c r="G825">
-        <v>5.313062803392014</v>
+        <v>5.240075183852009</v>
       </c>
     </row>
     <row r="826">
@@ -27613,7 +27613,7 @@
         </is>
       </c>
       <c r="G826">
-        <v>3.271797624163153</v>
+        <v>3.274409420230016</v>
       </c>
     </row>
     <row r="827">
@@ -27646,7 +27646,7 @@
         </is>
       </c>
       <c r="G827">
-        <v>6.938300767383422</v>
+        <v>6.845546292987778</v>
       </c>
     </row>
     <row r="828">
@@ -27679,7 +27679,7 @@
         </is>
       </c>
       <c r="G828">
-        <v>3.240887367246766</v>
+        <v>3.23717118173551</v>
       </c>
     </row>
     <row r="829">
@@ -27712,7 +27712,7 @@
         </is>
       </c>
       <c r="G829">
-        <v>9.530627126706973</v>
+        <v>9.240522914429656</v>
       </c>
     </row>
     <row r="830">
@@ -27745,7 +27745,7 @@
         </is>
       </c>
       <c r="G830">
-        <v>3.157651917889456</v>
+        <v>3.158453165317319</v>
       </c>
     </row>
     <row r="831">
@@ -27778,7 +27778,7 @@
         </is>
       </c>
       <c r="G831">
-        <v>11.93177885880078</v>
+        <v>11.6114373993306</v>
       </c>
     </row>
     <row r="832">
@@ -27811,7 +27811,7 @@
         </is>
       </c>
       <c r="G832">
-        <v>3.133284545278169</v>
+        <v>3.137351771297596</v>
       </c>
     </row>
     <row r="833">
@@ -27844,7 +27844,7 @@
         </is>
       </c>
       <c r="G833">
-        <v>14.87017190800244</v>
+        <v>14.54682686038454</v>
       </c>
     </row>
     <row r="834">
@@ -27877,7 +27877,7 @@
         </is>
       </c>
       <c r="G834">
-        <v>3.095856896925183</v>
+        <v>3.101223762706942</v>
       </c>
     </row>
     <row r="835">
@@ -27910,7 +27910,7 @@
         </is>
       </c>
       <c r="G835">
-        <v>17.98676243529707</v>
+        <v>17.69881121680977</v>
       </c>
     </row>
     <row r="836">
@@ -27943,7 +27943,7 @@
         </is>
       </c>
       <c r="G836">
-        <v>3.064867334271164</v>
+        <v>3.07007833182502</v>
       </c>
     </row>
     <row r="837">
@@ -27976,7 +27976,7 @@
         </is>
       </c>
       <c r="G837">
-        <v>21.50283219234036</v>
+        <v>21.27465250959941</v>
       </c>
     </row>
     <row r="838">
@@ -28009,7 +28009,7 @@
         </is>
       </c>
       <c r="G838">
-        <v>3.027424546152429</v>
+        <v>3.031545314923961</v>
       </c>
     </row>
     <row r="839">
@@ -28042,7 +28042,7 @@
         </is>
       </c>
       <c r="G839">
-        <v>25.33683709558293</v>
+        <v>25.17272412098593</v>
       </c>
     </row>
     <row r="840">
@@ -28075,7 +28075,7 @@
         </is>
       </c>
       <c r="G840">
-        <v>2.983846761937423</v>
+        <v>2.986834063954188</v>
       </c>
     </row>
     <row r="841">
@@ -28108,7 +28108,7 @@
         </is>
       </c>
       <c r="G841">
-        <v>29.43269950410312</v>
+        <v>29.32094730805921</v>
       </c>
     </row>
     <row r="842">
@@ -28141,7 +28141,7 @@
         </is>
       </c>
       <c r="G842">
-        <v>2.937544640406319</v>
+        <v>2.939832209611996</v>
       </c>
     </row>
     <row r="843">
@@ -28174,7 +28174,7 @@
         </is>
       </c>
       <c r="G843">
-        <v>33.74938518396134</v>
+        <v>33.67372245624125</v>
       </c>
     </row>
     <row r="844">
@@ -28207,7 +28207,7 @@
         </is>
       </c>
       <c r="G844">
-        <v>2.893011066149934</v>
+        <v>2.895089295277741</v>
       </c>
     </row>
     <row r="845">
@@ -28240,7 +28240,7 @@
         </is>
       </c>
       <c r="G845">
-        <v>38.30930425870282</v>
+        <v>38.25716581532884</v>
       </c>
     </row>
     <row r="846">
@@ -28273,7 +28273,7 @@
         </is>
       </c>
       <c r="G846">
-        <v>2.851271673421912</v>
+        <v>2.85351927135321</v>
       </c>
     </row>
     <row r="847">
@@ -28306,7 +28306,7 @@
         </is>
       </c>
       <c r="G847">
-        <v>42.97590321390632</v>
+        <v>42.9399493571838</v>
       </c>
     </row>
     <row r="848">
@@ -28339,7 +28339,7 @@
         </is>
       </c>
       <c r="G848">
-        <v>2.816342111866154</v>
+        <v>2.819061721977765</v>
       </c>
     </row>
     <row r="849">
@@ -28372,7 +28372,7 @@
         </is>
       </c>
       <c r="G849">
-        <v>47.75056266391508</v>
+        <v>47.72776202912392</v>
       </c>
     </row>
     <row r="850">
@@ -28405,7 +28405,7 @@
         </is>
       </c>
       <c r="G850">
-        <v>2.787339752658095</v>
+        <v>2.790712270835585</v>
       </c>
     </row>
     <row r="851">
@@ -28438,7 +28438,7 @@
         </is>
       </c>
       <c r="G851">
-        <v>52.36284729030645</v>
+        <v>52.35087732045136</v>
       </c>
     </row>
     <row r="852">
@@ -28504,7 +28504,7 @@
         </is>
       </c>
       <c r="G853">
-        <v>0.3971398248443654</v>
+        <v>0.3966852657595996</v>
       </c>
     </row>
     <row r="854">
@@ -28570,7 +28570,7 @@
         </is>
       </c>
       <c r="G855">
-        <v>0.5042696266797249</v>
+        <v>0.4990028347503203</v>
       </c>
     </row>
     <row r="856">
@@ -28636,7 +28636,7 @@
         </is>
       </c>
       <c r="G857">
-        <v>0.7556660726810844</v>
+        <v>0.749311271155727</v>
       </c>
     </row>
     <row r="858">
@@ -28702,7 +28702,7 @@
         </is>
       </c>
       <c r="G859">
-        <v>0.9465593588540788</v>
+        <v>0.9386764008059896</v>
       </c>
     </row>
     <row r="860">
@@ -28768,7 +28768,7 @@
         </is>
       </c>
       <c r="G861">
-        <v>1.217580083850305</v>
+        <v>1.207054450023943</v>
       </c>
     </row>
     <row r="862">
@@ -28834,7 +28834,7 @@
         </is>
       </c>
       <c r="G863">
-        <v>1.601659993681251</v>
+        <v>1.586938823256036</v>
       </c>
     </row>
     <row r="864">
@@ -28900,7 +28900,7 @@
         </is>
       </c>
       <c r="G865">
-        <v>2.024407453062718</v>
+        <v>2.004009077773663</v>
       </c>
     </row>
     <row r="866">
@@ -28966,7 +28966,7 @@
         </is>
       </c>
       <c r="G867">
-        <v>2.45978773838051</v>
+        <v>2.432146870491327</v>
       </c>
     </row>
     <row r="868">
@@ -29032,7 +29032,7 @@
         </is>
       </c>
       <c r="G869">
-        <v>3.031967015669539</v>
+        <v>2.995797668006222</v>
       </c>
     </row>
     <row r="870">
@@ -29098,7 +29098,7 @@
         </is>
       </c>
       <c r="G871">
-        <v>3.846913850751733</v>
+        <v>3.796691765319271</v>
       </c>
     </row>
     <row r="872">
@@ -29131,7 +29131,7 @@
         </is>
       </c>
       <c r="G872">
-        <v>4.496447858195709</v>
+        <v>4.485959529458442</v>
       </c>
     </row>
     <row r="873">
@@ -29164,7 +29164,7 @@
         </is>
       </c>
       <c r="G873">
-        <v>5.228769231260323</v>
+        <v>5.153945825043162</v>
       </c>
     </row>
     <row r="874">
@@ -29197,7 +29197,7 @@
         </is>
       </c>
       <c r="G874">
-        <v>4.47646190316562</v>
+        <v>4.470093717273282</v>
       </c>
     </row>
     <row r="875">
@@ -29230,7 +29230,7 @@
         </is>
       </c>
       <c r="G875">
-        <v>7.145505466780228</v>
+        <v>7.042189249464258</v>
       </c>
     </row>
     <row r="876">
@@ -29263,7 +29263,7 @@
         </is>
       </c>
       <c r="G876">
-        <v>4.413756910138905</v>
+        <v>4.412997151410625</v>
       </c>
     </row>
     <row r="877">
@@ -29296,7 +29296,7 @@
         </is>
       </c>
       <c r="G877">
-        <v>9.419806592721667</v>
+        <v>9.285591271195264</v>
       </c>
     </row>
     <row r="878">
@@ -29329,7 +29329,7 @@
         </is>
       </c>
       <c r="G878">
-        <v>4.409463792650198</v>
+        <v>4.394512332325299</v>
       </c>
     </row>
     <row r="879">
@@ -29362,7 +29362,7 @@
         </is>
       </c>
       <c r="G879">
-        <v>13.06080113813394</v>
+        <v>12.63734736707985</v>
       </c>
     </row>
     <row r="880">
@@ -29395,7 +29395,7 @@
         </is>
       </c>
       <c r="G880">
-        <v>4.344420567735271</v>
+        <v>4.334769124525482</v>
       </c>
     </row>
     <row r="881">
@@ -29428,7 +29428,7 @@
         </is>
       </c>
       <c r="G881">
-        <v>16.56415723763429</v>
+        <v>16.0832464740906</v>
       </c>
     </row>
     <row r="882">
@@ -29461,7 +29461,7 @@
         </is>
       </c>
       <c r="G882">
-        <v>4.227439519882928</v>
+        <v>4.222159447914492</v>
       </c>
     </row>
     <row r="883">
@@ -29494,7 +29494,7 @@
         </is>
       </c>
       <c r="G883">
-        <v>20.29440174160228</v>
+        <v>19.80744635170115</v>
       </c>
     </row>
     <row r="884">
@@ -29527,7 +29527,7 @@
         </is>
       </c>
       <c r="G884">
-        <v>4.080050840663588</v>
+        <v>4.077575577342549</v>
       </c>
     </row>
     <row r="885">
@@ -29560,7 +29560,7 @@
         </is>
       </c>
       <c r="G885">
-        <v>24.05248516490613</v>
+        <v>23.61761125050351</v>
       </c>
     </row>
     <row r="886">
@@ -29593,7 +29593,7 @@
         </is>
       </c>
       <c r="G886">
-        <v>3.934630148255579</v>
+        <v>3.933910937815572</v>
       </c>
     </row>
     <row r="887">
@@ -29626,7 +29626,7 @@
         </is>
       </c>
       <c r="G887">
-        <v>28.10715772716834</v>
+        <v>27.76195427513347</v>
       </c>
     </row>
     <row r="888">
@@ -29659,7 +29659,7 @@
         </is>
       </c>
       <c r="G888">
-        <v>3.783467297259511</v>
+        <v>3.783549705756491</v>
       </c>
     </row>
     <row r="889">
@@ -29692,7 +29692,7 @@
         </is>
       </c>
       <c r="G889">
-        <v>32.3573906161506</v>
+        <v>32.10928666928419</v>
       </c>
     </row>
     <row r="890">
@@ -29725,7 +29725,7 @@
         </is>
       </c>
       <c r="G890">
-        <v>3.633614937093723</v>
+        <v>3.634078792451255</v>
       </c>
     </row>
     <row r="891">
@@ -29758,7 +29758,7 @@
         </is>
       </c>
       <c r="G891">
-        <v>36.75602999940374</v>
+        <v>36.58786739580281</v>
       </c>
     </row>
     <row r="892">
@@ -29791,7 +29791,7 @@
         </is>
       </c>
       <c r="G892">
-        <v>3.489137007986703</v>
+        <v>3.48993146487788</v>
       </c>
     </row>
     <row r="893">
@@ -29824,7 +29824,7 @@
         </is>
       </c>
       <c r="G893">
-        <v>41.24792951702678</v>
+        <v>41.13512834027954</v>
       </c>
     </row>
     <row r="894">
@@ -29857,7 +29857,7 @@
         </is>
       </c>
       <c r="G894">
-        <v>3.352740637690589</v>
+        <v>3.353974979343669</v>
       </c>
     </row>
     <row r="895">
@@ -29890,7 +29890,7 @@
         </is>
       </c>
       <c r="G895">
-        <v>45.83426635622443</v>
+        <v>45.75743092610963</v>
       </c>
     </row>
     <row r="896">
@@ -29923,7 +29923,7 @@
         </is>
       </c>
       <c r="G896">
-        <v>3.224760620257206</v>
+        <v>3.22657922456334</v>
       </c>
     </row>
     <row r="897">
@@ -29956,7 +29956,7 @@
         </is>
       </c>
       <c r="G897">
-        <v>50.33882377473665</v>
+        <v>50.28639796830817</v>
       </c>
     </row>
     <row r="898">
@@ -29989,7 +29989,7 @@
         </is>
       </c>
       <c r="G898">
-        <v>3.109557113705137</v>
+        <v>3.112125855715534</v>
       </c>
     </row>
     <row r="899">
@@ -30022,7 +30022,7 @@
         </is>
       </c>
       <c r="G899">
-        <v>54.77099668681601</v>
+        <v>54.73765843111887</v>
       </c>
     </row>
     <row r="900">
@@ -30055,7 +30055,7 @@
         </is>
       </c>
       <c r="G900">
-        <v>3.007470005441005</v>
+        <v>3.010869518272182</v>
       </c>
     </row>
     <row r="901">
@@ -30088,7 +30088,7 @@
         </is>
       </c>
       <c r="G901">
-        <v>58.86000557378455</v>
+        <v>58.84184686854038</v>
       </c>
     </row>
     <row r="902">
@@ -30154,7 +30154,7 @@
         </is>
       </c>
       <c r="G903">
-        <v>0.4286854754881058</v>
+        <v>0.4281643956203291</v>
       </c>
     </row>
     <row r="904">
@@ -30220,7 +30220,7 @@
         </is>
       </c>
       <c r="G905">
-        <v>0.5462542721440377</v>
+        <v>0.540707677186065</v>
       </c>
     </row>
     <row r="906">
@@ -30286,7 +30286,7 @@
         </is>
       </c>
       <c r="G907">
-        <v>0.8289324828715577</v>
+        <v>0.8221238255591706</v>
       </c>
     </row>
     <row r="908">
@@ -30352,7 +30352,7 @@
         </is>
       </c>
       <c r="G909">
-        <v>1.052751915586738</v>
+        <v>1.044142118592164</v>
       </c>
     </row>
     <row r="910">
@@ -30418,7 +30418,7 @@
         </is>
       </c>
       <c r="G911">
-        <v>1.378982765030832</v>
+        <v>1.367220151599418</v>
       </c>
     </row>
     <row r="912">
@@ -30484,7 +30484,7 @@
         </is>
       </c>
       <c r="G913">
-        <v>1.851380979146942</v>
+        <v>1.834483221824428</v>
       </c>
     </row>
     <row r="914">
@@ -30550,7 +30550,7 @@
         </is>
       </c>
       <c r="G915">
-        <v>2.378422049813593</v>
+        <v>2.35443845769892</v>
       </c>
     </row>
     <row r="916">
@@ -30616,7 +30616,7 @@
         </is>
       </c>
       <c r="G917">
-        <v>2.923552984699529</v>
+        <v>2.890409828963567</v>
       </c>
     </row>
     <row r="918">
@@ -30682,7 +30682,7 @@
         </is>
       </c>
       <c r="G919">
-        <v>3.641751291043493</v>
+        <v>3.597608340049118</v>
       </c>
     </row>
     <row r="920">
@@ -30748,7 +30748,7 @@
         </is>
       </c>
       <c r="G921">
-        <v>4.678331990222591</v>
+        <v>4.615829530355688</v>
       </c>
     </row>
     <row r="922">
@@ -30781,7 +30781,7 @@
         </is>
       </c>
       <c r="G922">
-        <v>6.265018335334219</v>
+        <v>6.172606532885728</v>
       </c>
     </row>
     <row r="923">
@@ -30814,7 +30814,7 @@
         </is>
       </c>
       <c r="G923">
-        <v>6.265018335334219</v>
+        <v>6.172606532885728</v>
       </c>
     </row>
     <row r="924">
@@ -30847,7 +30847,7 @@
         </is>
       </c>
       <c r="G924">
-        <v>7.743068497761302</v>
+        <v>7.743132252144203</v>
       </c>
     </row>
     <row r="925">
@@ -30880,7 +30880,7 @@
         </is>
       </c>
       <c r="G925">
-        <v>8.470714077375058</v>
+        <v>8.343882977543835</v>
       </c>
     </row>
     <row r="926">
@@ -30913,7 +30913,7 @@
         </is>
       </c>
       <c r="G926">
-        <v>7.65085810407076</v>
+        <v>7.66279790979768</v>
       </c>
     </row>
     <row r="927">
@@ -30946,7 +30946,7 @@
         </is>
       </c>
       <c r="G927">
-        <v>11.034777073009</v>
+        <v>10.87095258900309</v>
       </c>
     </row>
     <row r="928">
@@ -30979,7 +30979,7 @@
         </is>
       </c>
       <c r="G928">
-        <v>7.626437582561477</v>
+        <v>7.627688800271926</v>
       </c>
     </row>
     <row r="929">
@@ -31012,7 +31012,7 @@
         </is>
       </c>
       <c r="G929">
-        <v>15.17024144539477</v>
+        <v>14.65477127711188</v>
       </c>
     </row>
     <row r="930">
@@ -31045,7 +31045,7 @@
         </is>
       </c>
       <c r="G930">
-        <v>7.476934536087473</v>
+        <v>7.487635153444153</v>
       </c>
     </row>
     <row r="931">
@@ -31078,7 +31078,7 @@
         </is>
       </c>
       <c r="G931">
-        <v>18.74451052160799</v>
+        <v>18.16703881205825</v>
       </c>
     </row>
     <row r="932">
@@ -31111,7 +31111,7 @@
         </is>
       </c>
       <c r="G932">
-        <v>7.376392662199155</v>
+        <v>7.393151686125742</v>
       </c>
     </row>
     <row r="933">
@@ -31144,7 +31144,7 @@
         </is>
       </c>
       <c r="G933">
-        <v>22.68067756598637</v>
+        <v>22.09538293995479</v>
       </c>
     </row>
     <row r="934">
@@ -31177,7 +31177,7 @@
         </is>
       </c>
       <c r="G934">
-        <v>7.233032776558044</v>
+        <v>7.25096392333454</v>
       </c>
     </row>
     <row r="935">
@@ -31210,7 +31210,7 @@
         </is>
       </c>
       <c r="G935">
-        <v>26.5112448288436</v>
+        <v>25.98836366880411</v>
       </c>
     </row>
     <row r="936">
@@ -31243,7 +31243,7 @@
         </is>
       </c>
       <c r="G936">
-        <v>7.096829792482636</v>
+        <v>7.112717477552098</v>
       </c>
     </row>
     <row r="937">
@@ -31276,7 +31276,7 @@
         </is>
       </c>
       <c r="G937">
-        <v>30.53877135992729</v>
+        <v>30.12374529201399</v>
       </c>
     </row>
     <row r="938">
@@ -31309,7 +31309,7 @@
         </is>
       </c>
       <c r="G938">
-        <v>6.949528921046658</v>
+        <v>6.961511818378553</v>
       </c>
     </row>
     <row r="939">
@@ -31342,7 +31342,7 @@
         </is>
       </c>
       <c r="G939">
-        <v>34.64975181646578</v>
+        <v>34.35178027787975</v>
       </c>
     </row>
     <row r="940">
@@ -31375,7 +31375,7 @@
         </is>
       </c>
       <c r="G940">
-        <v>6.792921419454475</v>
+        <v>6.801303974838628</v>
       </c>
     </row>
     <row r="941">
@@ -31408,7 +31408,7 @@
         </is>
       </c>
       <c r="G941">
-        <v>38.7889666080946</v>
+        <v>38.58750877786232</v>
       </c>
     </row>
     <row r="942">
@@ -31441,7 +31441,7 @@
         </is>
       </c>
       <c r="G942">
-        <v>6.635116321525575</v>
+        <v>6.64129421031175</v>
       </c>
     </row>
     <row r="943">
@@ -31474,7 +31474,7 @@
         </is>
       </c>
       <c r="G943">
-        <v>42.91176991667685</v>
+        <v>42.77722955901421</v>
       </c>
     </row>
     <row r="944">
@@ -31507,7 +31507,7 @@
         </is>
       </c>
       <c r="G944">
-        <v>6.485341698152792</v>
+        <v>6.490719758546803</v>
       </c>
     </row>
     <row r="945">
@@ -31540,7 +31540,7 @@
         </is>
       </c>
       <c r="G945">
-        <v>47.04257125502091</v>
+        <v>46.95136887204045</v>
       </c>
     </row>
     <row r="946">
@@ -31573,7 +31573,7 @@
         </is>
       </c>
       <c r="G946">
-        <v>6.346574907027365</v>
+        <v>6.352191220967287</v>
       </c>
     </row>
     <row r="947">
@@ -31606,7 +31606,7 @@
         </is>
       </c>
       <c r="G947">
-        <v>51.02891464564445</v>
+        <v>50.96691816859096</v>
       </c>
     </row>
     <row r="948">
@@ -31639,7 +31639,7 @@
         </is>
       </c>
       <c r="G948">
-        <v>6.227459213806399</v>
+        <v>6.234091227539281</v>
       </c>
     </row>
     <row r="949">
@@ -31672,7 +31672,7 @@
         </is>
       </c>
       <c r="G949">
-        <v>54.90363535675151</v>
+        <v>54.86405946928321</v>
       </c>
     </row>
     <row r="950">
@@ -31705,7 +31705,7 @@
         </is>
       </c>
       <c r="G950">
-        <v>6.130116832415272</v>
+        <v>6.138230320822522</v>
       </c>
     </row>
     <row r="951">
@@ -31738,7 +31738,7 @@
         </is>
       </c>
       <c r="G951">
-        <v>58.55185792449365</v>
+        <v>58.52980193626206</v>
       </c>
     </row>
     <row r="952">
@@ -31804,7 +31804,7 @@
         </is>
       </c>
       <c r="G953">
-        <v>0.4448588363070917</v>
+        <v>0.4443180401087431</v>
       </c>
     </row>
     <row r="954">
@@ -31870,7 +31870,7 @@
         </is>
       </c>
       <c r="G955">
-        <v>0.5938675114946059</v>
+        <v>0.5878327599645887</v>
       </c>
     </row>
     <row r="956">
@@ -31936,7 +31936,7 @@
         </is>
       </c>
       <c r="G957">
-        <v>0.9319173315631414</v>
+        <v>0.9242436291669857</v>
       </c>
     </row>
     <row r="958">
@@ -32002,7 +32002,7 @@
         </is>
       </c>
       <c r="G959">
-        <v>1.219143359338748</v>
+        <v>1.209128062463676</v>
       </c>
     </row>
     <row r="960">
@@ -32068,7 +32068,7 @@
         </is>
       </c>
       <c r="G961">
-        <v>1.636385891236137</v>
+        <v>1.622328784144979</v>
       </c>
     </row>
     <row r="962">
@@ -32134,7 +32134,7 @@
         </is>
       </c>
       <c r="G963">
-        <v>2.23789270838414</v>
+        <v>2.217250892096049</v>
       </c>
     </row>
     <row r="964">
@@ -32200,7 +32200,7 @@
         </is>
       </c>
       <c r="G965">
-        <v>2.93440391800964</v>
+        <v>2.904386080722477</v>
       </c>
     </row>
     <row r="966">
@@ -32266,7 +32266,7 @@
         </is>
       </c>
       <c r="G967">
-        <v>3.690669563664346</v>
+        <v>3.648039353593275</v>
       </c>
     </row>
     <row r="968">
@@ -32332,7 +32332,7 @@
         </is>
       </c>
       <c r="G969">
-        <v>4.695916590396903</v>
+        <v>4.637594075301211</v>
       </c>
     </row>
     <row r="970">
@@ -32398,7 +32398,7 @@
         </is>
       </c>
       <c r="G971">
-        <v>6.154990977378176</v>
+        <v>6.070259936331699</v>
       </c>
     </row>
     <row r="972">
@@ -32431,7 +32431,7 @@
         </is>
       </c>
       <c r="G972">
-        <v>8.370114092761114</v>
+        <v>8.24215193621507</v>
       </c>
     </row>
     <row r="973">
@@ -32464,7 +32464,7 @@
         </is>
       </c>
       <c r="G973">
-        <v>8.370114092761114</v>
+        <v>8.24215193621507</v>
       </c>
     </row>
     <row r="974">
@@ -32497,7 +32497,7 @@
         </is>
       </c>
       <c r="G974">
-        <v>10.42536292295875</v>
+        <v>10.41786238183835</v>
       </c>
     </row>
     <row r="975">
@@ -32530,7 +32530,7 @@
         </is>
       </c>
       <c r="G975">
-        <v>11.45714521293613</v>
+        <v>11.27810662645998</v>
       </c>
     </row>
     <row r="976">
@@ -32563,7 +32563,7 @@
         </is>
       </c>
       <c r="G976">
-        <v>10.40074355235281</v>
+        <v>10.40750601494664</v>
       </c>
     </row>
     <row r="977">
@@ -32596,7 +32596,7 @@
         </is>
       </c>
       <c r="G977">
-        <v>15.08359338400584</v>
+        <v>14.8473496167591</v>
       </c>
     </row>
     <row r="978">
@@ -32629,7 +32629,7 @@
         </is>
       </c>
       <c r="G978">
-        <v>10.46544018398703</v>
+        <v>10.44531675907733</v>
       </c>
     </row>
     <row r="979">
@@ -32662,7 +32662,7 @@
         </is>
       </c>
       <c r="G979">
-        <v>20.94661647249188</v>
+        <v>20.19680872800165</v>
       </c>
     </row>
     <row r="980">
@@ -32695,7 +32695,7 @@
         </is>
       </c>
       <c r="G980">
-        <v>10.38337764022973</v>
+        <v>10.3732647279262</v>
       </c>
     </row>
     <row r="981">
@@ -32728,7 +32728,7 @@
         </is>
       </c>
       <c r="G981">
-        <v>26.23651561709988</v>
+        <v>25.37333920117842</v>
       </c>
     </row>
     <row r="982">
@@ -32761,7 +32761,7 @@
         </is>
       </c>
       <c r="G982">
-        <v>10.05323923058528</v>
+        <v>10.04978927295508</v>
       </c>
     </row>
     <row r="983">
@@ -32794,7 +32794,7 @@
         </is>
       </c>
       <c r="G983">
-        <v>31.23234735461658</v>
+        <v>30.35526379149718</v>
       </c>
     </row>
     <row r="984">
@@ -32827,7 +32827,7 @@
         </is>
       </c>
       <c r="G984">
-        <v>9.632813195779347</v>
+        <v>9.632136043169348</v>
       </c>
     </row>
     <row r="985">
@@ -32860,7 +32860,7 @@
         </is>
       </c>
       <c r="G985">
-        <v>35.78438673559747</v>
+        <v>34.99897298990456</v>
       </c>
     </row>
     <row r="986">
@@ -32893,7 +32893,7 @@
         </is>
       </c>
       <c r="G986">
-        <v>9.204951713364153</v>
+        <v>9.20550645490067</v>
       </c>
     </row>
     <row r="987">
@@ -32926,7 +32926,7 @@
         </is>
       </c>
       <c r="G987">
-        <v>40.28751728237492</v>
+        <v>39.66310904496676</v>
       </c>
     </row>
     <row r="988">
@@ -32959,7 +32959,7 @@
         </is>
       </c>
       <c r="G988">
-        <v>8.769697662665958</v>
+        <v>8.770420015418935</v>
       </c>
     </row>
     <row r="989">
@@ -32992,7 +32992,7 @@
         </is>
       </c>
       <c r="G989">
-        <v>44.63748209154913</v>
+        <v>44.1891691977994</v>
       </c>
     </row>
     <row r="990">
@@ -33025,7 +33025,7 @@
         </is>
       </c>
       <c r="G990">
-        <v>8.347000244113278</v>
+        <v>8.347854828433066</v>
       </c>
     </row>
     <row r="991">
@@ -33058,7 +33058,7 @@
         </is>
       </c>
       <c r="G991">
-        <v>48.83257059183277</v>
+        <v>48.53017316413445</v>
       </c>
     </row>
     <row r="992">
@@ -33091,7 +33091,7 @@
         </is>
       </c>
       <c r="G992">
-        <v>7.947585850641641</v>
+        <v>7.948992908609247</v>
       </c>
     </row>
     <row r="993">
@@ -33124,7 +33124,7 @@
         </is>
       </c>
       <c r="G993">
-        <v>52.84015155225311</v>
+        <v>52.63916463495695</v>
       </c>
     </row>
     <row r="994">
@@ -33157,7 +33157,7 @@
         </is>
       </c>
       <c r="G994">
-        <v>7.576061922642448</v>
+        <v>7.578498026615923</v>
       </c>
     </row>
     <row r="995">
@@ -33190,7 +33190,7 @@
         </is>
       </c>
       <c r="G995">
-        <v>56.67874305574728</v>
+        <v>56.54319805774682</v>
       </c>
     </row>
     <row r="996">
@@ -33223,7 +33223,7 @@
         </is>
       </c>
       <c r="G996">
-        <v>7.232670936667475</v>
+        <v>7.236558182706611</v>
       </c>
     </row>
     <row r="997">
@@ -33256,7 +33256,7 @@
         </is>
       </c>
       <c r="G997">
-        <v>60.16559974103192</v>
+        <v>60.07367551635089</v>
       </c>
     </row>
     <row r="998">
@@ -33289,7 +33289,7 @@
         </is>
       </c>
       <c r="G998">
-        <v>6.925796845708766</v>
+        <v>6.931544403256064</v>
       </c>
     </row>
     <row r="999">
@@ -33322,7 +33322,7 @@
         </is>
       </c>
       <c r="G999">
-        <v>63.36266079025323</v>
+        <v>63.30333341695366</v>
       </c>
     </row>
     <row r="1000">
@@ -33355,7 +33355,7 @@
         </is>
       </c>
       <c r="G1000">
-        <v>6.658431573045351</v>
+        <v>6.666235579585108</v>
       </c>
     </row>
     <row r="1001">
@@ -33388,7 +33388,7 @@
         </is>
       </c>
       <c r="G1001">
-        <v>66.17889018204605</v>
+        <v>66.1444458852001</v>
       </c>
     </row>
     <row r="1002">
@@ -33421,7 +33421,7 @@
         </is>
       </c>
       <c r="G1002">
-        <v>0.3760751686629943</v>
+        <v>0.3758827476134916</v>
       </c>
     </row>
     <row r="1003">
@@ -33454,7 +33454,7 @@
         </is>
       </c>
       <c r="G1003">
-        <v>0.3760751686629943</v>
+        <v>0.3758827476134916</v>
       </c>
     </row>
     <row r="1004">
@@ -33487,7 +33487,7 @@
         </is>
       </c>
       <c r="G1004">
-        <v>0.4778281202494726</v>
+        <v>0.4717206974256394</v>
       </c>
     </row>
     <row r="1005">
@@ -33520,7 +33520,7 @@
         </is>
       </c>
       <c r="G1005">
-        <v>0.4778281202494726</v>
+        <v>0.4717206974256394</v>
       </c>
     </row>
     <row r="1006">
@@ -33553,7 +33553,7 @@
         </is>
       </c>
       <c r="G1006">
-        <v>0.6350048400689667</v>
+        <v>0.6278714334802673</v>
       </c>
     </row>
     <row r="1007">
@@ -33586,7 +33586,7 @@
         </is>
       </c>
       <c r="G1007">
-        <v>0.6350048400689667</v>
+        <v>0.6278714334802673</v>
       </c>
     </row>
     <row r="1008">
@@ -33619,7 +33619,7 @@
         </is>
       </c>
       <c r="G1008">
-        <v>0.8390216601781353</v>
+        <v>0.829936774033013</v>
       </c>
     </row>
     <row r="1009">
@@ -33652,7 +33652,7 @@
         </is>
       </c>
       <c r="G1009">
-        <v>0.8390216601781353</v>
+        <v>0.829936774033013</v>
       </c>
     </row>
     <row r="1010">
@@ -33685,7 +33685,7 @@
         </is>
       </c>
       <c r="G1010">
-        <v>1.076652122357384</v>
+        <v>1.06519138078969</v>
       </c>
     </row>
     <row r="1011">
@@ -33718,7 +33718,7 @@
         </is>
       </c>
       <c r="G1011">
-        <v>1.076652122357384</v>
+        <v>1.06519138078969</v>
       </c>
     </row>
     <row r="1012">
@@ -33751,7 +33751,7 @@
         </is>
       </c>
       <c r="G1012">
-        <v>1.404481942389398</v>
+        <v>1.389102159124596</v>
       </c>
     </row>
     <row r="1013">
@@ -33784,7 +33784,7 @@
         </is>
       </c>
       <c r="G1013">
-        <v>1.404481942389398</v>
+        <v>1.389102159124596</v>
       </c>
     </row>
     <row r="1014">
@@ -33817,7 +33817,7 @@
         </is>
       </c>
       <c r="G1014">
-        <v>1.867262767914808</v>
+        <v>1.846761328180617</v>
       </c>
     </row>
     <row r="1015">
@@ -33850,7 +33850,7 @@
         </is>
       </c>
       <c r="G1015">
-        <v>1.867262767914808</v>
+        <v>1.846761328180617</v>
       </c>
     </row>
     <row r="1016">
@@ -33883,7 +33883,7 @@
         </is>
       </c>
       <c r="G1016">
-        <v>2.299326416020189</v>
+        <v>2.272546881113096</v>
       </c>
     </row>
     <row r="1017">
@@ -33916,7 +33916,7 @@
         </is>
       </c>
       <c r="G1017">
-        <v>2.299326416020189</v>
+        <v>2.272546881113096</v>
       </c>
     </row>
     <row r="1018">
@@ -33949,7 +33949,7 @@
         </is>
       </c>
       <c r="G1018">
-        <v>2.83614958024397</v>
+        <v>2.800567253008186</v>
       </c>
     </row>
     <row r="1019">
@@ -33982,7 +33982,7 @@
         </is>
       </c>
       <c r="G1019">
-        <v>2.83614958024397</v>
+        <v>2.800567253008186</v>
       </c>
     </row>
     <row r="1020">
@@ -34015,7 +34015,7 @@
         </is>
       </c>
       <c r="G1020">
-        <v>3.534899120776397</v>
+        <v>3.487064406606547</v>
       </c>
     </row>
     <row r="1021">
@@ -34048,7 +34048,7 @@
         </is>
       </c>
       <c r="G1021">
-        <v>3.534899120776397</v>
+        <v>3.487064406606547</v>
       </c>
     </row>
     <row r="1022">
@@ -34081,7 +34081,7 @@
         </is>
       </c>
       <c r="G1022">
-        <v>4.082246420904882</v>
+        <v>4.073358847918063</v>
       </c>
     </row>
     <row r="1023">
@@ -34114,7 +34114,7 @@
         </is>
       </c>
       <c r="G1023">
-        <v>4.726741452045114</v>
+        <v>4.659552355896011</v>
       </c>
     </row>
     <row r="1024">
@@ -34147,7 +34147,7 @@
         </is>
       </c>
       <c r="G1024">
-        <v>3.950634274728754</v>
+        <v>3.944833453423789</v>
       </c>
     </row>
     <row r="1025">
@@ -34180,7 +34180,7 @@
         </is>
       </c>
       <c r="G1025">
-        <v>6.274705837528136</v>
+        <v>6.183266229188663</v>
       </c>
     </row>
     <row r="1026">
@@ -34213,7 +34213,7 @@
         </is>
       </c>
       <c r="G1026">
-        <v>3.819829434804796</v>
+        <v>3.818719317196407</v>
       </c>
     </row>
     <row r="1027">
@@ -34246,7 +34246,7 @@
         </is>
       </c>
       <c r="G1027">
-        <v>8.103875325028612</v>
+        <v>7.986801412645833</v>
       </c>
     </row>
     <row r="1028">
@@ -34279,7 +34279,7 @@
         </is>
       </c>
       <c r="G1028">
-        <v>3.727466969374548</v>
+        <v>3.712217692928007</v>
       </c>
     </row>
     <row r="1029">
@@ -34312,7 +34312,7 @@
         </is>
       </c>
       <c r="G1029">
-        <v>10.96716818895942</v>
+        <v>10.60191960126663</v>
       </c>
     </row>
     <row r="1030">
@@ -34345,7 +34345,7 @@
         </is>
       </c>
       <c r="G1030">
-        <v>3.511905659110457</v>
+        <v>3.499480410918141</v>
       </c>
     </row>
     <row r="1031">
@@ -34378,7 +34378,7 @@
         </is>
       </c>
       <c r="G1031">
-        <v>13.27780925076247</v>
+        <v>12.87227620095429</v>
       </c>
     </row>
     <row r="1032">
@@ -34411,7 +34411,7 @@
         </is>
       </c>
       <c r="G1032">
-        <v>3.372222817332678</v>
+        <v>3.362959688623962</v>
       </c>
     </row>
     <row r="1033">
@@ -34444,7 +34444,7 @@
         </is>
       </c>
       <c r="G1033">
-        <v>16.01347420414099</v>
+        <v>15.60191338323323</v>
       </c>
     </row>
     <row r="1034">
@@ -34477,7 +34477,7 @@
         </is>
       </c>
       <c r="G1034">
-        <v>3.238037706014662</v>
+        <v>3.232011587549889</v>
       </c>
     </row>
     <row r="1035">
@@ -34510,7 +34510,7 @@
         </is>
       </c>
       <c r="G1035">
-        <v>18.82388402440027</v>
+        <v>18.4559972862882</v>
       </c>
     </row>
     <row r="1036">
@@ -34543,7 +34543,7 @@
         </is>
       </c>
       <c r="G1036">
-        <v>3.120579490801471</v>
+        <v>3.117274083605106</v>
       </c>
     </row>
     <row r="1037">
@@ -34576,7 +34576,7 @@
         </is>
       </c>
       <c r="G1037">
-        <v>21.90653312027223</v>
+        <v>21.61430318930573</v>
       </c>
     </row>
     <row r="1038">
@@ -34609,7 +34609,7 @@
         </is>
       </c>
       <c r="G1038">
-        <v>3.029736602125035</v>
+        <v>3.028361840770897</v>
       </c>
     </row>
     <row r="1039">
@@ -34642,7 +34642,7 @@
         </is>
       </c>
       <c r="G1039">
-        <v>25.37103060105721</v>
+        <v>25.16096533407439</v>
       </c>
     </row>
     <row r="1040">
@@ -34675,7 +34675,7 @@
         </is>
       </c>
       <c r="G1040">
-        <v>2.960136738015727</v>
+        <v>2.959893548308755</v>
       </c>
     </row>
     <row r="1041">
@@ -34708,7 +34708,7 @@
         </is>
       </c>
       <c r="G1041">
-        <v>29.2160026099804</v>
+        <v>29.07354309579648</v>
       </c>
     </row>
     <row r="1042">
@@ -34741,7 +34741,7 @@
         </is>
       </c>
       <c r="G1042">
-        <v>2.90471132716014</v>
+        <v>2.905143859364357</v>
       </c>
     </row>
     <row r="1043">
@@ -34774,7 +34774,7 @@
         </is>
       </c>
       <c r="G1043">
-        <v>33.39196355016201</v>
+        <v>33.29611277453994</v>
       </c>
     </row>
     <row r="1044">
@@ -34807,7 +34807,7 @@
         </is>
       </c>
       <c r="G1044">
-        <v>2.862236613601316</v>
+        <v>2.863222832835963</v>
       </c>
     </row>
     <row r="1045">
@@ -34840,7 +34840,7 @@
         </is>
       </c>
       <c r="G1045">
-        <v>37.92292530664029</v>
+        <v>37.85715172199285</v>
       </c>
     </row>
     <row r="1046">
@@ -34873,7 +34873,7 @@
         </is>
       </c>
       <c r="G1046">
-        <v>2.827530356041547</v>
+        <v>2.829108112320575</v>
       </c>
     </row>
     <row r="1047">
@@ -34906,7 +34906,7 @@
         </is>
       </c>
       <c r="G1047">
-        <v>42.64210567264144</v>
+        <v>42.59661564879598</v>
       </c>
     </row>
     <row r="1048">
@@ -34939,7 +34939,7 @@
         </is>
       </c>
       <c r="G1048">
-        <v>2.800579243362396</v>
+        <v>2.802878090948489</v>
       </c>
     </row>
     <row r="1049">
@@ -34972,7 +34972,7 @@
         </is>
       </c>
       <c r="G1049">
-        <v>47.50859615347701</v>
+        <v>47.47903136692857</v>
       </c>
     </row>
     <row r="1050">
@@ -35005,7 +35005,7 @@
         </is>
       </c>
       <c r="G1050">
-        <v>2.778095049262614</v>
+        <v>2.781202944011681</v>
       </c>
     </row>
     <row r="1051">
@@ -35038,7 +35038,7 @@
         </is>
       </c>
       <c r="G1051">
-        <v>52.21724440087955</v>
+        <v>52.20054057510845</v>
       </c>
     </row>
     <row r="1052">
@@ -35071,7 +35071,7 @@
         </is>
       </c>
       <c r="G1052">
-        <v>0.3903380152917121</v>
+        <v>0.3901382516731689</v>
       </c>
     </row>
     <row r="1053">
@@ -35104,7 +35104,7 @@
         </is>
       </c>
       <c r="G1053">
-        <v>0.3903380152917121</v>
+        <v>0.3901382516731689</v>
       </c>
     </row>
     <row r="1054">
@@ -35137,7 +35137,7 @@
         </is>
       </c>
       <c r="G1054">
-        <v>0.5196862427044653</v>
+        <v>0.5130394752874314</v>
       </c>
     </row>
     <row r="1055">
@@ -35170,7 +35170,7 @@
         </is>
       </c>
       <c r="G1055">
-        <v>0.5196862427044653</v>
+        <v>0.5130394752874314</v>
       </c>
     </row>
     <row r="1056">
@@ -35203,7 +35203,7 @@
         </is>
       </c>
       <c r="G1056">
-        <v>0.7141290276608735</v>
+        <v>0.7060854349427141</v>
       </c>
     </row>
     <row r="1057">
@@ -35236,7 +35236,7 @@
         </is>
       </c>
       <c r="G1057">
-        <v>0.7141290276608735</v>
+        <v>0.7060854349427141</v>
       </c>
     </row>
     <row r="1058">
@@ -35269,7 +35269,7 @@
         </is>
       </c>
       <c r="G1058">
-        <v>0.9715203532894144</v>
+        <v>0.9609488778248095</v>
       </c>
     </row>
     <row r="1059">
@@ -35302,7 +35302,7 @@
         </is>
       </c>
       <c r="G1059">
-        <v>0.9715203532894144</v>
+        <v>0.9609488778248095</v>
       </c>
     </row>
     <row r="1060">
@@ -35335,7 +35335,7 @@
         </is>
       </c>
       <c r="G1060">
-        <v>1.277632629539891</v>
+        <v>1.263926751529495</v>
       </c>
     </row>
     <row r="1061">
@@ -35368,7 +35368,7 @@
         </is>
       </c>
       <c r="G1061">
-        <v>1.277632629539891</v>
+        <v>1.263926751529495</v>
       </c>
     </row>
     <row r="1062">
@@ -35401,7 +35401,7 @@
         </is>
       </c>
       <c r="G1062">
-        <v>1.698228569034433</v>
+        <v>1.679421057051742</v>
       </c>
     </row>
     <row r="1063">
@@ -35434,7 +35434,7 @@
         </is>
       </c>
       <c r="G1063">
-        <v>1.698228569034433</v>
+        <v>1.679421057051742</v>
       </c>
     </row>
     <row r="1064">
@@ -35467,7 +35467,7 @@
         </is>
       </c>
       <c r="G1064">
-        <v>2.306370370966131</v>
+        <v>2.280674289672886</v>
       </c>
     </row>
     <row r="1065">
@@ -35500,7 +35500,7 @@
         </is>
       </c>
       <c r="G1065">
-        <v>2.306370370966131</v>
+        <v>2.280674289672886</v>
       </c>
     </row>
     <row r="1066">
@@ -35533,7 +35533,7 @@
         </is>
       </c>
       <c r="G1066">
-        <v>2.908521335503783</v>
+        <v>2.874010683748469</v>
       </c>
     </row>
     <row r="1067">
@@ -35566,7 +35566,7 @@
         </is>
       </c>
       <c r="G1067">
-        <v>2.908521335503783</v>
+        <v>2.874010683748469</v>
       </c>
     </row>
     <row r="1068">
@@ -35599,7 +35599,7 @@
         </is>
       </c>
       <c r="G1068">
-        <v>3.668041365986013</v>
+        <v>3.620926348908724</v>
       </c>
     </row>
     <row r="1069">
@@ -35632,7 +35632,7 @@
         </is>
       </c>
       <c r="G1069">
-        <v>3.668041365986013</v>
+        <v>3.620926348908724</v>
       </c>
     </row>
     <row r="1070">
@@ -35665,7 +35665,7 @@
         </is>
       </c>
       <c r="G1070">
-        <v>4.667088385535414</v>
+        <v>4.602071450839002</v>
       </c>
     </row>
     <row r="1071">
@@ -35698,7 +35698,7 @@
         </is>
       </c>
       <c r="G1071">
-        <v>4.667088385535414</v>
+        <v>4.602071450839002</v>
       </c>
     </row>
     <row r="1072">
@@ -35731,7 +35731,7 @@
         </is>
       </c>
       <c r="G1072">
-        <v>5.450345787700399</v>
+        <v>5.435407986455243</v>
       </c>
     </row>
     <row r="1073">
@@ -35764,7 +35764,7 @@
         </is>
       </c>
       <c r="G1073">
-        <v>6.338782166239645</v>
+        <v>6.24546537644353</v>
       </c>
     </row>
     <row r="1074">
@@ -35797,7 +35797,7 @@
         </is>
       </c>
       <c r="G1074">
-        <v>5.332851635447242</v>
+        <v>5.321270203014372</v>
       </c>
     </row>
     <row r="1075">
@@ -35830,7 +35830,7 @@
         </is>
       </c>
       <c r="G1075">
-        <v>8.515188111298251</v>
+        <v>8.385721036269686</v>
       </c>
     </row>
     <row r="1076">
@@ -35863,7 +35863,7 @@
         </is>
       </c>
       <c r="G1076">
-        <v>5.204097646038262</v>
+        <v>5.198010252207658</v>
       </c>
     </row>
     <row r="1077">
@@ -35896,7 +35896,7 @@
         </is>
       </c>
       <c r="G1077">
-        <v>11.11152913950355</v>
+        <v>10.94223090048816</v>
       </c>
     </row>
     <row r="1078">
@@ -35929,7 +35929,7 @@
         </is>
       </c>
       <c r="G1078">
-        <v>5.122640336992864</v>
+        <v>5.090985882070745</v>
       </c>
     </row>
     <row r="1079">
@@ -35962,7 +35962,7 @@
         </is>
       </c>
       <c r="G1079">
-        <v>15.18160117147743</v>
+        <v>14.64819860483166</v>
       </c>
     </row>
     <row r="1080">
@@ -35995,7 +35995,7 @@
         </is>
       </c>
       <c r="G1080">
-        <v>4.880515048099109</v>
+        <v>4.851311429031754</v>
       </c>
     </row>
     <row r="1081">
@@ -36028,7 +36028,7 @@
         </is>
       </c>
       <c r="G1081">
-        <v>18.61947188158106</v>
+        <v>18.01064184377456</v>
       </c>
     </row>
     <row r="1082">
@@ -36061,7 +36061,7 @@
         </is>
       </c>
       <c r="G1082">
-        <v>4.592982327624139</v>
+        <v>4.568103746244791</v>
       </c>
     </row>
     <row r="1083">
@@ -36094,7 +36094,7 @@
         </is>
       </c>
       <c r="G1083">
-        <v>22.06351676552103</v>
+        <v>21.44417853679209</v>
       </c>
     </row>
     <row r="1084">
@@ -36127,7 +36127,7 @@
         </is>
       </c>
       <c r="G1084">
-        <v>4.302753585418466</v>
+        <v>4.283611209155628</v>
       </c>
     </row>
     <row r="1085">
@@ -36160,7 +36160,7 @@
         </is>
       </c>
       <c r="G1085">
-        <v>25.38230114962726</v>
+        <v>24.82749745605003</v>
       </c>
     </row>
     <row r="1086">
@@ -36193,7 +36193,7 @@
         </is>
       </c>
       <c r="G1086">
-        <v>4.033123828381754</v>
+        <v>4.02005329015796</v>
       </c>
     </row>
     <row r="1087">
@@ -36226,7 +36226,7 @@
         </is>
       </c>
       <c r="G1087">
-        <v>28.8304457350784</v>
+        <v>28.38920380434157</v>
       </c>
     </row>
     <row r="1088">
@@ -36259,7 +36259,7 @@
         </is>
       </c>
       <c r="G1088">
-        <v>3.805016867100584</v>
+        <v>3.797180714329415</v>
       </c>
     </row>
     <row r="1089">
@@ -36292,7 +36292,7 @@
         </is>
       </c>
       <c r="G1089">
-        <v>32.56449802865865</v>
+        <v>32.24750928269844</v>
       </c>
     </row>
     <row r="1090">
@@ -36325,7 +36325,7 @@
         </is>
       </c>
       <c r="G1090">
-        <v>3.616662910551822</v>
+        <v>3.612493137938117</v>
       </c>
     </row>
     <row r="1091">
@@ -36358,7 +36358,7 @@
         </is>
       </c>
       <c r="G1091">
-        <v>36.61097405972624</v>
+        <v>36.39678136332235</v>
       </c>
     </row>
     <row r="1092">
@@ -36391,7 +36391,7 @@
         </is>
       </c>
       <c r="G1092">
-        <v>3.457440918582592</v>
+        <v>3.455585355482881</v>
       </c>
     </row>
     <row r="1093">
@@ -36424,7 +36424,7 @@
         </is>
       </c>
       <c r="G1093">
-        <v>40.90372428832193</v>
+        <v>40.7606704839306</v>
       </c>
     </row>
     <row r="1094">
@@ -36457,7 +36457,7 @@
         </is>
       </c>
       <c r="G1094">
-        <v>3.321483787666915</v>
+        <v>3.321164454313607</v>
       </c>
     </row>
     <row r="1095">
@@ -36490,7 +36490,7 @@
         </is>
       </c>
       <c r="G1095">
-        <v>45.43958964248152</v>
+        <v>45.34234651378086</v>
       </c>
     </row>
     <row r="1096">
@@ -36523,7 +36523,7 @@
         </is>
       </c>
       <c r="G1096">
-        <v>3.200555700134637</v>
+        <v>3.201426152578937</v>
       </c>
     </row>
     <row r="1097">
@@ -36556,7 +36556,7 @@
         </is>
       </c>
       <c r="G1097">
-        <v>49.99818077781146</v>
+        <v>49.93152207297172</v>
       </c>
     </row>
     <row r="1098">
@@ -36589,7 +36589,7 @@
         </is>
       </c>
       <c r="G1098">
-        <v>3.093824136875224</v>
+        <v>3.095801506289753</v>
       </c>
     </row>
     <row r="1099">
@@ -36622,7 +36622,7 @@
         </is>
       </c>
       <c r="G1099">
-        <v>54.53310085299265</v>
+        <v>54.48971460804284</v>
       </c>
     </row>
     <row r="1100">
@@ -36655,7 +36655,7 @@
         </is>
       </c>
       <c r="G1100">
-        <v>2.998638616943885</v>
+        <v>3.001669640516135</v>
       </c>
     </row>
     <row r="1101">
@@ -36688,7 +36688,7 @@
         </is>
       </c>
       <c r="G1101">
-        <v>58.73079469784371</v>
+        <v>58.70564918695155</v>
       </c>
     </row>
     <row r="1102">
@@ -36721,7 +36721,7 @@
         </is>
       </c>
       <c r="G1102">
-        <v>0.4214261542215228</v>
+        <v>0.4211961896220597</v>
       </c>
     </row>
     <row r="1103">
@@ -36754,7 +36754,7 @@
         </is>
       </c>
       <c r="G1103">
-        <v>0.4214261542215228</v>
+        <v>0.4211961896220597</v>
       </c>
     </row>
     <row r="1104">
@@ -36787,7 +36787,7 @@
         </is>
       </c>
       <c r="G1104">
-        <v>0.5630953408779972</v>
+        <v>0.5560586822779416</v>
       </c>
     </row>
     <row r="1105">
@@ -36820,7 +36820,7 @@
         </is>
       </c>
       <c r="G1105">
-        <v>0.5630953408779972</v>
+        <v>0.5560586822779416</v>
       </c>
     </row>
     <row r="1106">
@@ -36853,7 +36853,7 @@
         </is>
       </c>
       <c r="G1106">
-        <v>0.782861249620826</v>
+        <v>0.7741970083370653</v>
       </c>
     </row>
     <row r="1107">
@@ -36886,7 +36886,7 @@
         </is>
       </c>
       <c r="G1107">
-        <v>0.782861249620826</v>
+        <v>0.7741970083370653</v>
       </c>
     </row>
     <row r="1108">
@@ -36919,7 +36919,7 @@
         </is>
       </c>
       <c r="G1108">
-        <v>1.080916247756608</v>
+        <v>1.069304111527772</v>
       </c>
     </row>
     <row r="1109">
@@ -36952,7 +36952,7 @@
         </is>
       </c>
       <c r="G1109">
-        <v>1.080916247756608</v>
+        <v>1.069304111527772</v>
       </c>
     </row>
     <row r="1110">
@@ -36985,7 +36985,7 @@
         </is>
       </c>
       <c r="G1110">
-        <v>1.448075219135011</v>
+        <v>1.43267658642608</v>
       </c>
     </row>
     <row r="1111">
@@ -37018,7 +37018,7 @@
         </is>
       </c>
       <c r="G1111">
-        <v>1.448075219135011</v>
+        <v>1.43267658642608</v>
       </c>
     </row>
     <row r="1112">
@@ -37051,7 +37051,7 @@
         </is>
       </c>
       <c r="G1112">
-        <v>1.966691795862715</v>
+        <v>1.944992665442652</v>
       </c>
     </row>
     <row r="1113">
@@ -37084,7 +37084,7 @@
         </is>
       </c>
       <c r="G1113">
-        <v>1.966691795862715</v>
+        <v>1.944992665442652</v>
       </c>
     </row>
     <row r="1114">
@@ -37117,7 +37117,7 @@
         </is>
       </c>
       <c r="G1114">
-        <v>2.722922492740672</v>
+        <v>2.692572407307709</v>
       </c>
     </row>
     <row r="1115">
@@ -37150,7 +37150,7 @@
         </is>
       </c>
       <c r="G1115">
-        <v>2.722922492740672</v>
+        <v>2.692572407307709</v>
       </c>
     </row>
     <row r="1116">
@@ -37183,7 +37183,7 @@
         </is>
       </c>
       <c r="G1116">
-        <v>3.483036271722939</v>
+        <v>3.441480177896676</v>
       </c>
     </row>
     <row r="1117">
@@ -37216,7 +37216,7 @@
         </is>
       </c>
       <c r="G1117">
-        <v>3.483036271722939</v>
+        <v>3.441480177896676</v>
       </c>
     </row>
     <row r="1118">
@@ -37249,7 +37249,7 @@
         </is>
       </c>
       <c r="G1118">
-        <v>4.450805989287345</v>
+        <v>4.392986973255916</v>
       </c>
     </row>
     <row r="1119">
@@ -37282,7 +37282,7 @@
         </is>
       </c>
       <c r="G1119">
-        <v>4.450805989287345</v>
+        <v>4.392986973255916</v>
       </c>
     </row>
     <row r="1120">
@@ -37315,7 +37315,7 @@
         </is>
       </c>
       <c r="G1120">
-        <v>5.74224775334786</v>
+        <v>5.660925845826183</v>
       </c>
     </row>
     <row r="1121">
@@ -37348,7 +37348,7 @@
         </is>
       </c>
       <c r="G1121">
-        <v>5.74224775334786</v>
+        <v>5.660925845826183</v>
       </c>
     </row>
     <row r="1122">
@@ -37381,7 +37381,7 @@
         </is>
       </c>
       <c r="G1122">
-        <v>7.691434400882277</v>
+        <v>7.575796083449543</v>
       </c>
     </row>
     <row r="1123">
@@ -37414,7 +37414,7 @@
         </is>
       </c>
       <c r="G1123">
-        <v>7.691434400882277</v>
+        <v>7.575796083449543</v>
       </c>
     </row>
     <row r="1124">
@@ -37447,7 +37447,7 @@
         </is>
       </c>
       <c r="G1124">
-        <v>9.341565927082261</v>
+        <v>9.335761309385394</v>
       </c>
     </row>
     <row r="1125">
@@ -37480,7 +37480,7 @@
         </is>
       </c>
       <c r="G1125">
-        <v>10.2198553643567</v>
+        <v>10.06042877932188</v>
       </c>
     </row>
     <row r="1126">
@@ -37513,7 +37513,7 @@
         </is>
       </c>
       <c r="G1126">
-        <v>9.137507199519263</v>
+        <v>9.143720540929269</v>
       </c>
     </row>
     <row r="1127">
@@ -37546,7 +37546,7 @@
         </is>
       </c>
       <c r="G1127">
-        <v>13.18093228343478</v>
+        <v>12.97375574156704</v>
       </c>
     </row>
     <row r="1128">
@@ -37579,7 +37579,7 @@
         </is>
       </c>
       <c r="G1128">
-        <v>8.968848013002582</v>
+        <v>8.946978657359992</v>
       </c>
     </row>
     <row r="1129">
@@ -37612,7 +37612,7 @@
         </is>
       </c>
       <c r="G1129">
-        <v>17.84481957889148</v>
+        <v>17.19346840642986</v>
       </c>
     </row>
     <row r="1130">
@@ -37645,7 +37645,7 @@
         </is>
       </c>
       <c r="G1130">
-        <v>8.492823538669201</v>
+        <v>8.473289227780169</v>
       </c>
     </row>
     <row r="1131">
@@ -37678,7 +37678,7 @@
         </is>
       </c>
       <c r="G1131">
-        <v>21.29745187077332</v>
+        <v>20.56428070661341</v>
       </c>
     </row>
     <row r="1132">
@@ -37711,7 +37711,7 @@
         </is>
       </c>
       <c r="G1132">
-        <v>8.090920578130358</v>
+        <v>8.074466750615539</v>
       </c>
     </row>
     <row r="1133">
@@ -37744,7 +37744,7 @@
         </is>
       </c>
       <c r="G1133">
-        <v>24.88559556556438</v>
+        <v>24.13912096419235</v>
       </c>
     </row>
     <row r="1134">
@@ -37777,7 +37777,7 @@
         </is>
       </c>
       <c r="G1134">
-        <v>7.686170149412576</v>
+        <v>7.673719119367957</v>
       </c>
     </row>
     <row r="1135">
@@ -37810,7 +37810,7 @@
         </is>
       </c>
       <c r="G1135">
-        <v>28.18151832333492</v>
+        <v>27.51261848279629</v>
       </c>
     </row>
     <row r="1136">
@@ -37843,7 +37843,7 @@
         </is>
       </c>
       <c r="G1136">
-        <v>7.314824739297459</v>
+        <v>7.30667376430203</v>
       </c>
     </row>
     <row r="1137">
@@ -37876,7 +37876,7 @@
         </is>
       </c>
       <c r="G1137">
-        <v>31.48765174111406</v>
+        <v>30.95572273139884</v>
       </c>
     </row>
     <row r="1138">
@@ -37909,7 +37909,7 @@
         </is>
       </c>
       <c r="G1138">
-        <v>7.014441304744431</v>
+        <v>7.010153217142484</v>
       </c>
     </row>
     <row r="1139">
@@ -37942,7 +37942,7 @@
         </is>
       </c>
       <c r="G1139">
-        <v>34.98573644540095</v>
+        <v>34.60393367070137</v>
       </c>
     </row>
     <row r="1140">
@@ -37975,7 +37975,7 @@
         </is>
       </c>
       <c r="G1140">
-        <v>6.775708488031347</v>
+        <v>6.774133471427804</v>
       </c>
     </row>
     <row r="1141">
@@ -38008,7 +38008,7 @@
         </is>
       </c>
       <c r="G1141">
-        <v>38.70472225715924</v>
+        <v>38.44725795675414</v>
       </c>
     </row>
     <row r="1142">
@@ -38041,7 +38041,7 @@
         </is>
       </c>
       <c r="G1142">
-        <v>6.582376265346468</v>
+        <v>6.582640393933229</v>
       </c>
     </row>
     <row r="1143">
@@ -38074,7 +38074,7 @@
         </is>
       </c>
       <c r="G1143">
-        <v>42.58659080072977</v>
+        <v>42.41524737649436</v>
       </c>
     </row>
     <row r="1144">
@@ -38107,7 +38107,7 @@
         </is>
       </c>
       <c r="G1144">
-        <v>6.428151901304233</v>
+        <v>6.42994857073073</v>
       </c>
     </row>
     <row r="1145">
@@ -38140,7 +38140,7 @@
         </is>
       </c>
       <c r="G1145">
-        <v>46.64442812183744</v>
+        <v>46.52840186521911</v>
       </c>
     </row>
     <row r="1146">
@@ -38173,7 +38173,7 @@
         </is>
       </c>
       <c r="G1146">
-        <v>6.299930830172531</v>
+        <v>6.303296891240562</v>
       </c>
     </row>
     <row r="1147">
@@ -38206,7 +38206,7 @@
         </is>
       </c>
       <c r="G1147">
-        <v>50.67253160927816</v>
+        <v>50.59321906903767</v>
       </c>
     </row>
     <row r="1148">
@@ -38239,7 +38239,7 @@
         </is>
       </c>
       <c r="G1148">
-        <v>6.195623447477415</v>
+        <v>6.200811937326376</v>
       </c>
     </row>
     <row r="1149">
@@ -38272,7 +38272,7 @@
         </is>
       </c>
       <c r="G1149">
-        <v>54.64223510411313</v>
+        <v>54.59042122472388</v>
       </c>
     </row>
     <row r="1150">
@@ -38305,7 +38305,7 @@
         </is>
       </c>
       <c r="G1150">
-        <v>6.111322859759846</v>
+        <v>6.118511958740817</v>
       </c>
     </row>
     <row r="1151">
@@ -38338,7 +38338,7 @@
         </is>
       </c>
       <c r="G1151">
-        <v>58.39340372898446</v>
+        <v>58.3628099868675</v>
       </c>
     </row>
     <row r="1152">
@@ -38371,7 +38371,7 @@
         </is>
       </c>
       <c r="G1152">
-        <v>0.4373931591323327</v>
+        <v>0.4371544301720377</v>
       </c>
     </row>
     <row r="1153">
@@ -38404,7 +38404,7 @@
         </is>
       </c>
       <c r="G1153">
-        <v>0.4373931591323327</v>
+        <v>0.4371544301720377</v>
       </c>
     </row>
     <row r="1154">
@@ -38437,7 +38437,7 @@
         </is>
       </c>
       <c r="G1154">
-        <v>0.6123508850363784</v>
+        <v>0.604693850148539</v>
       </c>
     </row>
     <row r="1155">
@@ -38470,7 +38470,7 @@
         </is>
       </c>
       <c r="G1155">
-        <v>0.6123508850363784</v>
+        <v>0.604693850148539</v>
       </c>
     </row>
     <row r="1156">
@@ -38503,7 +38503,7 @@
         </is>
       </c>
       <c r="G1156">
-        <v>0.8803889717314297</v>
+        <v>0.8706214802402428</v>
       </c>
     </row>
     <row r="1157">
@@ -38536,7 +38536,7 @@
         </is>
       </c>
       <c r="G1157">
-        <v>0.8803889717314297</v>
+        <v>0.8706214802402428</v>
       </c>
     </row>
     <row r="1158">
@@ -38569,7 +38569,7 @@
         </is>
       </c>
       <c r="G1158">
-        <v>1.251827246091813</v>
+        <v>1.238319484393418</v>
       </c>
     </row>
     <row r="1159">
@@ -38602,7 +38602,7 @@
         </is>
       </c>
       <c r="G1159">
-        <v>1.251827246091813</v>
+        <v>1.238319484393418</v>
       </c>
     </row>
     <row r="1160">
@@ -38635,7 +38635,7 @@
         </is>
       </c>
       <c r="G1160">
-        <v>1.719240855803296</v>
+        <v>1.700834448763278</v>
       </c>
     </row>
     <row r="1161">
@@ -38668,7 +38668,7 @@
         </is>
       </c>
       <c r="G1161">
-        <v>1.719240855803296</v>
+        <v>1.700834448763278</v>
       </c>
     </row>
     <row r="1162">
@@ -38701,7 +38701,7 @@
         </is>
       </c>
       <c r="G1162">
-        <v>2.380141876963897</v>
+        <v>2.353625594620185</v>
       </c>
     </row>
     <row r="1163">
@@ -38734,7 +38734,7 @@
         </is>
       </c>
       <c r="G1163">
-        <v>2.380141876963897</v>
+        <v>2.353625594620185</v>
       </c>
     </row>
     <row r="1164">
@@ -38767,7 +38767,7 @@
         </is>
       </c>
       <c r="G1164">
-        <v>3.367695451796009</v>
+        <v>3.329692498690069</v>
       </c>
     </row>
     <row r="1165">
@@ -38800,7 +38800,7 @@
         </is>
       </c>
       <c r="G1165">
-        <v>3.367695451796009</v>
+        <v>3.329692498690069</v>
       </c>
     </row>
     <row r="1166">
@@ -38833,7 +38833,7 @@
         </is>
       </c>
       <c r="G1166">
-        <v>4.414005147132947</v>
+        <v>4.360520115744526</v>
       </c>
     </row>
     <row r="1167">
@@ -38866,7 +38866,7 @@
         </is>
       </c>
       <c r="G1167">
-        <v>4.414005147132947</v>
+        <v>4.360520115744526</v>
       </c>
     </row>
     <row r="1168">
@@ -38899,7 +38899,7 @@
         </is>
       </c>
       <c r="G1168">
-        <v>5.770654106380673</v>
+        <v>5.694214283451897</v>
       </c>
     </row>
     <row r="1169">
@@ -38932,7 +38932,7 @@
         </is>
       </c>
       <c r="G1169">
-        <v>5.770654106380673</v>
+        <v>5.694214283451897</v>
       </c>
     </row>
     <row r="1170">
@@ -38965,7 +38965,7 @@
         </is>
       </c>
       <c r="G1170">
-        <v>7.60578611881451</v>
+        <v>7.495465891689316</v>
       </c>
     </row>
     <row r="1171">
@@ -38998,7 +38998,7 @@
         </is>
       </c>
       <c r="G1171">
-        <v>7.60578611881451</v>
+        <v>7.495465891689316</v>
       </c>
     </row>
     <row r="1172">
@@ -39031,7 +39031,7 @@
         </is>
       </c>
       <c r="G1172">
-        <v>10.35685717205249</v>
+        <v>10.19659351414861</v>
       </c>
     </row>
     <row r="1173">
@@ -39064,7 +39064,7 @@
         </is>
       </c>
       <c r="G1173">
-        <v>10.35685717205249</v>
+        <v>10.19659351414861</v>
       </c>
     </row>
     <row r="1174">
@@ -39097,7 +39097,7 @@
         </is>
       </c>
       <c r="G1174">
-        <v>12.68400334752723</v>
+        <v>12.66817641271379</v>
       </c>
     </row>
     <row r="1175">
@@ -39130,7 +39130,7 @@
         </is>
       </c>
       <c r="G1175">
-        <v>13.93995747347594</v>
+        <v>13.71477030171532</v>
       </c>
     </row>
     <row r="1176">
@@ -39163,7 +39163,7 @@
         </is>
       </c>
       <c r="G1176">
-        <v>12.53825667463718</v>
+        <v>12.53674773081416</v>
       </c>
     </row>
     <row r="1177">
@@ -39196,7 +39196,7 @@
         </is>
       </c>
       <c r="G1177">
-        <v>18.1864034010961</v>
+        <v>17.88767555425394</v>
       </c>
     </row>
     <row r="1178">
@@ -39229,7 +39229,7 @@
         </is>
       </c>
       <c r="G1178">
-        <v>12.4262477345063</v>
+        <v>12.37256562713937</v>
       </c>
     </row>
     <row r="1179">
@@ -39262,7 +39262,7 @@
         </is>
       </c>
       <c r="G1179">
-        <v>24.8775621985143</v>
+        <v>23.92922821242976</v>
       </c>
     </row>
     <row r="1180">
@@ -39295,7 +39295,7 @@
         </is>
       </c>
       <c r="G1180">
-        <v>11.91273313382674</v>
+        <v>11.8579000049034</v>
       </c>
     </row>
     <row r="1181">
@@ -39328,7 +39328,7 @@
         </is>
       </c>
       <c r="G1181">
-        <v>30.11019776593566</v>
+        <v>29.01361078856091</v>
       </c>
     </row>
     <row r="1182">
@@ -39361,7 +39361,7 @@
         </is>
       </c>
       <c r="G1182">
-        <v>11.13709443488616</v>
+        <v>11.08481069635734</v>
       </c>
     </row>
     <row r="1183">
@@ -39394,7 +39394,7 @@
         </is>
       </c>
       <c r="G1183">
-        <v>34.61163954199827</v>
+        <v>33.49305525460882</v>
       </c>
     </row>
     <row r="1184">
@@ -39427,7 +39427,7 @@
         </is>
       </c>
       <c r="G1184">
-        <v>10.33094504119471</v>
+        <v>10.28582451021567</v>
       </c>
     </row>
     <row r="1185">
@@ -39460,7 +39460,7 @@
         </is>
       </c>
       <c r="G1185">
-        <v>38.39221889790944</v>
+        <v>37.3880519873362</v>
       </c>
     </row>
     <row r="1186">
@@ -39493,7 +39493,7 @@
         </is>
       </c>
       <c r="G1186">
-        <v>9.564110403147515</v>
+        <v>9.529810765908884</v>
       </c>
     </row>
     <row r="1187">
@@ -39526,7 +39526,7 @@
         </is>
       </c>
       <c r="G1187">
-        <v>41.87606186271048</v>
+        <v>41.07659107388495</v>
       </c>
     </row>
     <row r="1188">
@@ -39559,7 +39559,7 @@
         </is>
       </c>
       <c r="G1188">
-        <v>8.907696986304375</v>
+        <v>8.884981094192163</v>
       </c>
     </row>
     <row r="1189">
@@ -39592,7 +39592,7 @@
         </is>
       </c>
       <c r="G1189">
-        <v>45.35886710521535</v>
+        <v>44.78502782437956</v>
       </c>
     </row>
     <row r="1190">
@@ -39625,7 +39625,7 @@
         </is>
       </c>
       <c r="G1190">
-        <v>8.364167986117085</v>
+        <v>8.350743325025203</v>
       </c>
     </row>
     <row r="1191">
@@ -39658,7 +39658,7 @@
         </is>
       </c>
       <c r="G1191">
-        <v>48.95462793615523</v>
+        <v>48.56836011213257</v>
       </c>
     </row>
     <row r="1192">
@@ -39691,7 +39691,7 @@
         </is>
       </c>
       <c r="G1192">
-        <v>7.909797981678075</v>
+        <v>7.902755937105903</v>
       </c>
     </row>
     <row r="1193">
@@ -39724,7 +39724,7 @@
         </is>
       </c>
       <c r="G1193">
-        <v>52.61343883329342</v>
+        <v>52.35734458237216</v>
       </c>
     </row>
     <row r="1194">
@@ -39757,7 +39757,7 @@
         </is>
       </c>
       <c r="G1194">
-        <v>7.525965024645891</v>
+        <v>7.523301021995604</v>
       </c>
     </row>
     <row r="1195">
@@ -39790,7 +39790,7 @@
         </is>
       </c>
       <c r="G1195">
-        <v>56.32972565359161</v>
+        <v>56.15704027033053</v>
       </c>
     </row>
     <row r="1196">
@@ -39823,7 +39823,7 @@
         </is>
       </c>
       <c r="G1196">
-        <v>7.19057604579533</v>
+        <v>7.191270953907139</v>
       </c>
     </row>
     <row r="1197">
@@ -39856,7 +39856,7 @@
         </is>
       </c>
       <c r="G1197">
-        <v>59.84428119299928</v>
+        <v>59.72650033487037</v>
       </c>
     </row>
     <row r="1198">
@@ -39889,7 +39889,7 @@
         </is>
       </c>
       <c r="G1198">
-        <v>6.897919259593804</v>
+        <v>6.901629565418597</v>
       </c>
     </row>
     <row r="1199">
@@ -39922,7 +39922,7 @@
         </is>
       </c>
       <c r="G1199">
-        <v>63.13749030319574</v>
+        <v>63.05994983116212</v>
       </c>
     </row>
     <row r="1200">
@@ -39955,7 +39955,7 @@
         </is>
       </c>
       <c r="G1200">
-        <v>6.643374088659892</v>
+        <v>6.649882671021598</v>
       </c>
     </row>
     <row r="1201">
@@ -39988,7 +39988,7 @@
         </is>
       </c>
       <c r="G1201">
-        <v>66.06193265238367</v>
+        <v>66.01484030903735</v>
       </c>
     </row>
   </sheetData>
